--- a/Quality.xlsx
+++ b/Quality.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30431"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ppgclindia-my.sharepoint.com/personal/bikram_mohapatra_ppgcl_co_in/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72C31736-1AE6-4E80-8C99-9F65D0F5CD82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA2327CE-418C-4AB9-A556-5A5AA38B8110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JULY-26" sheetId="11" r:id="rId1"/>
     <sheet name="Aug-26" sheetId="12" r:id="rId2"/>
+    <sheet name="Sep-26" sheetId="13" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2537" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2107" uniqueCount="56">
   <si>
     <t>IGI Report</t>
   </si>
@@ -217,9 +218,6 @@
     <t>GCV kcal/kg</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>DW-1</t>
   </si>
   <si>
@@ -303,7 +301,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -340,8 +338,14 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -509,11 +513,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -617,14 +654,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -632,7 +684,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -656,10 +708,16 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1005,21 +1063,21 @@
       <c r="U1" s="13"/>
       <c r="V1" s="13"/>
       <c r="W1" s="13"/>
-      <c r="X1" s="35" t="s">
+      <c r="X1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="36"/>
-      <c r="AD1" s="36"/>
-      <c r="AE1" s="36"/>
-      <c r="AF1" s="36"/>
-      <c r="AG1" s="36"/>
-      <c r="AH1" s="36"/>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="37"/>
+      <c r="Y1" s="54"/>
+      <c r="Z1" s="54"/>
+      <c r="AA1" s="54"/>
+      <c r="AB1" s="54"/>
+      <c r="AC1" s="54"/>
+      <c r="AD1" s="54"/>
+      <c r="AE1" s="54"/>
+      <c r="AF1" s="54"/>
+      <c r="AG1" s="54"/>
+      <c r="AH1" s="54"/>
+      <c r="AI1" s="54"/>
+      <c r="AJ1" s="55"/>
     </row>
     <row r="2" spans="1:36" ht="15" customHeight="1">
       <c r="A2" s="15"/>
@@ -1037,43 +1095,43 @@
       <c r="M2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="38" t="s">
+      <c r="N2" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="39"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="44"/>
       <c r="W2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="40" t="s">
+      <c r="X2" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="Y2" s="42" t="s">
+      <c r="Y2" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="Z2" s="43"/>
-      <c r="AA2" s="43"/>
-      <c r="AB2" s="44"/>
-      <c r="AC2" s="48" t="s">
+      <c r="Z2" s="48"/>
+      <c r="AA2" s="48"/>
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="AD2" s="48" t="s">
+      <c r="AD2" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="42" t="s">
+      <c r="AE2" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="AF2" s="43"/>
-      <c r="AG2" s="43"/>
-      <c r="AH2" s="43"/>
-      <c r="AI2" s="44"/>
-      <c r="AJ2" s="48" t="s">
+      <c r="AF2" s="48"/>
+      <c r="AG2" s="48"/>
+      <c r="AH2" s="48"/>
+      <c r="AI2" s="49"/>
+      <c r="AJ2" s="41" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1147,19 +1205,19 @@
       <c r="W3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="45"/>
-      <c r="Z3" s="46"/>
-      <c r="AA3" s="46"/>
-      <c r="AB3" s="47"/>
-      <c r="AC3" s="48"/>
-      <c r="AD3" s="48"/>
-      <c r="AE3" s="45"/>
-      <c r="AF3" s="46"/>
-      <c r="AG3" s="46"/>
-      <c r="AH3" s="46"/>
-      <c r="AI3" s="47"/>
-      <c r="AJ3" s="48"/>
+      <c r="X3" s="46"/>
+      <c r="Y3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
+      <c r="AB3" s="52"/>
+      <c r="AC3" s="41"/>
+      <c r="AD3" s="41"/>
+      <c r="AE3" s="50"/>
+      <c r="AF3" s="51"/>
+      <c r="AG3" s="51"/>
+      <c r="AH3" s="51"/>
+      <c r="AI3" s="52"/>
+      <c r="AJ3" s="41"/>
     </row>
     <row r="4" spans="1:36" ht="60.75">
       <c r="A4" s="11" t="s">
@@ -1246,8 +1304,8 @@
       <c r="AB4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AC4" s="49"/>
-      <c r="AD4" s="49"/>
+      <c r="AC4" s="42"/>
+      <c r="AD4" s="42"/>
       <c r="AE4" s="6" t="s">
         <v>32</v>
       </c>
@@ -1263,7 +1321,7 @@
       <c r="AI4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AJ4" s="49"/>
+      <c r="AJ4" s="42"/>
     </row>
     <row r="5" spans="1:36">
       <c r="A5" s="24">
@@ -14369,7 +14427,9 @@
   <dimension ref="A1:AJ112"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="16384" width="10.42578125" style="1"/>
+    <col min="1" max="8" width="10.42578125" style="1"/>
+    <col min="9" max="9" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.42578125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36">
@@ -14396,21 +14456,21 @@
       <c r="U1" s="13"/>
       <c r="V1" s="13"/>
       <c r="W1" s="13"/>
-      <c r="X1" s="35" t="s">
+      <c r="X1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="36"/>
-      <c r="AD1" s="36"/>
-      <c r="AE1" s="36"/>
-      <c r="AF1" s="36"/>
-      <c r="AG1" s="36"/>
-      <c r="AH1" s="36"/>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="37"/>
+      <c r="Y1" s="54"/>
+      <c r="Z1" s="54"/>
+      <c r="AA1" s="54"/>
+      <c r="AB1" s="54"/>
+      <c r="AC1" s="54"/>
+      <c r="AD1" s="54"/>
+      <c r="AE1" s="54"/>
+      <c r="AF1" s="54"/>
+      <c r="AG1" s="54"/>
+      <c r="AH1" s="54"/>
+      <c r="AI1" s="54"/>
+      <c r="AJ1" s="55"/>
     </row>
     <row r="2" spans="1:36" ht="15.75" customHeight="1">
       <c r="A2" s="15"/>
@@ -14426,43 +14486,43 @@
       <c r="K2" s="31"/>
       <c r="L2" s="16"/>
       <c r="M2" s="17"/>
-      <c r="N2" s="38" t="s">
+      <c r="N2" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="39"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="44"/>
       <c r="W2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="40" t="s">
+      <c r="X2" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="Y2" s="42" t="s">
+      <c r="Y2" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="Z2" s="43"/>
-      <c r="AA2" s="43"/>
-      <c r="AB2" s="44"/>
-      <c r="AC2" s="48" t="s">
+      <c r="Z2" s="48"/>
+      <c r="AA2" s="48"/>
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="AD2" s="48" t="s">
+      <c r="AD2" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="42" t="s">
+      <c r="AE2" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="AF2" s="43"/>
-      <c r="AG2" s="43"/>
-      <c r="AH2" s="43"/>
-      <c r="AI2" s="44"/>
-      <c r="AJ2" s="48" t="s">
+      <c r="AF2" s="48"/>
+      <c r="AG2" s="48"/>
+      <c r="AH2" s="48"/>
+      <c r="AI2" s="49"/>
+      <c r="AJ2" s="41" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14510,19 +14570,19 @@
       <c r="W3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="45"/>
-      <c r="Z3" s="46"/>
-      <c r="AA3" s="46"/>
-      <c r="AB3" s="47"/>
-      <c r="AC3" s="48"/>
-      <c r="AD3" s="48"/>
-      <c r="AE3" s="45"/>
-      <c r="AF3" s="46"/>
-      <c r="AG3" s="46"/>
-      <c r="AH3" s="46"/>
-      <c r="AI3" s="47"/>
-      <c r="AJ3" s="48"/>
+      <c r="X3" s="46"/>
+      <c r="Y3" s="50"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
+      <c r="AB3" s="52"/>
+      <c r="AC3" s="41"/>
+      <c r="AD3" s="41"/>
+      <c r="AE3" s="50"/>
+      <c r="AF3" s="51"/>
+      <c r="AG3" s="51"/>
+      <c r="AH3" s="51"/>
+      <c r="AI3" s="52"/>
+      <c r="AJ3" s="41"/>
     </row>
     <row r="4" spans="1:36" ht="60.75">
       <c r="A4" s="11" t="s">
@@ -14609,8 +14669,8 @@
       <c r="AB4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AC4" s="49"/>
-      <c r="AD4" s="49"/>
+      <c r="AC4" s="42"/>
+      <c r="AD4" s="42"/>
       <c r="AE4" s="6" t="s">
         <v>32</v>
       </c>
@@ -14626,7 +14686,7 @@
       <c r="AI4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AJ4" s="49"/>
+      <c r="AJ4" s="42"/>
     </row>
     <row r="5" spans="1:36">
       <c r="A5" s="24">
@@ -18486,7 +18546,7 @@
         <v>16526</v>
       </c>
       <c r="C40" s="25">
-        <v>46607</v>
+        <v>46242</v>
       </c>
       <c r="D40" s="20" t="s">
         <v>1</v>
@@ -18596,7 +18656,7 @@
         <v>16527</v>
       </c>
       <c r="C41" s="25">
-        <v>46973</v>
+        <v>46242</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>1</v>
@@ -18706,7 +18766,7 @@
         <v>16528</v>
       </c>
       <c r="C42" s="25">
-        <v>46973</v>
+        <v>46242</v>
       </c>
       <c r="D42" s="20" t="s">
         <v>1</v>
@@ -18816,7 +18876,7 @@
         <v>16529</v>
       </c>
       <c r="C43" s="25">
-        <v>46973</v>
+        <v>46242</v>
       </c>
       <c r="D43" s="20" t="s">
         <v>1</v>
@@ -18926,7 +18986,7 @@
         <v>16530</v>
       </c>
       <c r="C44" s="25">
-        <v>46973</v>
+        <v>46242</v>
       </c>
       <c r="D44" s="20" t="s">
         <v>1</v>
@@ -19978,44 +20038,44 @@
       <c r="W53" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X53" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y53" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z53" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA53" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB53" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC53" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD53" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE53" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF53" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG53" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH53" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI53" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ53" s="20" t="s">
-        <v>1</v>
+      <c r="X53" s="27">
+        <v>19.670000000000002</v>
+      </c>
+      <c r="Y53" s="27">
+        <v>5.97</v>
+      </c>
+      <c r="Z53" s="27">
+        <v>22.79</v>
+      </c>
+      <c r="AA53" s="27">
+        <v>42.81</v>
+      </c>
+      <c r="AB53" s="27">
+        <v>28.43</v>
+      </c>
+      <c r="AC53" s="27">
+        <v>3571</v>
+      </c>
+      <c r="AD53" s="28">
+        <v>3051</v>
+      </c>
+      <c r="AE53" s="27">
+        <v>6.41</v>
+      </c>
+      <c r="AF53" s="29">
+        <v>22.68</v>
+      </c>
+      <c r="AG53" s="29">
+        <v>42.61</v>
+      </c>
+      <c r="AH53" s="29">
+        <v>28.3</v>
+      </c>
+      <c r="AI53" s="29">
+        <v>3554</v>
+      </c>
+      <c r="AJ53" s="20">
+        <v>3051</v>
       </c>
     </row>
     <row r="54" spans="1:36">
@@ -20088,44 +20148,44 @@
       <c r="W54" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X54" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y54" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z54" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA54" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB54" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC54" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD54" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE54" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF54" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG54" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH54" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI54" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ54" s="20" t="s">
-        <v>1</v>
+      <c r="X54" s="27">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="Y54" s="27">
+        <v>5.49</v>
+      </c>
+      <c r="Z54" s="27">
+        <v>21.31</v>
+      </c>
+      <c r="AA54" s="27">
+        <v>47.64</v>
+      </c>
+      <c r="AB54" s="27">
+        <v>25.56</v>
+      </c>
+      <c r="AC54" s="27">
+        <v>3253</v>
+      </c>
+      <c r="AD54" s="28">
+        <v>2820</v>
+      </c>
+      <c r="AE54" s="27">
+        <v>5.96</v>
+      </c>
+      <c r="AF54" s="29">
+        <v>21.2</v>
+      </c>
+      <c r="AG54" s="29">
+        <v>47.4</v>
+      </c>
+      <c r="AH54" s="29">
+        <v>25.43</v>
+      </c>
+      <c r="AI54" s="29">
+        <v>3237</v>
+      </c>
+      <c r="AJ54" s="20">
+        <v>2820</v>
       </c>
     </row>
     <row r="55" spans="1:36">
@@ -20198,44 +20258,44 @@
       <c r="W55" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X55" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y55" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z55" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA55" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB55" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC55" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD55" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE55" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF55" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG55" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH55" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI55" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ55" s="20" t="s">
-        <v>1</v>
+      <c r="X55" s="27">
+        <v>19.77</v>
+      </c>
+      <c r="Y55" s="27">
+        <v>5.89</v>
+      </c>
+      <c r="Z55" s="27">
+        <v>22.11</v>
+      </c>
+      <c r="AA55" s="27">
+        <v>43.49</v>
+      </c>
+      <c r="AB55" s="27">
+        <v>28.51</v>
+      </c>
+      <c r="AC55" s="27">
+        <v>3537</v>
+      </c>
+      <c r="AD55" s="28">
+        <v>3015</v>
+      </c>
+      <c r="AE55" s="27">
+        <v>6.32</v>
+      </c>
+      <c r="AF55" s="29">
+        <v>22.01</v>
+      </c>
+      <c r="AG55" s="29">
+        <v>43.29</v>
+      </c>
+      <c r="AH55" s="29">
+        <v>28.38</v>
+      </c>
+      <c r="AI55" s="29">
+        <v>3521</v>
+      </c>
+      <c r="AJ55" s="20">
+        <v>3015</v>
       </c>
     </row>
     <row r="56" spans="1:36">
@@ -20308,44 +20368,44 @@
       <c r="W56" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X56" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y56" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z56" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA56" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB56" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC56" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD56" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE56" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF56" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG56" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH56" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI56" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ56" s="20" t="s">
-        <v>1</v>
+      <c r="X56" s="27">
+        <v>17.329999999999998</v>
+      </c>
+      <c r="Y56" s="27">
+        <v>5.18</v>
+      </c>
+      <c r="Z56" s="27">
+        <v>21.38</v>
+      </c>
+      <c r="AA56" s="27">
+        <v>44.93</v>
+      </c>
+      <c r="AB56" s="27">
+        <v>28.51</v>
+      </c>
+      <c r="AC56" s="27">
+        <v>3455</v>
+      </c>
+      <c r="AD56" s="28">
+        <v>3012</v>
+      </c>
+      <c r="AE56" s="27">
+        <v>5.67</v>
+      </c>
+      <c r="AF56" s="29">
+        <v>21.27</v>
+      </c>
+      <c r="AG56" s="29">
+        <v>44.7</v>
+      </c>
+      <c r="AH56" s="29">
+        <v>28.36</v>
+      </c>
+      <c r="AI56" s="29">
+        <v>3437</v>
+      </c>
+      <c r="AJ56" s="20">
+        <v>3012</v>
       </c>
     </row>
     <row r="57" spans="1:36">
@@ -20418,44 +20478,44 @@
       <c r="W57" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X57" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y57" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z57" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA57" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB57" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC57" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD57" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE57" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF57" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG57" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH57" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI57" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ57" s="20" t="s">
-        <v>1</v>
+      <c r="X57" s="27">
+        <v>19.190000000000001</v>
+      </c>
+      <c r="Y57" s="27">
+        <v>6.95</v>
+      </c>
+      <c r="Z57" s="27">
+        <v>21.89</v>
+      </c>
+      <c r="AA57" s="27">
+        <v>43.52</v>
+      </c>
+      <c r="AB57" s="27">
+        <v>27.64</v>
+      </c>
+      <c r="AC57" s="27">
+        <v>3373</v>
+      </c>
+      <c r="AD57" s="28">
+        <v>2929</v>
+      </c>
+      <c r="AE57" s="27">
+        <v>7.34</v>
+      </c>
+      <c r="AF57" s="29">
+        <v>21.8</v>
+      </c>
+      <c r="AG57" s="29">
+        <v>43.34</v>
+      </c>
+      <c r="AH57" s="29">
+        <v>27.52</v>
+      </c>
+      <c r="AI57" s="29">
+        <v>3359</v>
+      </c>
+      <c r="AJ57" s="20">
+        <v>2929</v>
       </c>
     </row>
     <row r="58" spans="1:36">
@@ -20528,44 +20588,44 @@
       <c r="W58" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X58" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y58" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z58" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA58" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB58" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC58" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD58" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE58" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF58" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG58" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH58" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI58" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ58" s="20" t="s">
-        <v>1</v>
+      <c r="X58" s="27">
+        <v>21.67</v>
+      </c>
+      <c r="Y58" s="27">
+        <v>6.39</v>
+      </c>
+      <c r="Z58" s="27">
+        <v>24.65</v>
+      </c>
+      <c r="AA58" s="27">
+        <v>33.549999999999997</v>
+      </c>
+      <c r="AB58" s="27">
+        <v>35.409999999999997</v>
+      </c>
+      <c r="AC58" s="27">
+        <v>4559</v>
+      </c>
+      <c r="AD58" s="28">
+        <v>3815</v>
+      </c>
+      <c r="AE58" s="27">
+        <v>6.78</v>
+      </c>
+      <c r="AF58" s="29">
+        <v>24.55</v>
+      </c>
+      <c r="AG58" s="29">
+        <v>33.409999999999997</v>
+      </c>
+      <c r="AH58" s="29">
+        <v>35.26</v>
+      </c>
+      <c r="AI58" s="29">
+        <v>4540</v>
+      </c>
+      <c r="AJ58" s="20">
+        <v>3815</v>
       </c>
     </row>
     <row r="59" spans="1:36">
@@ -20638,44 +20698,44 @@
       <c r="W59" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X59" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y59" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z59" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA59" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB59" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC59" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD59" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE59" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF59" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG59" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH59" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI59" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ59" s="20" t="s">
-        <v>1</v>
+      <c r="X59" s="27">
+        <v>19.45</v>
+      </c>
+      <c r="Y59" s="27">
+        <v>5.89</v>
+      </c>
+      <c r="Z59" s="27">
+        <v>21.99</v>
+      </c>
+      <c r="AA59" s="27">
+        <v>43.12</v>
+      </c>
+      <c r="AB59" s="27">
+        <v>29</v>
+      </c>
+      <c r="AC59" s="27">
+        <v>3521</v>
+      </c>
+      <c r="AD59" s="28">
+        <v>3014</v>
+      </c>
+      <c r="AE59" s="27">
+        <v>6.33</v>
+      </c>
+      <c r="AF59" s="29">
+        <v>21.89</v>
+      </c>
+      <c r="AG59" s="29">
+        <v>42.92</v>
+      </c>
+      <c r="AH59" s="29">
+        <v>28.86</v>
+      </c>
+      <c r="AI59" s="29">
+        <v>3505</v>
+      </c>
+      <c r="AJ59" s="20">
+        <v>3014</v>
       </c>
     </row>
     <row r="60" spans="1:36">
@@ -20748,44 +20808,44 @@
       <c r="W60" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X60" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y60" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z60" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA60" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB60" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC60" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD60" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE60" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF60" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG60" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH60" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI60" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ60" s="20" t="s">
-        <v>1</v>
+      <c r="X60" s="27">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="Y60" s="27">
+        <v>6.49</v>
+      </c>
+      <c r="Z60" s="27">
+        <v>23.71</v>
+      </c>
+      <c r="AA60" s="27">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="AB60" s="27">
+        <v>31.1</v>
+      </c>
+      <c r="AC60" s="27">
+        <v>3870</v>
+      </c>
+      <c r="AD60" s="28">
+        <v>3294</v>
+      </c>
+      <c r="AE60" s="27">
+        <v>7.03</v>
+      </c>
+      <c r="AF60" s="29">
+        <v>23.57</v>
+      </c>
+      <c r="AG60" s="29">
+        <v>38.479999999999997</v>
+      </c>
+      <c r="AH60" s="29">
+        <v>30.92</v>
+      </c>
+      <c r="AI60" s="29">
+        <v>3848</v>
+      </c>
+      <c r="AJ60" s="20">
+        <v>3294</v>
       </c>
     </row>
     <row r="61" spans="1:36">
@@ -20858,44 +20918,44 @@
       <c r="W61" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X61" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y61" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z61" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA61" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB61" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC61" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD61" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE61" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF61" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG61" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH61" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI61" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ61" s="20" t="s">
-        <v>1</v>
+      <c r="X61" s="27">
+        <v>21.71</v>
+      </c>
+      <c r="Y61" s="27">
+        <v>5.43</v>
+      </c>
+      <c r="Z61" s="27">
+        <v>23.62</v>
+      </c>
+      <c r="AA61" s="27">
+        <v>39.909999999999997</v>
+      </c>
+      <c r="AB61" s="27">
+        <v>31.04</v>
+      </c>
+      <c r="AC61" s="27">
+        <v>3857</v>
+      </c>
+      <c r="AD61" s="28">
+        <v>3193</v>
+      </c>
+      <c r="AE61" s="27">
+        <v>6.87</v>
+      </c>
+      <c r="AF61" s="29">
+        <v>23.26</v>
+      </c>
+      <c r="AG61" s="29">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="AH61" s="29">
+        <v>30.57</v>
+      </c>
+      <c r="AI61" s="29">
+        <v>3798</v>
+      </c>
+      <c r="AJ61" s="20">
+        <v>3193</v>
       </c>
     </row>
     <row r="62" spans="1:36">
@@ -20968,44 +21028,44 @@
       <c r="W62" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X62" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y62" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z62" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA62" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB62" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC62" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD62" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE62" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF62" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG62" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH62" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI62" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ62" s="20" t="s">
-        <v>1</v>
+      <c r="X62" s="27">
+        <v>20.67</v>
+      </c>
+      <c r="Y62" s="27">
+        <v>5.53</v>
+      </c>
+      <c r="Z62" s="27">
+        <v>25.26</v>
+      </c>
+      <c r="AA62" s="27">
+        <v>37.08</v>
+      </c>
+      <c r="AB62" s="27">
+        <v>32.130000000000003</v>
+      </c>
+      <c r="AC62" s="27">
+        <v>4110</v>
+      </c>
+      <c r="AD62" s="28">
+        <v>3451</v>
+      </c>
+      <c r="AE62" s="27">
+        <v>6.91</v>
+      </c>
+      <c r="AF62" s="29">
+        <v>24.89</v>
+      </c>
+      <c r="AG62" s="29">
+        <v>36.54</v>
+      </c>
+      <c r="AH62" s="29">
+        <v>31.66</v>
+      </c>
+      <c r="AI62" s="29">
+        <v>4050</v>
+      </c>
+      <c r="AJ62" s="20">
+        <v>3451</v>
       </c>
     </row>
     <row r="63" spans="1:36">
@@ -21078,44 +21138,44 @@
       <c r="W63" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X63" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y63" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z63" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA63" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB63" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC63" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD63" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE63" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF63" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG63" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH63" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI63" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ63" s="20" t="s">
-        <v>1</v>
+      <c r="X63" s="27">
+        <v>21.36</v>
+      </c>
+      <c r="Y63" s="27">
+        <v>5.84</v>
+      </c>
+      <c r="Z63" s="27">
+        <v>24.05</v>
+      </c>
+      <c r="AA63" s="27">
+        <v>38.81</v>
+      </c>
+      <c r="AB63" s="27">
+        <v>31.3</v>
+      </c>
+      <c r="AC63" s="27">
+        <v>3945</v>
+      </c>
+      <c r="AD63" s="28">
+        <v>3295</v>
+      </c>
+      <c r="AE63" s="27">
+        <v>7.28</v>
+      </c>
+      <c r="AF63" s="29">
+        <v>23.68</v>
+      </c>
+      <c r="AG63" s="29">
+        <v>38.22</v>
+      </c>
+      <c r="AH63" s="29">
+        <v>30.82</v>
+      </c>
+      <c r="AI63" s="29">
+        <v>3885</v>
+      </c>
+      <c r="AJ63" s="20">
+        <v>3295</v>
       </c>
     </row>
     <row r="64" spans="1:36">
@@ -21188,44 +21248,44 @@
       <c r="W64" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X64" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y64" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z64" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA64" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB64" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC64" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD64" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE64" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF64" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG64" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH64" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI64" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ64" s="20" t="s">
-        <v>1</v>
+      <c r="X64" s="27">
+        <v>20.03</v>
+      </c>
+      <c r="Y64" s="27">
+        <v>6.7</v>
+      </c>
+      <c r="Z64" s="27">
+        <v>23.93</v>
+      </c>
+      <c r="AA64" s="27">
+        <v>38.94</v>
+      </c>
+      <c r="AB64" s="27">
+        <v>30.43</v>
+      </c>
+      <c r="AC64" s="27">
+        <v>3791</v>
+      </c>
+      <c r="AD64" s="28">
+        <v>3249</v>
+      </c>
+      <c r="AE64" s="27">
+        <v>7.23</v>
+      </c>
+      <c r="AF64" s="29">
+        <v>23.79</v>
+      </c>
+      <c r="AG64" s="29">
+        <v>38.72</v>
+      </c>
+      <c r="AH64" s="29">
+        <v>30.26</v>
+      </c>
+      <c r="AI64" s="29">
+        <v>3769</v>
+      </c>
+      <c r="AJ64" s="20">
+        <v>3249</v>
       </c>
     </row>
     <row r="65" spans="1:36">
@@ -21298,44 +21358,44 @@
       <c r="W65" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X65" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y65" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z65" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA65" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB65" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC65" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD65" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE65" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF65" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG65" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH65" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI65" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ65" s="20" t="s">
-        <v>1</v>
+      <c r="X65" s="27">
+        <v>23.33</v>
+      </c>
+      <c r="Y65" s="27">
+        <v>6.25</v>
+      </c>
+      <c r="Z65" s="27">
+        <v>26.71</v>
+      </c>
+      <c r="AA65" s="27">
+        <v>27.25</v>
+      </c>
+      <c r="AB65" s="27">
+        <v>39.79</v>
+      </c>
+      <c r="AC65" s="27">
+        <v>4895</v>
+      </c>
+      <c r="AD65" s="28">
+        <v>4003</v>
+      </c>
+      <c r="AE65" s="27">
+        <v>7.55</v>
+      </c>
+      <c r="AF65" s="29">
+        <v>26.34</v>
+      </c>
+      <c r="AG65" s="29">
+        <v>26.87</v>
+      </c>
+      <c r="AH65" s="29">
+        <v>39.24</v>
+      </c>
+      <c r="AI65" s="29">
+        <v>4827</v>
+      </c>
+      <c r="AJ65" s="20">
+        <v>4003</v>
       </c>
     </row>
     <row r="66" spans="1:36">
@@ -21408,44 +21468,44 @@
       <c r="W66" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X66" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y66" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z66" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA66" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB66" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC66" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD66" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE66" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF66" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG66" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH66" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI66" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ66" s="20" t="s">
-        <v>1</v>
+      <c r="X66" s="27">
+        <v>23.06</v>
+      </c>
+      <c r="Y66" s="27">
+        <v>6.64</v>
+      </c>
+      <c r="Z66" s="27">
+        <v>22.05</v>
+      </c>
+      <c r="AA66" s="27">
+        <v>37.31</v>
+      </c>
+      <c r="AB66" s="27">
+        <v>34</v>
+      </c>
+      <c r="AC66" s="27">
+        <v>3946</v>
+      </c>
+      <c r="AD66" s="28">
+        <v>3252</v>
+      </c>
+      <c r="AE66" s="27">
+        <v>7.04</v>
+      </c>
+      <c r="AF66" s="29">
+        <v>21.96</v>
+      </c>
+      <c r="AG66" s="29">
+        <v>37.15</v>
+      </c>
+      <c r="AH66" s="29">
+        <v>33.85</v>
+      </c>
+      <c r="AI66" s="29">
+        <v>3929</v>
+      </c>
+      <c r="AJ66" s="20">
+        <v>3252</v>
       </c>
     </row>
     <row r="67" spans="1:36">
@@ -21518,44 +21578,44 @@
       <c r="W67" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X67" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y67" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z67" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA67" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB67" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC67" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD67" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE67" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF67" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG67" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH67" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI67" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ67" s="20" t="s">
-        <v>1</v>
+      <c r="X67" s="27">
+        <v>22.48</v>
+      </c>
+      <c r="Y67" s="27">
+        <v>6.27</v>
+      </c>
+      <c r="Z67" s="27">
+        <v>22.41</v>
+      </c>
+      <c r="AA67" s="27">
+        <v>42.8</v>
+      </c>
+      <c r="AB67" s="27">
+        <v>28.52</v>
+      </c>
+      <c r="AC67" s="27">
+        <v>3501</v>
+      </c>
+      <c r="AD67" s="28">
+        <v>2896</v>
+      </c>
+      <c r="AE67" s="27">
+        <v>6.67</v>
+      </c>
+      <c r="AF67" s="29">
+        <v>22.31</v>
+      </c>
+      <c r="AG67" s="29">
+        <v>42.62</v>
+      </c>
+      <c r="AH67" s="29">
+        <v>28.4</v>
+      </c>
+      <c r="AI67" s="29">
+        <v>3486</v>
+      </c>
+      <c r="AJ67" s="20">
+        <v>2896</v>
       </c>
     </row>
     <row r="68" spans="1:36">
@@ -21628,44 +21688,44 @@
       <c r="W68" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X68" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y68" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z68" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA68" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB68" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC68" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD68" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE68" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF68" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG68" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH68" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI68" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ68" s="20" t="s">
-        <v>1</v>
+      <c r="X68" s="27">
+        <v>22.82</v>
+      </c>
+      <c r="Y68" s="27">
+        <v>6.82</v>
+      </c>
+      <c r="Z68" s="27">
+        <v>23.77</v>
+      </c>
+      <c r="AA68" s="27">
+        <v>40.75</v>
+      </c>
+      <c r="AB68" s="27">
+        <v>28.66</v>
+      </c>
+      <c r="AC68" s="27">
+        <v>3616</v>
+      </c>
+      <c r="AD68" s="28">
+        <v>2995</v>
+      </c>
+      <c r="AE68" s="27">
+        <v>7.24</v>
+      </c>
+      <c r="AF68" s="29">
+        <v>23.66</v>
+      </c>
+      <c r="AG68" s="29">
+        <v>40.57</v>
+      </c>
+      <c r="AH68" s="29">
+        <v>28.53</v>
+      </c>
+      <c r="AI68" s="29">
+        <v>3600</v>
+      </c>
+      <c r="AJ68" s="20">
+        <v>2995</v>
       </c>
     </row>
     <row r="69" spans="1:36">
@@ -21738,44 +21798,44 @@
       <c r="W69" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X69" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y69" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z69" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA69" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB69" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC69" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD69" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE69" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF69" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG69" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH69" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI69" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ69" s="20" t="s">
-        <v>1</v>
+      <c r="X69" s="27">
+        <v>23.8</v>
+      </c>
+      <c r="Y69" s="27">
+        <v>6.2</v>
+      </c>
+      <c r="Z69" s="27">
+        <v>24.11</v>
+      </c>
+      <c r="AA69" s="27">
+        <v>35.04</v>
+      </c>
+      <c r="AB69" s="27">
+        <v>34.65</v>
+      </c>
+      <c r="AC69" s="27">
+        <v>4240</v>
+      </c>
+      <c r="AD69" s="28">
+        <v>3444</v>
+      </c>
+      <c r="AE69" s="27">
+        <v>6.59</v>
+      </c>
+      <c r="AF69" s="29">
+        <v>24.01</v>
+      </c>
+      <c r="AG69" s="29">
+        <v>34.89</v>
+      </c>
+      <c r="AH69" s="29">
+        <v>34.51</v>
+      </c>
+      <c r="AI69" s="29">
+        <v>4222</v>
+      </c>
+      <c r="AJ69" s="20">
+        <v>3444</v>
       </c>
     </row>
     <row r="70" spans="1:36">
@@ -21848,44 +21908,44 @@
       <c r="W70" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X70" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y70" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z70" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA70" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB70" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC70" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD70" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE70" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF70" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG70" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH70" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI70" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ70" s="20" t="s">
-        <v>1</v>
+      <c r="X70" s="27">
+        <v>23.1</v>
+      </c>
+      <c r="Y70" s="27">
+        <v>6.68</v>
+      </c>
+      <c r="Z70" s="27">
+        <v>24.31</v>
+      </c>
+      <c r="AA70" s="27">
+        <v>33.4</v>
+      </c>
+      <c r="AB70" s="27">
+        <v>35.61</v>
+      </c>
+      <c r="AC70" s="27">
+        <v>4282</v>
+      </c>
+      <c r="AD70" s="28">
+        <v>3529</v>
+      </c>
+      <c r="AE70" s="27">
+        <v>7.13</v>
+      </c>
+      <c r="AF70" s="29">
+        <v>24.19</v>
+      </c>
+      <c r="AG70" s="29">
+        <v>33.24</v>
+      </c>
+      <c r="AH70" s="29">
+        <v>35.44</v>
+      </c>
+      <c r="AI70" s="29">
+        <v>4261</v>
+      </c>
+      <c r="AJ70" s="20">
+        <v>3529</v>
       </c>
     </row>
     <row r="71" spans="1:36">
@@ -21958,44 +22018,44 @@
       <c r="W71" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X71" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y71" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z71" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA71" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB71" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC71" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD71" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE71" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF71" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG71" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH71" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI71" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ71" s="20" t="s">
-        <v>1</v>
+      <c r="X71" s="27">
+        <v>23.75</v>
+      </c>
+      <c r="Y71" s="27">
+        <v>6.59</v>
+      </c>
+      <c r="Z71" s="27">
+        <v>23.1</v>
+      </c>
+      <c r="AA71" s="27">
+        <v>37.07</v>
+      </c>
+      <c r="AB71" s="27">
+        <v>33.24</v>
+      </c>
+      <c r="AC71" s="27">
+        <v>4060</v>
+      </c>
+      <c r="AD71" s="28">
+        <v>3314</v>
+      </c>
+      <c r="AE71" s="27">
+        <v>7.02</v>
+      </c>
+      <c r="AF71" s="29">
+        <v>22.99</v>
+      </c>
+      <c r="AG71" s="29">
+        <v>36.9</v>
+      </c>
+      <c r="AH71" s="29">
+        <v>33.090000000000003</v>
+      </c>
+      <c r="AI71" s="29">
+        <v>4041</v>
+      </c>
+      <c r="AJ71" s="20">
+        <v>3314</v>
       </c>
     </row>
     <row r="72" spans="1:36">
@@ -22068,44 +22128,44 @@
       <c r="W72" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X72" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y72" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z72" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA72" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB72" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC72" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD72" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE72" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF72" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG72" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH72" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI72" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ72" s="20" t="s">
-        <v>1</v>
+      <c r="X72" s="27">
+        <v>22.5</v>
+      </c>
+      <c r="Y72" s="27">
+        <v>6.81</v>
+      </c>
+      <c r="Z72" s="27">
+        <v>25.77</v>
+      </c>
+      <c r="AA72" s="27">
+        <v>33.85</v>
+      </c>
+      <c r="AB72" s="27">
+        <v>33.57</v>
+      </c>
+      <c r="AC72" s="27">
+        <v>4248</v>
+      </c>
+      <c r="AD72" s="28">
+        <v>3533</v>
+      </c>
+      <c r="AE72" s="27">
+        <v>7.25</v>
+      </c>
+      <c r="AF72" s="29">
+        <v>25.65</v>
+      </c>
+      <c r="AG72" s="29">
+        <v>33.69</v>
+      </c>
+      <c r="AH72" s="29">
+        <v>33.409999999999997</v>
+      </c>
+      <c r="AI72" s="29">
+        <v>4228</v>
+      </c>
+      <c r="AJ72" s="20">
+        <v>3533</v>
       </c>
     </row>
     <row r="73" spans="1:36">
@@ -22178,44 +22238,44 @@
       <c r="W73" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X73" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y73" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z73" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA73" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB73" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC73" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD73" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE73" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF73" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG73" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH73" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI73" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ73" s="20" t="s">
-        <v>1</v>
+      <c r="X73" s="27">
+        <v>21.53</v>
+      </c>
+      <c r="Y73" s="27">
+        <v>6.2</v>
+      </c>
+      <c r="Z73" s="27">
+        <v>24.55</v>
+      </c>
+      <c r="AA73" s="27">
+        <v>38.68</v>
+      </c>
+      <c r="AB73" s="27">
+        <v>30.57</v>
+      </c>
+      <c r="AC73" s="27">
+        <v>3892</v>
+      </c>
+      <c r="AD73" s="28">
+        <v>3256</v>
+      </c>
+      <c r="AE73" s="27">
+        <v>6.58</v>
+      </c>
+      <c r="AF73" s="29">
+        <v>24.45</v>
+      </c>
+      <c r="AG73" s="29">
+        <v>38.520000000000003</v>
+      </c>
+      <c r="AH73" s="29">
+        <v>30.45</v>
+      </c>
+      <c r="AI73" s="29">
+        <v>3876</v>
+      </c>
+      <c r="AJ73" s="20">
+        <v>3256</v>
       </c>
     </row>
     <row r="74" spans="1:36">
@@ -22288,44 +22348,44 @@
       <c r="W74" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X74" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y74" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z74" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA74" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB74" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC74" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD74" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE74" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF74" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG74" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH74" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI74" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ74" s="20" t="s">
-        <v>1</v>
+      <c r="X74" s="27">
+        <v>22.91</v>
+      </c>
+      <c r="Y74" s="27">
+        <v>5.74</v>
+      </c>
+      <c r="Z74" s="27">
+        <v>24.95</v>
+      </c>
+      <c r="AA74" s="27">
+        <v>38.11</v>
+      </c>
+      <c r="AB74" s="27">
+        <v>31.2</v>
+      </c>
+      <c r="AC74" s="27">
+        <v>4090</v>
+      </c>
+      <c r="AD74" s="28">
+        <v>3345</v>
+      </c>
+      <c r="AE74" s="27">
+        <v>7.08</v>
+      </c>
+      <c r="AF74" s="29">
+        <v>24.6</v>
+      </c>
+      <c r="AG74" s="29">
+        <v>37.57</v>
+      </c>
+      <c r="AH74" s="29">
+        <v>30.76</v>
+      </c>
+      <c r="AI74" s="29">
+        <v>4032</v>
+      </c>
+      <c r="AJ74" s="20">
+        <v>3345</v>
       </c>
     </row>
     <row r="75" spans="1:36">
@@ -22398,44 +22458,44 @@
       <c r="W75" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X75" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y75" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z75" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA75" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB75" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC75" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD75" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE75" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF75" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG75" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH75" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI75" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ75" s="20" t="s">
-        <v>1</v>
+      <c r="X75" s="27">
+        <v>24.49</v>
+      </c>
+      <c r="Y75" s="27">
+        <v>5.87</v>
+      </c>
+      <c r="Z75" s="27">
+        <v>23.47</v>
+      </c>
+      <c r="AA75" s="27">
+        <v>42.24</v>
+      </c>
+      <c r="AB75" s="27">
+        <v>28.42</v>
+      </c>
+      <c r="AC75" s="27">
+        <v>3727</v>
+      </c>
+      <c r="AD75" s="28">
+        <v>2990</v>
+      </c>
+      <c r="AE75" s="27">
+        <v>7.19</v>
+      </c>
+      <c r="AF75" s="29">
+        <v>23.14</v>
+      </c>
+      <c r="AG75" s="29">
+        <v>41.65</v>
+      </c>
+      <c r="AH75" s="29">
+        <v>28.02</v>
+      </c>
+      <c r="AI75" s="29">
+        <v>3675</v>
+      </c>
+      <c r="AJ75" s="20">
+        <v>2990</v>
       </c>
     </row>
     <row r="76" spans="1:36">
@@ -22508,44 +22568,44 @@
       <c r="W76" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X76" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y76" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z76" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA76" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB76" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC76" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD76" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE76" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF76" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG76" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="AH76" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI76" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ76" s="20" t="s">
-        <v>1</v>
+      <c r="X76" s="27">
+        <v>24.64</v>
+      </c>
+      <c r="Y76" s="27">
+        <v>6.59</v>
+      </c>
+      <c r="Z76" s="27">
+        <v>25.04</v>
+      </c>
+      <c r="AA76" s="27">
+        <v>36.479999999999997</v>
+      </c>
+      <c r="AB76" s="27">
+        <v>31.89</v>
+      </c>
+      <c r="AC76" s="27">
+        <v>4084</v>
+      </c>
+      <c r="AD76" s="28">
+        <v>3295</v>
+      </c>
+      <c r="AE76" s="27">
+        <v>6.92</v>
+      </c>
+      <c r="AF76" s="29">
+        <v>24.95</v>
+      </c>
+      <c r="AG76" s="29">
+        <v>36.35</v>
+      </c>
+      <c r="AH76" s="29">
+        <v>31.78</v>
+      </c>
+      <c r="AI76" s="29">
+        <v>4070</v>
+      </c>
+      <c r="AJ76" s="20">
+        <v>3295</v>
       </c>
     </row>
     <row r="77" spans="1:36">
@@ -22618,44 +22678,44 @@
       <c r="W77" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X77" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y77" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z77" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA77" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB77" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC77" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD77" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE77" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF77" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG77" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH77" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI77" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ77" s="20" t="s">
-        <v>1</v>
+      <c r="X77" s="27">
+        <v>24.22</v>
+      </c>
+      <c r="Y77" s="27">
+        <v>6.32</v>
+      </c>
+      <c r="Z77" s="27">
+        <v>25.05</v>
+      </c>
+      <c r="AA77" s="27">
+        <v>30.99</v>
+      </c>
+      <c r="AB77" s="27">
+        <v>37.64</v>
+      </c>
+      <c r="AC77" s="27">
+        <v>4593</v>
+      </c>
+      <c r="AD77" s="28">
+        <v>3715</v>
+      </c>
+      <c r="AE77" s="27">
+        <v>7.53</v>
+      </c>
+      <c r="AF77" s="29">
+        <v>24.73</v>
+      </c>
+      <c r="AG77" s="29">
+        <v>30.59</v>
+      </c>
+      <c r="AH77" s="29">
+        <v>37.15</v>
+      </c>
+      <c r="AI77" s="29">
+        <v>4534</v>
+      </c>
+      <c r="AJ77" s="20">
+        <v>3715</v>
       </c>
     </row>
     <row r="78" spans="1:36">
@@ -22728,44 +22788,44 @@
       <c r="W78" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X78" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y78" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z78" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA78" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB78" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC78" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD78" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE78" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF78" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG78" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH78" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI78" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ78" s="20" t="s">
-        <v>1</v>
+      <c r="X78" s="27">
+        <v>24.29</v>
+      </c>
+      <c r="Y78" s="27">
+        <v>6.33</v>
+      </c>
+      <c r="Z78" s="27">
+        <v>24.15</v>
+      </c>
+      <c r="AA78" s="27">
+        <v>38</v>
+      </c>
+      <c r="AB78" s="27">
+        <v>31.52</v>
+      </c>
+      <c r="AC78" s="27">
+        <v>3948</v>
+      </c>
+      <c r="AD78" s="28">
+        <v>3191</v>
+      </c>
+      <c r="AE78" s="27">
+        <v>6.61</v>
+      </c>
+      <c r="AF78" s="29">
+        <v>24.08</v>
+      </c>
+      <c r="AG78" s="29">
+        <v>37.89</v>
+      </c>
+      <c r="AH78" s="29">
+        <v>31.43</v>
+      </c>
+      <c r="AI78" s="29">
+        <v>3936</v>
+      </c>
+      <c r="AJ78" s="20">
+        <v>3191</v>
       </c>
     </row>
     <row r="79" spans="1:36">
@@ -22838,44 +22898,44 @@
       <c r="W79" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X79" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y79" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z79" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA79" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB79" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC79" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD79" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE79" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF79" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG79" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH79" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI79" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ79" s="20" t="s">
-        <v>1</v>
+      <c r="X79" s="27">
+        <v>22.85</v>
+      </c>
+      <c r="Y79" s="27">
+        <v>5.66</v>
+      </c>
+      <c r="Z79" s="27">
+        <v>24.3</v>
+      </c>
+      <c r="AA79" s="27">
+        <v>35.08</v>
+      </c>
+      <c r="AB79" s="27">
+        <v>34.96</v>
+      </c>
+      <c r="AC79" s="27">
+        <v>4384</v>
+      </c>
+      <c r="AD79" s="28">
+        <v>3585</v>
+      </c>
+      <c r="AE79" s="27">
+        <v>7.05</v>
+      </c>
+      <c r="AF79" s="29">
+        <v>23.94</v>
+      </c>
+      <c r="AG79" s="29">
+        <v>34.56</v>
+      </c>
+      <c r="AH79" s="29">
+        <v>34.44</v>
+      </c>
+      <c r="AI79" s="29">
+        <v>4319</v>
+      </c>
+      <c r="AJ79" s="20">
+        <v>3585</v>
       </c>
     </row>
     <row r="80" spans="1:36">
@@ -22948,44 +23008,44 @@
       <c r="W80" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X80" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y80" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z80" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA80" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB80" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC80" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD80" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE80" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF80" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG80" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH80" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI80" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ80" s="20" t="s">
-        <v>1</v>
+      <c r="X80" s="27">
+        <v>23.1</v>
+      </c>
+      <c r="Y80" s="27">
+        <v>6.19</v>
+      </c>
+      <c r="Z80" s="27">
+        <v>24.26</v>
+      </c>
+      <c r="AA80" s="27">
+        <v>38.520000000000003</v>
+      </c>
+      <c r="AB80" s="27">
+        <v>31.03</v>
+      </c>
+      <c r="AC80" s="27">
+        <v>3944</v>
+      </c>
+      <c r="AD80" s="28">
+        <v>3233</v>
+      </c>
+      <c r="AE80" s="27">
+        <v>6.52</v>
+      </c>
+      <c r="AF80" s="29">
+        <v>24.17</v>
+      </c>
+      <c r="AG80" s="29">
+        <v>38.380000000000003</v>
+      </c>
+      <c r="AH80" s="29">
+        <v>30.92</v>
+      </c>
+      <c r="AI80" s="29">
+        <v>3930</v>
+      </c>
+      <c r="AJ80" s="20">
+        <v>3233</v>
       </c>
     </row>
     <row r="81" spans="1:36">
@@ -23058,44 +23118,44 @@
       <c r="W81" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X81" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y81" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z81" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA81" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB81" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC81" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD81" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE81" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF81" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG81" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH81" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI81" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ81" s="20" t="s">
-        <v>1</v>
+      <c r="X81" s="27">
+        <v>23.1</v>
+      </c>
+      <c r="Y81" s="27">
+        <v>5.54</v>
+      </c>
+      <c r="Z81" s="27">
+        <v>26.01</v>
+      </c>
+      <c r="AA81" s="27">
+        <v>32.979999999999997</v>
+      </c>
+      <c r="AB81" s="27">
+        <v>35.47</v>
+      </c>
+      <c r="AC81" s="27">
+        <v>4657</v>
+      </c>
+      <c r="AD81" s="28">
+        <v>3791</v>
+      </c>
+      <c r="AE81" s="27">
+        <v>5.93</v>
+      </c>
+      <c r="AF81" s="29">
+        <v>25.9</v>
+      </c>
+      <c r="AG81" s="29">
+        <v>32.840000000000003</v>
+      </c>
+      <c r="AH81" s="29">
+        <v>35.32</v>
+      </c>
+      <c r="AI81" s="29">
+        <v>4638</v>
+      </c>
+      <c r="AJ81" s="20">
+        <v>3791</v>
       </c>
     </row>
     <row r="82" spans="1:36">
@@ -23168,44 +23228,44 @@
       <c r="W82" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X82" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y82" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z82" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA82" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB82" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC82" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD82" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE82" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF82" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG82" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH82" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI82" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ82" s="20" t="s">
-        <v>1</v>
+      <c r="X82" s="27">
+        <v>23.86</v>
+      </c>
+      <c r="Y82" s="27">
+        <v>5.5</v>
+      </c>
+      <c r="Z82" s="27">
+        <v>25.75</v>
+      </c>
+      <c r="AA82" s="27">
+        <v>35.47</v>
+      </c>
+      <c r="AB82" s="27">
+        <v>33.28</v>
+      </c>
+      <c r="AC82" s="27">
+        <v>4299</v>
+      </c>
+      <c r="AD82" s="28">
+        <v>3464</v>
+      </c>
+      <c r="AE82" s="27">
+        <v>6.87</v>
+      </c>
+      <c r="AF82" s="29">
+        <v>25.38</v>
+      </c>
+      <c r="AG82" s="29">
+        <v>34.96</v>
+      </c>
+      <c r="AH82" s="29">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="AI82" s="29">
+        <v>4237</v>
+      </c>
+      <c r="AJ82" s="20">
+        <v>3464</v>
       </c>
     </row>
     <row r="83" spans="1:36">
@@ -23278,44 +23338,44 @@
       <c r="W83" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X83" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y83" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z83" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA83" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB83" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC83" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD83" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE83" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF83" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG83" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH83" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI83" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ83" s="20" t="s">
-        <v>1</v>
+      <c r="X83" s="27">
+        <v>24.7</v>
+      </c>
+      <c r="Y83" s="27">
+        <v>6.63</v>
+      </c>
+      <c r="Z83" s="27">
+        <v>27.05</v>
+      </c>
+      <c r="AA83" s="27">
+        <v>27.91</v>
+      </c>
+      <c r="AB83" s="27">
+        <v>38.409999999999997</v>
+      </c>
+      <c r="AC83" s="27">
+        <v>4844</v>
+      </c>
+      <c r="AD83" s="28">
+        <v>3907</v>
+      </c>
+      <c r="AE83" s="27">
+        <v>7.04</v>
+      </c>
+      <c r="AF83" s="29">
+        <v>26.93</v>
+      </c>
+      <c r="AG83" s="29">
+        <v>27.79</v>
+      </c>
+      <c r="AH83" s="29">
+        <v>38.24</v>
+      </c>
+      <c r="AI83" s="29">
+        <v>4823</v>
+      </c>
+      <c r="AJ83" s="20">
+        <v>3907</v>
       </c>
     </row>
     <row r="84" spans="1:36">
@@ -23388,44 +23448,44 @@
       <c r="W84" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X84" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y84" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z84" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA84" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB84" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC84" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD84" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE84" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF84" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG84" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH84" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI84" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ84" s="20" t="s">
-        <v>1</v>
+      <c r="X84" s="27">
+        <v>23.19</v>
+      </c>
+      <c r="Y84" s="27">
+        <v>5.6</v>
+      </c>
+      <c r="Z84" s="27">
+        <v>22.23</v>
+      </c>
+      <c r="AA84" s="27">
+        <v>41.42</v>
+      </c>
+      <c r="AB84" s="27">
+        <v>30.75</v>
+      </c>
+      <c r="AC84" s="27">
+        <v>3812</v>
+      </c>
+      <c r="AD84" s="28">
+        <v>3102</v>
+      </c>
+      <c r="AE84" s="27">
+        <v>6.96</v>
+      </c>
+      <c r="AF84" s="29">
+        <v>21.91</v>
+      </c>
+      <c r="AG84" s="29">
+        <v>40.82</v>
+      </c>
+      <c r="AH84" s="29">
+        <v>30.31</v>
+      </c>
+      <c r="AI84" s="29">
+        <v>3757</v>
+      </c>
+      <c r="AJ84" s="20">
+        <v>3102</v>
       </c>
     </row>
     <row r="85" spans="1:36">
@@ -23498,44 +23558,44 @@
       <c r="W85" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X85" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y85" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z85" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA85" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB85" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC85" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD85" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE85" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF85" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG85" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH85" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI85" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ85" s="20" t="s">
-        <v>1</v>
+      <c r="X85" s="27">
+        <v>23.06</v>
+      </c>
+      <c r="Y85" s="27">
+        <v>5.9</v>
+      </c>
+      <c r="Z85" s="27">
+        <v>21.6</v>
+      </c>
+      <c r="AA85" s="27">
+        <v>45.97</v>
+      </c>
+      <c r="AB85" s="27">
+        <v>26.53</v>
+      </c>
+      <c r="AC85" s="27">
+        <v>3360</v>
+      </c>
+      <c r="AD85" s="28">
+        <v>2747</v>
+      </c>
+      <c r="AE85" s="27">
+        <v>6.24</v>
+      </c>
+      <c r="AF85" s="29">
+        <v>21.52</v>
+      </c>
+      <c r="AG85" s="29">
+        <v>45.8</v>
+      </c>
+      <c r="AH85" s="29">
+        <v>26.43</v>
+      </c>
+      <c r="AI85" s="29">
+        <v>3348</v>
+      </c>
+      <c r="AJ85" s="20">
+        <v>2747</v>
       </c>
     </row>
     <row r="86" spans="1:36">
@@ -23608,44 +23668,44 @@
       <c r="W86" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X86" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y86" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z86" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA86" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB86" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC86" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD86" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE86" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF86" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG86" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH86" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI86" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ86" s="20" t="s">
-        <v>1</v>
+      <c r="X86" s="27">
+        <v>24.26</v>
+      </c>
+      <c r="Y86" s="27">
+        <v>4.76</v>
+      </c>
+      <c r="Z86" s="27">
+        <v>22.96</v>
+      </c>
+      <c r="AA86" s="27">
+        <v>43.59</v>
+      </c>
+      <c r="AB86" s="27">
+        <v>28.69</v>
+      </c>
+      <c r="AC86" s="27">
+        <v>3670</v>
+      </c>
+      <c r="AD86" s="28">
+        <v>2919</v>
+      </c>
+      <c r="AE86" s="27">
+        <v>6.29</v>
+      </c>
+      <c r="AF86" s="29">
+        <v>22.59</v>
+      </c>
+      <c r="AG86" s="29">
+        <v>42.89</v>
+      </c>
+      <c r="AH86" s="29">
+        <v>28.23</v>
+      </c>
+      <c r="AI86" s="29">
+        <v>3611</v>
+      </c>
+      <c r="AJ86" s="20">
+        <v>2919</v>
       </c>
     </row>
     <row r="87" spans="1:36">
@@ -23718,44 +23778,44 @@
       <c r="W87" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X87" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y87" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z87" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA87" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB87" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC87" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD87" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE87" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF87" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG87" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH87" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI87" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ87" s="20" t="s">
-        <v>1</v>
+      <c r="X87" s="27">
+        <v>22.64</v>
+      </c>
+      <c r="Y87" s="27">
+        <v>5.17</v>
+      </c>
+      <c r="Z87" s="27">
+        <v>19.72</v>
+      </c>
+      <c r="AA87" s="27">
+        <v>48.17</v>
+      </c>
+      <c r="AB87" s="27">
+        <v>26.94</v>
+      </c>
+      <c r="AC87" s="27">
+        <v>3175</v>
+      </c>
+      <c r="AD87" s="28">
+        <v>2590</v>
+      </c>
+      <c r="AE87" s="27">
+        <v>5.68</v>
+      </c>
+      <c r="AF87" s="29">
+        <v>19.61</v>
+      </c>
+      <c r="AG87" s="29">
+        <v>47.91</v>
+      </c>
+      <c r="AH87" s="29">
+        <v>26.8</v>
+      </c>
+      <c r="AI87" s="29">
+        <v>3158</v>
+      </c>
+      <c r="AJ87" s="20">
+        <v>2590</v>
       </c>
     </row>
     <row r="88" spans="1:36">
@@ -23783,8 +23843,8 @@
       <c r="H88" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="I88" s="20">
-        <v>162001411</v>
+      <c r="I88" s="35">
+        <v>162004411</v>
       </c>
       <c r="J88" s="25">
         <v>46255</v>
@@ -23828,44 +23888,44 @@
       <c r="W88" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X88" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y88" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z88" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA88" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB88" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC88" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD88" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE88" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF88" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG88" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH88" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI88" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ88" s="20" t="s">
-        <v>1</v>
+      <c r="X88" s="27">
+        <v>23.57</v>
+      </c>
+      <c r="Y88" s="27">
+        <v>7.17</v>
+      </c>
+      <c r="Z88" s="27">
+        <v>25.32</v>
+      </c>
+      <c r="AA88" s="27">
+        <v>34.880000000000003</v>
+      </c>
+      <c r="AB88" s="27">
+        <v>32.630000000000003</v>
+      </c>
+      <c r="AC88" s="27">
+        <v>4074</v>
+      </c>
+      <c r="AD88" s="28">
+        <v>3354</v>
+      </c>
+      <c r="AE88" s="27">
+        <v>7.46</v>
+      </c>
+      <c r="AF88" s="29">
+        <v>25.24</v>
+      </c>
+      <c r="AG88" s="29">
+        <v>34.770000000000003</v>
+      </c>
+      <c r="AH88" s="29">
+        <v>32.53</v>
+      </c>
+      <c r="AI88" s="29">
+        <v>4061</v>
+      </c>
+      <c r="AJ88" s="20">
+        <v>3354</v>
       </c>
     </row>
     <row r="89" spans="1:36">
@@ -23938,44 +23998,44 @@
       <c r="W89" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X89" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y89" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z89" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA89" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB89" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC89" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD89" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE89" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF89" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG89" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH89" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI89" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ89" s="20" t="s">
-        <v>1</v>
+      <c r="X89" s="27">
+        <v>22.23</v>
+      </c>
+      <c r="Y89" s="27">
+        <v>6.39</v>
+      </c>
+      <c r="Z89" s="27">
+        <v>24.7</v>
+      </c>
+      <c r="AA89" s="27">
+        <v>32.53</v>
+      </c>
+      <c r="AB89" s="27">
+        <v>36.380000000000003</v>
+      </c>
+      <c r="AC89" s="27">
+        <v>4472</v>
+      </c>
+      <c r="AD89" s="28">
+        <v>3715</v>
+      </c>
+      <c r="AE89" s="27">
+        <v>6.89</v>
+      </c>
+      <c r="AF89" s="29">
+        <v>24.57</v>
+      </c>
+      <c r="AG89" s="29">
+        <v>32.36</v>
+      </c>
+      <c r="AH89" s="29">
+        <v>36.19</v>
+      </c>
+      <c r="AI89" s="29">
+        <v>4448</v>
+      </c>
+      <c r="AJ89" s="20">
+        <v>3715</v>
       </c>
     </row>
     <row r="90" spans="1:36">
@@ -24048,44 +24108,44 @@
       <c r="W90" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X90" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y90" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z90" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA90" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB90" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC90" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD90" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE90" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF90" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG90" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH90" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI90" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ90" s="20" t="s">
-        <v>1</v>
+      <c r="X90" s="27">
+        <v>22.64</v>
+      </c>
+      <c r="Y90" s="27">
+        <v>4.55</v>
+      </c>
+      <c r="Z90" s="27">
+        <v>21.04</v>
+      </c>
+      <c r="AA90" s="27">
+        <v>49.1</v>
+      </c>
+      <c r="AB90" s="27">
+        <v>25.31</v>
+      </c>
+      <c r="AC90" s="27">
+        <v>3133</v>
+      </c>
+      <c r="AD90" s="28">
+        <v>2539</v>
+      </c>
+      <c r="AE90" s="27">
+        <v>6.17</v>
+      </c>
+      <c r="AF90" s="29">
+        <v>20.68</v>
+      </c>
+      <c r="AG90" s="29">
+        <v>48.27</v>
+      </c>
+      <c r="AH90" s="29">
+        <v>24.88</v>
+      </c>
+      <c r="AI90" s="29">
+        <v>3080</v>
+      </c>
+      <c r="AJ90" s="20">
+        <v>2539</v>
       </c>
     </row>
     <row r="91" spans="1:36">
@@ -24158,44 +24218,44 @@
       <c r="W91" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X91" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y91" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z91" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA91" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB91" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC91" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD91" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE91" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF91" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG91" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH91" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI91" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ91" s="20" t="s">
-        <v>1</v>
+      <c r="X91" s="27">
+        <v>21.29</v>
+      </c>
+      <c r="Y91" s="27">
+        <v>5.9</v>
+      </c>
+      <c r="Z91" s="27">
+        <v>22.09</v>
+      </c>
+      <c r="AA91" s="27">
+        <v>41.37</v>
+      </c>
+      <c r="AB91" s="27">
+        <v>30.64</v>
+      </c>
+      <c r="AC91" s="27">
+        <v>3700</v>
+      </c>
+      <c r="AD91" s="28">
+        <v>3095</v>
+      </c>
+      <c r="AE91" s="27">
+        <v>6.36</v>
+      </c>
+      <c r="AF91" s="29">
+        <v>21.98</v>
+      </c>
+      <c r="AG91" s="29">
+        <v>41.17</v>
+      </c>
+      <c r="AH91" s="29">
+        <v>30.49</v>
+      </c>
+      <c r="AI91" s="29">
+        <v>3682</v>
+      </c>
+      <c r="AJ91" s="20">
+        <v>3095</v>
       </c>
     </row>
     <row r="92" spans="1:36">
@@ -24268,44 +24328,44 @@
       <c r="W92" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X92" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y92" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z92" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA92" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB92" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC92" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD92" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE92" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF92" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG92" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH92" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI92" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ92" s="20" t="s">
-        <v>1</v>
+      <c r="X92" s="27">
+        <v>20.059999999999999</v>
+      </c>
+      <c r="Y92" s="27">
+        <v>6.47</v>
+      </c>
+      <c r="Z92" s="27">
+        <v>23.66</v>
+      </c>
+      <c r="AA92" s="27">
+        <v>41.61</v>
+      </c>
+      <c r="AB92" s="27">
+        <v>28.26</v>
+      </c>
+      <c r="AC92" s="27">
+        <v>3532</v>
+      </c>
+      <c r="AD92" s="28">
+        <v>3019</v>
+      </c>
+      <c r="AE92" s="27">
+        <v>7.15</v>
+      </c>
+      <c r="AF92" s="29">
+        <v>23.49</v>
+      </c>
+      <c r="AG92" s="29">
+        <v>41.31</v>
+      </c>
+      <c r="AH92" s="29">
+        <v>28.05</v>
+      </c>
+      <c r="AI92" s="29">
+        <v>3506</v>
+      </c>
+      <c r="AJ92" s="20">
+        <v>3019</v>
       </c>
     </row>
     <row r="93" spans="1:36">
@@ -24378,44 +24438,44 @@
       <c r="W93" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X93" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y93" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z93" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA93" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB93" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC93" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD93" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE93" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF93" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG93" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH93" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI93" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ93" s="20" t="s">
-        <v>1</v>
+      <c r="X93" s="27">
+        <v>22.35</v>
+      </c>
+      <c r="Y93" s="27">
+        <v>6.3</v>
+      </c>
+      <c r="Z93" s="27">
+        <v>24.73</v>
+      </c>
+      <c r="AA93" s="27">
+        <v>37.1</v>
+      </c>
+      <c r="AB93" s="27">
+        <v>31.87</v>
+      </c>
+      <c r="AC93" s="27">
+        <v>4018</v>
+      </c>
+      <c r="AD93" s="28">
+        <v>3330</v>
+      </c>
+      <c r="AE93" s="27">
+        <v>6.87</v>
+      </c>
+      <c r="AF93" s="29">
+        <v>24.58</v>
+      </c>
+      <c r="AG93" s="29">
+        <v>36.869999999999997</v>
+      </c>
+      <c r="AH93" s="29">
+        <v>31.68</v>
+      </c>
+      <c r="AI93" s="29">
+        <v>3994</v>
+      </c>
+      <c r="AJ93" s="20">
+        <v>3330</v>
       </c>
     </row>
     <row r="94" spans="1:36">
@@ -24488,44 +24548,44 @@
       <c r="W94" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X94" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y94" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z94" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA94" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB94" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC94" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD94" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE94" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF94" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG94" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH94" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI94" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ94" s="20" t="s">
-        <v>1</v>
+      <c r="X94" s="27">
+        <v>20.21</v>
+      </c>
+      <c r="Y94" s="27">
+        <v>5.35</v>
+      </c>
+      <c r="Z94" s="27">
+        <v>23.51</v>
+      </c>
+      <c r="AA94" s="27">
+        <v>41.23</v>
+      </c>
+      <c r="AB94" s="27">
+        <v>29.91</v>
+      </c>
+      <c r="AC94" s="27">
+        <v>3835</v>
+      </c>
+      <c r="AD94" s="28">
+        <v>3233</v>
+      </c>
+      <c r="AE94" s="27">
+        <v>6.73</v>
+      </c>
+      <c r="AF94" s="29">
+        <v>23.17</v>
+      </c>
+      <c r="AG94" s="29">
+        <v>40.630000000000003</v>
+      </c>
+      <c r="AH94" s="29">
+        <v>29.47</v>
+      </c>
+      <c r="AI94" s="29">
+        <v>3779</v>
+      </c>
+      <c r="AJ94" s="20">
+        <v>3233</v>
       </c>
     </row>
     <row r="95" spans="1:36">
@@ -24568,17 +24628,17 @@
       <c r="M95" s="20">
         <v>3579.4</v>
       </c>
-      <c r="N95" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="O95" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P95" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q95" s="20" t="s">
-        <v>1</v>
+      <c r="N95" s="20">
+        <v>7.17</v>
+      </c>
+      <c r="O95" s="20">
+        <v>25.19</v>
+      </c>
+      <c r="P95" s="20">
+        <v>43.42</v>
+      </c>
+      <c r="Q95" s="20">
+        <v>3580</v>
       </c>
       <c r="R95" s="7">
         <v>20.95</v>
@@ -24587,55 +24647,55 @@
         <v>21.45</v>
       </c>
       <c r="T95" s="7">
-        <v>36.979999999999997</v>
+        <v>36.97</v>
       </c>
       <c r="U95" s="7">
-        <v>20.62</v>
+        <v>20.63</v>
       </c>
       <c r="V95" s="26">
-        <v>3048</v>
+        <v>3049</v>
       </c>
       <c r="W95" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X95" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y95" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z95" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA95" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB95" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC95" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD95" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE95" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF95" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG95" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH95" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI95" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ95" s="20" t="s">
-        <v>1</v>
+      <c r="X95" s="27">
+        <v>20.95</v>
+      </c>
+      <c r="Y95" s="27">
+        <v>5.9</v>
+      </c>
+      <c r="Z95" s="27">
+        <v>23.2</v>
+      </c>
+      <c r="AA95" s="27">
+        <v>45.08</v>
+      </c>
+      <c r="AB95" s="27">
+        <v>25.82</v>
+      </c>
+      <c r="AC95" s="27">
+        <v>3546</v>
+      </c>
+      <c r="AD95" s="28">
+        <v>2979</v>
+      </c>
+      <c r="AE95" s="27">
+        <v>6.36</v>
+      </c>
+      <c r="AF95" s="29">
+        <v>23.09</v>
+      </c>
+      <c r="AG95" s="29">
+        <v>44.86</v>
+      </c>
+      <c r="AH95" s="29">
+        <v>25.69</v>
+      </c>
+      <c r="AI95" s="29">
+        <v>3529</v>
+      </c>
+      <c r="AJ95" s="20">
+        <v>2979</v>
       </c>
     </row>
     <row r="96" spans="1:36">
@@ -24678,17 +24738,17 @@
       <c r="M96" s="20">
         <v>4017</v>
       </c>
-      <c r="N96" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="O96" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P96" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q96" s="20" t="s">
-        <v>1</v>
+      <c r="N96" s="20">
+        <v>7.01</v>
+      </c>
+      <c r="O96" s="20">
+        <v>24.18</v>
+      </c>
+      <c r="P96" s="20">
+        <v>45.34</v>
+      </c>
+      <c r="Q96" s="20">
+        <v>3306</v>
       </c>
       <c r="R96" s="7">
         <v>19.059999999999999</v>
@@ -24703,7 +24763,7 @@
         <v>20.43</v>
       </c>
       <c r="V96" s="26">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="W96" s="26" t="s">
         <v>1</v>
@@ -24788,17 +24848,17 @@
       <c r="M97" s="20">
         <v>3890.3</v>
       </c>
-      <c r="N97" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="O97" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P97" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q97" s="20" t="s">
-        <v>1</v>
+      <c r="N97" s="20">
+        <v>6.93</v>
+      </c>
+      <c r="O97" s="20">
+        <v>22.63</v>
+      </c>
+      <c r="P97" s="20">
+        <v>41.17</v>
+      </c>
+      <c r="Q97" s="20">
+        <v>3749</v>
       </c>
       <c r="R97" s="7">
         <v>22.74</v>
@@ -24810,7 +24870,7 @@
         <v>34.18</v>
       </c>
       <c r="U97" s="7">
-        <v>24.3</v>
+        <v>24.29</v>
       </c>
       <c r="V97" s="26">
         <v>3112</v>
@@ -24898,17 +24958,17 @@
       <c r="M98" s="20">
         <v>4223.2</v>
       </c>
-      <c r="N98" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="O98" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P98" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q98" s="20" t="s">
-        <v>1</v>
+      <c r="N98" s="20">
+        <v>7.52</v>
+      </c>
+      <c r="O98" s="20">
+        <v>26.96</v>
+      </c>
+      <c r="P98" s="20">
+        <v>37.880000000000003</v>
+      </c>
+      <c r="Q98" s="20">
+        <v>3870</v>
       </c>
       <c r="R98" s="7">
         <v>23.64</v>
@@ -25008,32 +25068,32 @@
       <c r="M99" s="20">
         <v>3911.6</v>
       </c>
-      <c r="N99" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="O99" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P99" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q99" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R99" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S99" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T99" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U99" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V99" s="26" t="s">
-        <v>1</v>
+      <c r="N99" s="20">
+        <v>6.9</v>
+      </c>
+      <c r="O99" s="20">
+        <v>26.68</v>
+      </c>
+      <c r="P99" s="20">
+        <v>39.94</v>
+      </c>
+      <c r="Q99" s="20">
+        <v>3772</v>
+      </c>
+      <c r="R99" s="7">
+        <v>23.76</v>
+      </c>
+      <c r="S99" s="7">
+        <v>21.85</v>
+      </c>
+      <c r="T99" s="7">
+        <v>32.71</v>
+      </c>
+      <c r="U99" s="7">
+        <v>21.68</v>
+      </c>
+      <c r="V99" s="26">
+        <v>3089</v>
       </c>
       <c r="W99" s="26" t="s">
         <v>1</v>
@@ -25118,32 +25178,32 @@
       <c r="M100" s="20">
         <v>4007.4</v>
       </c>
-      <c r="N100" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="O100" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P100" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q100" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R100" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S100" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T100" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U100" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V100" s="26" t="s">
-        <v>1</v>
+      <c r="N100" s="20">
+        <v>6.46</v>
+      </c>
+      <c r="O100" s="20">
+        <v>24.32</v>
+      </c>
+      <c r="P100" s="20">
+        <v>46.35</v>
+      </c>
+      <c r="Q100" s="20">
+        <v>3281</v>
+      </c>
+      <c r="R100" s="7">
+        <v>21.11</v>
+      </c>
+      <c r="S100" s="7">
+        <v>20.51</v>
+      </c>
+      <c r="T100" s="7">
+        <v>39.090000000000003</v>
+      </c>
+      <c r="U100" s="7">
+        <v>19.29</v>
+      </c>
+      <c r="V100" s="26">
+        <v>2767</v>
       </c>
       <c r="W100" s="26" t="s">
         <v>1</v>
@@ -25228,32 +25288,32 @@
       <c r="M101" s="20">
         <v>3300.2</v>
       </c>
-      <c r="N101" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="O101" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P101" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q101" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R101" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S101" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T101" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U101" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V101" s="26" t="s">
-        <v>1</v>
+      <c r="N101" s="20">
+        <v>6.82</v>
+      </c>
+      <c r="O101" s="20">
+        <v>23.5</v>
+      </c>
+      <c r="P101" s="20">
+        <v>47.49</v>
+      </c>
+      <c r="Q101" s="20">
+        <v>3195</v>
+      </c>
+      <c r="R101" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="S101" s="7">
+        <v>19.55</v>
+      </c>
+      <c r="T101" s="7">
+        <v>39.5</v>
+      </c>
+      <c r="U101" s="7">
+        <v>18.45</v>
+      </c>
+      <c r="V101" s="26">
+        <v>2657</v>
       </c>
       <c r="W101" s="26" t="s">
         <v>1</v>
@@ -25338,32 +25398,32 @@
       <c r="M102" s="20">
         <v>3693.2</v>
       </c>
-      <c r="N102" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="O102" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P102" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q102" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R102" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S102" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T102" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U102" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V102" s="26" t="s">
-        <v>1</v>
+      <c r="N102" s="20">
+        <v>7.76</v>
+      </c>
+      <c r="O102" s="20">
+        <v>26.31</v>
+      </c>
+      <c r="P102" s="20">
+        <v>34.04</v>
+      </c>
+      <c r="Q102" s="20">
+        <v>4293</v>
+      </c>
+      <c r="R102" s="7">
+        <v>23.29</v>
+      </c>
+      <c r="S102" s="7">
+        <v>21.88</v>
+      </c>
+      <c r="T102" s="7">
+        <v>28.31</v>
+      </c>
+      <c r="U102" s="7">
+        <v>26.52</v>
+      </c>
+      <c r="V102" s="26">
+        <v>3570</v>
       </c>
       <c r="W102" s="26" t="s">
         <v>1</v>
@@ -25448,32 +25508,32 @@
       <c r="M103" s="20">
         <v>3810.8</v>
       </c>
-      <c r="N103" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="O103" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P103" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q103" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R103" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S103" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T103" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U103" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V103" s="26" t="s">
-        <v>1</v>
+      <c r="N103" s="20">
+        <v>7.36</v>
+      </c>
+      <c r="O103" s="20">
+        <v>22.93</v>
+      </c>
+      <c r="P103" s="20">
+        <v>40.85</v>
+      </c>
+      <c r="Q103" s="20">
+        <v>3771</v>
+      </c>
+      <c r="R103" s="7">
+        <v>22.91</v>
+      </c>
+      <c r="S103" s="7">
+        <v>19.079999999999998</v>
+      </c>
+      <c r="T103" s="7">
+        <v>33.99</v>
+      </c>
+      <c r="U103" s="7">
+        <v>24.02</v>
+      </c>
+      <c r="V103" s="26">
+        <v>3138</v>
       </c>
       <c r="W103" s="26" t="s">
         <v>1</v>
@@ -25558,32 +25618,32 @@
       <c r="M104" s="20">
         <v>4100.08</v>
       </c>
-      <c r="N104" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="O104" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P104" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q104" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R104" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S104" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T104" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U104" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V104" s="26" t="s">
-        <v>1</v>
+      <c r="N104" s="20">
+        <v>7.69</v>
+      </c>
+      <c r="O104" s="20">
+        <v>24.63</v>
+      </c>
+      <c r="P104" s="20">
+        <v>42.59</v>
+      </c>
+      <c r="Q104" s="20">
+        <v>3529</v>
+      </c>
+      <c r="R104" s="7">
+        <v>21.91</v>
+      </c>
+      <c r="S104" s="7">
+        <v>20.84</v>
+      </c>
+      <c r="T104" s="7">
+        <v>36.03</v>
+      </c>
+      <c r="U104" s="7">
+        <v>21.22</v>
+      </c>
+      <c r="V104" s="26">
+        <v>2985</v>
       </c>
       <c r="W104" s="26" t="s">
         <v>1</v>
@@ -25668,32 +25728,32 @@
       <c r="M105" s="20">
         <v>3912.4</v>
       </c>
-      <c r="N105" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="O105" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P105" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q105" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R105" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S105" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T105" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U105" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V105" s="26" t="s">
-        <v>1</v>
+      <c r="N105" s="20">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="O105" s="20">
+        <v>26.31</v>
+      </c>
+      <c r="P105" s="20">
+        <v>39.11</v>
+      </c>
+      <c r="Q105" s="20">
+        <v>3711</v>
+      </c>
+      <c r="R105" s="7">
+        <v>22.19</v>
+      </c>
+      <c r="S105" s="7">
+        <v>22.32</v>
+      </c>
+      <c r="T105" s="7">
+        <v>33.18</v>
+      </c>
+      <c r="U105" s="7">
+        <v>22.31</v>
+      </c>
+      <c r="V105" s="26">
+        <v>3149</v>
       </c>
       <c r="W105" s="26" t="s">
         <v>1</v>
@@ -25778,32 +25838,32 @@
       <c r="M106" s="20">
         <v>3848.2</v>
       </c>
-      <c r="N106" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="O106" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P106" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q106" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R106" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S106" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T106" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U106" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V106" s="26" t="s">
-        <v>1</v>
+      <c r="N106" s="20">
+        <v>7.13</v>
+      </c>
+      <c r="O106" s="20">
+        <v>24.07</v>
+      </c>
+      <c r="P106" s="20">
+        <v>45.7</v>
+      </c>
+      <c r="Q106" s="20">
+        <v>3246</v>
+      </c>
+      <c r="R106" s="7">
+        <v>23.48</v>
+      </c>
+      <c r="S106" s="7">
+        <v>19.829999999999998</v>
+      </c>
+      <c r="T106" s="7">
+        <v>37.65</v>
+      </c>
+      <c r="U106" s="7">
+        <v>19.04</v>
+      </c>
+      <c r="V106" s="26">
+        <v>2675</v>
       </c>
       <c r="W106" s="26" t="s">
         <v>1</v>
@@ -25888,32 +25948,32 @@
       <c r="M107" s="20">
         <v>3856.4</v>
       </c>
-      <c r="N107" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="O107" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="P107" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q107" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R107" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S107" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="T107" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="U107" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V107" s="26" t="s">
-        <v>1</v>
+      <c r="N107" s="20">
+        <v>6.89</v>
+      </c>
+      <c r="O107" s="20">
+        <v>22.61</v>
+      </c>
+      <c r="P107" s="20">
+        <v>42.14</v>
+      </c>
+      <c r="Q107" s="20">
+        <v>3670</v>
+      </c>
+      <c r="R107" s="7">
+        <v>22.02</v>
+      </c>
+      <c r="S107" s="7">
+        <v>18.940000000000001</v>
+      </c>
+      <c r="T107" s="7">
+        <v>35.29</v>
+      </c>
+      <c r="U107" s="7">
+        <v>23.75</v>
+      </c>
+      <c r="V107" s="26">
+        <v>3074</v>
       </c>
       <c r="W107" s="26" t="s">
         <v>1</v>
@@ -25963,7 +26023,7 @@
         <v>105</v>
       </c>
       <c r="B108" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C108" s="25">
         <v>46260</v>
@@ -26073,7 +26133,7 @@
         <v>106</v>
       </c>
       <c r="B109" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C109" s="25">
         <v>46260</v>
@@ -26183,7 +26243,7 @@
         <v>107</v>
       </c>
       <c r="B110" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C110" s="25">
         <v>46260</v>
@@ -26290,7 +26350,7 @@
     </row>
     <row r="112" spans="1:36" ht="45.75">
       <c r="B112" s="34" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -26306,4 +26366,1406 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD3CE46B-EBFB-40D5-8B95-D45149ED2B06}">
+  <dimension ref="A1:AL16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="1.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="6.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.42578125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="1.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="5" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:38" ht="15" customHeight="1">
+      <c r="A1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="44"/>
+      <c r="Y1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z1" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA1" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB1" s="48"/>
+      <c r="AC1" s="48"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF1" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG1" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH1" s="48"/>
+      <c r="AI1" s="48"/>
+      <c r="AJ1" s="48"/>
+      <c r="AK1" s="49"/>
+      <c r="AL1" s="40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" ht="15.75">
+      <c r="A2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="46"/>
+      <c r="AA2" s="50"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="52"/>
+      <c r="AE2" s="41"/>
+      <c r="AF2" s="41"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="52"/>
+      <c r="AL2" s="41"/>
+    </row>
+    <row r="3" spans="1:38" ht="60.75">
+      <c r="A3" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="P3" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="S3" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE3" s="42"/>
+      <c r="AF3" s="42"/>
+      <c r="AG3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL3" s="42"/>
+    </row>
+    <row r="4" spans="1:38">
+      <c r="A4" s="24">
+        <v>1</v>
+      </c>
+      <c r="B4" s="20">
+        <v>16646</v>
+      </c>
+      <c r="C4" s="25">
+        <v>46266</v>
+      </c>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="20">
+        <v>162011737</v>
+      </c>
+      <c r="K4" s="25">
+        <v>46263</v>
+      </c>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20">
+        <v>3694.6</v>
+      </c>
+      <c r="N4" s="20">
+        <v>3845.8</v>
+      </c>
+      <c r="O4" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P4" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R4" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="7">
+        <v>21.3</v>
+      </c>
+      <c r="U4" s="7">
+        <v>19.93</v>
+      </c>
+      <c r="V4" s="7">
+        <v>34.26</v>
+      </c>
+      <c r="W4" s="7">
+        <v>24.5</v>
+      </c>
+      <c r="X4" s="26">
+        <v>3219</v>
+      </c>
+      <c r="Y4" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG4" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ4" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK4" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL4" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38">
+      <c r="A5" s="24">
+        <v>2</v>
+      </c>
+      <c r="B5" s="20">
+        <v>16647</v>
+      </c>
+      <c r="C5" s="25">
+        <v>46266</v>
+      </c>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="20">
+        <v>162003229</v>
+      </c>
+      <c r="K5" s="25">
+        <v>46263</v>
+      </c>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20">
+        <v>3542.7</v>
+      </c>
+      <c r="N5" s="20">
+        <v>3514.2</v>
+      </c>
+      <c r="O5" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="7">
+        <v>21.34</v>
+      </c>
+      <c r="U5" s="7">
+        <v>23.17</v>
+      </c>
+      <c r="V5" s="7">
+        <v>32.43</v>
+      </c>
+      <c r="W5" s="7">
+        <v>23.06</v>
+      </c>
+      <c r="X5" s="26">
+        <v>3320</v>
+      </c>
+      <c r="Y5" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ5" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK5" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL5" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38">
+      <c r="A6" s="24">
+        <v>3</v>
+      </c>
+      <c r="B6" s="20">
+        <v>16649</v>
+      </c>
+      <c r="C6" s="25">
+        <v>46266</v>
+      </c>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="20">
+        <v>162011741</v>
+      </c>
+      <c r="K6" s="25">
+        <v>46265</v>
+      </c>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20">
+        <v>3894.1</v>
+      </c>
+      <c r="N6" s="20">
+        <v>3901.4</v>
+      </c>
+      <c r="O6" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P6" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R6" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S6" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="7">
+        <v>23.67</v>
+      </c>
+      <c r="U6" s="7">
+        <v>18.16</v>
+      </c>
+      <c r="V6" s="7">
+        <v>33.659999999999997</v>
+      </c>
+      <c r="W6" s="7">
+        <v>24.51</v>
+      </c>
+      <c r="X6" s="26">
+        <v>3148</v>
+      </c>
+      <c r="Y6" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ6" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38">
+      <c r="A7" s="24">
+        <v>4</v>
+      </c>
+      <c r="B7" s="20">
+        <v>16651</v>
+      </c>
+      <c r="C7" s="25">
+        <v>46267</v>
+      </c>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="20">
+        <v>162011739</v>
+      </c>
+      <c r="K7" s="25">
+        <v>46264</v>
+      </c>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20">
+        <v>4009.9</v>
+      </c>
+      <c r="N7" s="20">
+        <v>4241.8</v>
+      </c>
+      <c r="O7" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P7" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R7" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="7">
+        <v>22.39</v>
+      </c>
+      <c r="U7" s="7">
+        <v>17.53</v>
+      </c>
+      <c r="V7" s="7">
+        <v>36.83</v>
+      </c>
+      <c r="W7" s="7">
+        <v>23.25</v>
+      </c>
+      <c r="X7" s="26">
+        <v>2923</v>
+      </c>
+      <c r="Y7" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ7" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK7" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL7" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38">
+      <c r="A8" s="24">
+        <v>5</v>
+      </c>
+      <c r="B8" s="20">
+        <v>16652</v>
+      </c>
+      <c r="C8" s="25">
+        <v>46267</v>
+      </c>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="20">
+        <v>162011743</v>
+      </c>
+      <c r="K8" s="25">
+        <v>46265</v>
+      </c>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20">
+        <v>3979.7</v>
+      </c>
+      <c r="N8" s="20">
+        <v>3935.8</v>
+      </c>
+      <c r="O8" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P8" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R8" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S8" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="7">
+        <v>21.88</v>
+      </c>
+      <c r="U8" s="7">
+        <v>17.86</v>
+      </c>
+      <c r="V8" s="7">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="W8" s="7">
+        <v>24.46</v>
+      </c>
+      <c r="X8" s="26">
+        <v>2971</v>
+      </c>
+      <c r="Y8" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ8" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK8" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL8" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38">
+      <c r="A9" s="24">
+        <v>6</v>
+      </c>
+      <c r="B9" s="20">
+        <v>16653</v>
+      </c>
+      <c r="C9" s="25">
+        <v>46268</v>
+      </c>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9" s="20">
+        <v>162011744</v>
+      </c>
+      <c r="K9" s="25">
+        <v>46266</v>
+      </c>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20">
+        <v>3650.5</v>
+      </c>
+      <c r="N9" s="20">
+        <v>3714.4</v>
+      </c>
+      <c r="O9" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P9" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R9" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S9" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="7">
+        <v>23.36</v>
+      </c>
+      <c r="U9" s="7">
+        <v>18.8</v>
+      </c>
+      <c r="V9" s="7">
+        <v>33.020000000000003</v>
+      </c>
+      <c r="W9" s="7">
+        <v>24.82</v>
+      </c>
+      <c r="X9" s="26">
+        <v>3092</v>
+      </c>
+      <c r="Y9" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ9" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK9" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL9" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38">
+      <c r="A10" s="24">
+        <v>7</v>
+      </c>
+      <c r="B10" s="20">
+        <v>16656</v>
+      </c>
+      <c r="C10" s="25">
+        <v>46269</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J10" s="20">
+        <v>162011745</v>
+      </c>
+      <c r="K10" s="25">
+        <v>46268</v>
+      </c>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20">
+        <v>3273.8</v>
+      </c>
+      <c r="N10" s="20">
+        <v>3166.6</v>
+      </c>
+      <c r="O10" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="P10" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R10" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="S10" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="7">
+        <v>23.63</v>
+      </c>
+      <c r="U10" s="7">
+        <v>21.12</v>
+      </c>
+      <c r="V10" s="7">
+        <v>27.45</v>
+      </c>
+      <c r="W10" s="7">
+        <v>27.81</v>
+      </c>
+      <c r="X10" s="26">
+        <v>3608</v>
+      </c>
+      <c r="Y10" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ10" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK10" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL10" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38">
+      <c r="A11" s="24">
+        <v>8</v>
+      </c>
+      <c r="B11" s="20">
+        <v>16659</v>
+      </c>
+      <c r="C11" s="25">
+        <v>46270</v>
+      </c>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" s="20">
+        <v>162011747</v>
+      </c>
+      <c r="K11" s="25">
+        <v>46269</v>
+      </c>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20">
+        <v>4014.4</v>
+      </c>
+      <c r="N11" s="20">
+        <v>4018.4</v>
+      </c>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="26"/>
+      <c r="Y11" s="26"/>
+      <c r="Z11" s="27"/>
+      <c r="AA11" s="27"/>
+      <c r="AB11" s="27"/>
+      <c r="AC11" s="27"/>
+      <c r="AD11" s="27"/>
+      <c r="AE11" s="27"/>
+      <c r="AF11" s="28"/>
+      <c r="AG11" s="27"/>
+      <c r="AH11" s="29"/>
+      <c r="AI11" s="29"/>
+      <c r="AJ11" s="29"/>
+      <c r="AK11" s="29"/>
+      <c r="AL11" s="20"/>
+    </row>
+    <row r="12" spans="1:38">
+      <c r="A12" s="24">
+        <v>9</v>
+      </c>
+      <c r="B12" s="20">
+        <v>16660</v>
+      </c>
+      <c r="C12" s="25">
+        <v>46271</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J12" s="20">
+        <v>162006498</v>
+      </c>
+      <c r="K12" s="25">
+        <v>46269</v>
+      </c>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20">
+        <v>4141.8999999999996</v>
+      </c>
+      <c r="N12" s="20">
+        <v>4098.3999999999996</v>
+      </c>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="26"/>
+      <c r="Y12" s="26"/>
+      <c r="Z12" s="27"/>
+      <c r="AA12" s="27"/>
+      <c r="AB12" s="27"/>
+      <c r="AC12" s="27"/>
+      <c r="AD12" s="27"/>
+      <c r="AE12" s="27"/>
+      <c r="AF12" s="28"/>
+      <c r="AG12" s="27"/>
+      <c r="AH12" s="29"/>
+      <c r="AI12" s="29"/>
+      <c r="AJ12" s="29"/>
+      <c r="AK12" s="29"/>
+      <c r="AL12" s="20"/>
+    </row>
+    <row r="13" spans="1:38">
+      <c r="A13" s="24">
+        <v>10</v>
+      </c>
+      <c r="B13" s="20">
+        <v>16662</v>
+      </c>
+      <c r="C13" s="25">
+        <v>46272</v>
+      </c>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J13" s="20">
+        <v>162011750</v>
+      </c>
+      <c r="K13" s="25">
+        <v>46270</v>
+      </c>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20">
+        <v>3389.7</v>
+      </c>
+      <c r="N13" s="35">
+        <f>M13</f>
+        <v>3389.7</v>
+      </c>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="26"/>
+      <c r="Y13" s="26"/>
+      <c r="Z13" s="27"/>
+      <c r="AA13" s="27"/>
+      <c r="AB13" s="27"/>
+      <c r="AC13" s="27"/>
+      <c r="AD13" s="27"/>
+      <c r="AE13" s="27"/>
+      <c r="AF13" s="28"/>
+      <c r="AG13" s="27"/>
+      <c r="AH13" s="29"/>
+      <c r="AI13" s="29"/>
+      <c r="AJ13" s="29"/>
+      <c r="AK13" s="29"/>
+      <c r="AL13" s="20"/>
+    </row>
+    <row r="14" spans="1:38">
+      <c r="A14" s="24">
+        <v>11</v>
+      </c>
+      <c r="B14" s="20">
+        <v>16663</v>
+      </c>
+      <c r="C14" s="25">
+        <v>46272</v>
+      </c>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J14" s="20">
+        <v>162004434</v>
+      </c>
+      <c r="K14" s="25">
+        <v>46270</v>
+      </c>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20">
+        <v>3923.6</v>
+      </c>
+      <c r="N14" s="20">
+        <v>3786.6</v>
+      </c>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="26"/>
+      <c r="Y14" s="26"/>
+      <c r="Z14" s="27"/>
+      <c r="AA14" s="27"/>
+      <c r="AB14" s="27"/>
+      <c r="AC14" s="27"/>
+      <c r="AD14" s="27"/>
+      <c r="AE14" s="27"/>
+      <c r="AF14" s="28"/>
+      <c r="AG14" s="27"/>
+      <c r="AH14" s="29"/>
+      <c r="AI14" s="29"/>
+      <c r="AJ14" s="29"/>
+      <c r="AK14" s="29"/>
+      <c r="AL14" s="20"/>
+    </row>
+    <row r="15" spans="1:38">
+      <c r="A15" s="24">
+        <v>12</v>
+      </c>
+      <c r="B15" s="20">
+        <v>16664</v>
+      </c>
+      <c r="C15" s="25">
+        <v>46272</v>
+      </c>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J15" s="20">
+        <v>162006500</v>
+      </c>
+      <c r="K15" s="25">
+        <v>46270</v>
+      </c>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20">
+        <v>3714.9</v>
+      </c>
+      <c r="N15" s="20">
+        <v>3665</v>
+      </c>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="26"/>
+      <c r="Y15" s="26"/>
+      <c r="Z15" s="27"/>
+      <c r="AA15" s="27"/>
+      <c r="AB15" s="27"/>
+      <c r="AC15" s="27"/>
+      <c r="AD15" s="27"/>
+      <c r="AE15" s="27"/>
+      <c r="AF15" s="28"/>
+      <c r="AG15" s="27"/>
+      <c r="AH15" s="29"/>
+      <c r="AI15" s="29"/>
+      <c r="AJ15" s="29"/>
+      <c r="AK15" s="29"/>
+      <c r="AL15" s="20"/>
+    </row>
+    <row r="16" spans="1:38">
+      <c r="A16" s="24">
+        <v>13</v>
+      </c>
+      <c r="B16" s="20">
+        <v>16666</v>
+      </c>
+      <c r="C16" s="25">
+        <v>46272</v>
+      </c>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J16" s="20">
+        <v>162006503</v>
+      </c>
+      <c r="K16" s="25">
+        <v>46271</v>
+      </c>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20">
+        <v>3711.6</v>
+      </c>
+      <c r="N16" s="20">
+        <v>3669.6</v>
+      </c>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="26"/>
+      <c r="Y16" s="26"/>
+      <c r="Z16" s="27"/>
+      <c r="AA16" s="27"/>
+      <c r="AB16" s="27"/>
+      <c r="AC16" s="27"/>
+      <c r="AD16" s="27"/>
+      <c r="AE16" s="27"/>
+      <c r="AF16" s="28"/>
+      <c r="AG16" s="27"/>
+      <c r="AH16" s="29"/>
+      <c r="AI16" s="29"/>
+      <c r="AJ16" s="29"/>
+      <c r="AK16" s="29"/>
+      <c r="AL16" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="AL1:AL3"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="Z1:Z2"/>
+    <mergeCell ref="AA1:AD2"/>
+    <mergeCell ref="AE1:AE3"/>
+    <mergeCell ref="AF1:AF3"/>
+    <mergeCell ref="AG1:AK2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Quality.xlsx
+++ b/Quality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30431"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30502"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ppgclindia-my.sharepoint.com/personal/bikram_mohapatra_ppgcl_co_in/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA2327CE-418C-4AB9-A556-5A5AA38B8110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{826187C2-81AF-4FE5-9A89-100E910FC15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JULY-26" sheetId="11" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2107" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1942" uniqueCount="56">
   <si>
     <t>IGI Report</t>
   </si>
@@ -669,14 +669,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -684,7 +684,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -708,16 +708,16 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1063,21 +1063,21 @@
       <c r="U1" s="13"/>
       <c r="V1" s="13"/>
       <c r="W1" s="13"/>
-      <c r="X1" s="53" t="s">
+      <c r="X1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="Y1" s="54"/>
-      <c r="Z1" s="54"/>
-      <c r="AA1" s="54"/>
-      <c r="AB1" s="54"/>
-      <c r="AC1" s="54"/>
-      <c r="AD1" s="54"/>
-      <c r="AE1" s="54"/>
-      <c r="AF1" s="54"/>
-      <c r="AG1" s="54"/>
-      <c r="AH1" s="54"/>
-      <c r="AI1" s="54"/>
-      <c r="AJ1" s="55"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="41"/>
+      <c r="AA1" s="41"/>
+      <c r="AB1" s="41"/>
+      <c r="AC1" s="41"/>
+      <c r="AD1" s="41"/>
+      <c r="AE1" s="41"/>
+      <c r="AF1" s="41"/>
+      <c r="AG1" s="41"/>
+      <c r="AH1" s="41"/>
+      <c r="AI1" s="41"/>
+      <c r="AJ1" s="42"/>
     </row>
     <row r="2" spans="1:36" ht="15" customHeight="1">
       <c r="A2" s="15"/>
@@ -1109,7 +1109,7 @@
       <c r="W2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="56" t="s">
+      <c r="X2" s="45" t="s">
         <v>3</v>
       </c>
       <c r="Y2" s="47" t="s">
@@ -1118,10 +1118,10 @@
       <c r="Z2" s="48"/>
       <c r="AA2" s="48"/>
       <c r="AB2" s="49"/>
-      <c r="AC2" s="41" t="s">
+      <c r="AC2" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="AD2" s="41" t="s">
+      <c r="AD2" s="53" t="s">
         <v>6</v>
       </c>
       <c r="AE2" s="47" t="s">
@@ -1131,7 +1131,7 @@
       <c r="AG2" s="48"/>
       <c r="AH2" s="48"/>
       <c r="AI2" s="49"/>
-      <c r="AJ2" s="41" t="s">
+      <c r="AJ2" s="53" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1210,14 +1210,14 @@
       <c r="Z3" s="51"/>
       <c r="AA3" s="51"/>
       <c r="AB3" s="52"/>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="41"/>
+      <c r="AC3" s="53"/>
+      <c r="AD3" s="53"/>
       <c r="AE3" s="50"/>
       <c r="AF3" s="51"/>
       <c r="AG3" s="51"/>
       <c r="AH3" s="51"/>
       <c r="AI3" s="52"/>
-      <c r="AJ3" s="41"/>
+      <c r="AJ3" s="53"/>
     </row>
     <row r="4" spans="1:36" ht="60.75">
       <c r="A4" s="11" t="s">
@@ -1304,8 +1304,8 @@
       <c r="AB4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AC4" s="42"/>
-      <c r="AD4" s="42"/>
+      <c r="AC4" s="54"/>
+      <c r="AD4" s="54"/>
       <c r="AE4" s="6" t="s">
         <v>32</v>
       </c>
@@ -1321,7 +1321,7 @@
       <c r="AI4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AJ4" s="42"/>
+      <c r="AJ4" s="54"/>
     </row>
     <row r="5" spans="1:36">
       <c r="A5" s="24">
@@ -14456,21 +14456,21 @@
       <c r="U1" s="13"/>
       <c r="V1" s="13"/>
       <c r="W1" s="13"/>
-      <c r="X1" s="53" t="s">
+      <c r="X1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="Y1" s="54"/>
-      <c r="Z1" s="54"/>
-      <c r="AA1" s="54"/>
-      <c r="AB1" s="54"/>
-      <c r="AC1" s="54"/>
-      <c r="AD1" s="54"/>
-      <c r="AE1" s="54"/>
-      <c r="AF1" s="54"/>
-      <c r="AG1" s="54"/>
-      <c r="AH1" s="54"/>
-      <c r="AI1" s="54"/>
-      <c r="AJ1" s="55"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="41"/>
+      <c r="AA1" s="41"/>
+      <c r="AB1" s="41"/>
+      <c r="AC1" s="41"/>
+      <c r="AD1" s="41"/>
+      <c r="AE1" s="41"/>
+      <c r="AF1" s="41"/>
+      <c r="AG1" s="41"/>
+      <c r="AH1" s="41"/>
+      <c r="AI1" s="41"/>
+      <c r="AJ1" s="42"/>
     </row>
     <row r="2" spans="1:36" ht="15.75" customHeight="1">
       <c r="A2" s="15"/>
@@ -14500,7 +14500,7 @@
       <c r="W2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="56" t="s">
+      <c r="X2" s="45" t="s">
         <v>3</v>
       </c>
       <c r="Y2" s="47" t="s">
@@ -14509,10 +14509,10 @@
       <c r="Z2" s="48"/>
       <c r="AA2" s="48"/>
       <c r="AB2" s="49"/>
-      <c r="AC2" s="41" t="s">
+      <c r="AC2" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="AD2" s="41" t="s">
+      <c r="AD2" s="53" t="s">
         <v>6</v>
       </c>
       <c r="AE2" s="47" t="s">
@@ -14522,7 +14522,7 @@
       <c r="AG2" s="48"/>
       <c r="AH2" s="48"/>
       <c r="AI2" s="49"/>
-      <c r="AJ2" s="41" t="s">
+      <c r="AJ2" s="53" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14575,14 +14575,14 @@
       <c r="Z3" s="51"/>
       <c r="AA3" s="51"/>
       <c r="AB3" s="52"/>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="41"/>
+      <c r="AC3" s="53"/>
+      <c r="AD3" s="53"/>
       <c r="AE3" s="50"/>
       <c r="AF3" s="51"/>
       <c r="AG3" s="51"/>
       <c r="AH3" s="51"/>
       <c r="AI3" s="52"/>
-      <c r="AJ3" s="41"/>
+      <c r="AJ3" s="53"/>
     </row>
     <row r="4" spans="1:36" ht="60.75">
       <c r="A4" s="11" t="s">
@@ -14669,8 +14669,8 @@
       <c r="AB4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AC4" s="42"/>
-      <c r="AD4" s="42"/>
+      <c r="AC4" s="54"/>
+      <c r="AD4" s="54"/>
       <c r="AE4" s="6" t="s">
         <v>32</v>
       </c>
@@ -14686,7 +14686,7 @@
       <c r="AI4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AJ4" s="42"/>
+      <c r="AJ4" s="54"/>
     </row>
     <row r="5" spans="1:36">
       <c r="A5" s="24">
@@ -23541,19 +23541,19 @@
         <v>3394</v>
       </c>
       <c r="R85" s="7">
-        <v>23.93</v>
+        <v>23.06</v>
       </c>
       <c r="S85" s="7">
-        <v>18.77</v>
+        <v>18.989999999999998</v>
       </c>
       <c r="T85" s="7">
-        <v>37.049999999999997</v>
+        <v>37.47</v>
       </c>
       <c r="U85" s="7">
-        <v>20.25</v>
+        <v>20.48</v>
       </c>
       <c r="V85" s="26">
-        <v>2775</v>
+        <v>2807</v>
       </c>
       <c r="W85" s="26" t="s">
         <v>1</v>
@@ -24768,44 +24768,44 @@
       <c r="W96" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X96" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y96" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z96" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA96" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB96" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC96" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD96" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE96" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF96" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG96" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH96" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI96" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ96" s="20" t="s">
-        <v>1</v>
+      <c r="X96" s="27">
+        <v>19.059999999999999</v>
+      </c>
+      <c r="Y96" s="27">
+        <v>6.09</v>
+      </c>
+      <c r="Z96" s="27">
+        <v>22.59</v>
+      </c>
+      <c r="AA96" s="27">
+        <v>44.94</v>
+      </c>
+      <c r="AB96" s="27">
+        <v>26.38</v>
+      </c>
+      <c r="AC96" s="27">
+        <v>3318</v>
+      </c>
+      <c r="AD96" s="28">
+        <v>2860</v>
+      </c>
+      <c r="AE96" s="27">
+        <v>6.45</v>
+      </c>
+      <c r="AF96" s="29">
+        <v>22.5</v>
+      </c>
+      <c r="AG96" s="29">
+        <v>44.77</v>
+      </c>
+      <c r="AH96" s="29">
+        <v>26.28</v>
+      </c>
+      <c r="AI96" s="29">
+        <v>3305</v>
+      </c>
+      <c r="AJ96" s="20">
+        <v>2860</v>
       </c>
     </row>
     <row r="97" spans="1:36">
@@ -24878,44 +24878,44 @@
       <c r="W97" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X97" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y97" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z97" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA97" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB97" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC97" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD97" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE97" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF97" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG97" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH97" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI97" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ97" s="20" t="s">
-        <v>1</v>
+      <c r="X97" s="27">
+        <v>22.74</v>
+      </c>
+      <c r="Y97" s="27">
+        <v>5.57</v>
+      </c>
+      <c r="Z97" s="27">
+        <v>21.23</v>
+      </c>
+      <c r="AA97" s="27">
+        <v>41.28</v>
+      </c>
+      <c r="AB97" s="27">
+        <v>31.92</v>
+      </c>
+      <c r="AC97" s="27">
+        <v>3747</v>
+      </c>
+      <c r="AD97" s="28">
+        <v>3066</v>
+      </c>
+      <c r="AE97" s="27">
+        <v>5.95</v>
+      </c>
+      <c r="AF97" s="29">
+        <v>21.14</v>
+      </c>
+      <c r="AG97" s="29">
+        <v>41.11</v>
+      </c>
+      <c r="AH97" s="29">
+        <v>31.79</v>
+      </c>
+      <c r="AI97" s="29">
+        <v>3732</v>
+      </c>
+      <c r="AJ97" s="20">
+        <v>3066</v>
       </c>
     </row>
     <row r="98" spans="1:36">
@@ -24988,44 +24988,44 @@
       <c r="W98" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X98" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y98" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z98" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA98" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB98" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC98" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD98" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE98" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF98" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG98" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH98" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI98" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ98" s="20" t="s">
-        <v>1</v>
+      <c r="X98" s="27">
+        <v>23.64</v>
+      </c>
+      <c r="Y98" s="27">
+        <v>6.41</v>
+      </c>
+      <c r="Z98" s="27">
+        <v>25.83</v>
+      </c>
+      <c r="AA98" s="27">
+        <v>39.01</v>
+      </c>
+      <c r="AB98" s="27">
+        <v>28.75</v>
+      </c>
+      <c r="AC98" s="27">
+        <v>3831</v>
+      </c>
+      <c r="AD98" s="28">
+        <v>3126</v>
+      </c>
+      <c r="AE98" s="27">
+        <v>6.74</v>
+      </c>
+      <c r="AF98" s="29">
+        <v>25.74</v>
+      </c>
+      <c r="AG98" s="29">
+        <v>38.869999999999997</v>
+      </c>
+      <c r="AH98" s="29">
+        <v>28.65</v>
+      </c>
+      <c r="AI98" s="29">
+        <v>3817</v>
+      </c>
+      <c r="AJ98" s="20">
+        <v>3126</v>
       </c>
     </row>
     <row r="99" spans="1:36">
@@ -25098,44 +25098,44 @@
       <c r="W99" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X99" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y99" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z99" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA99" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB99" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC99" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD99" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE99" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF99" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG99" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH99" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI99" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ99" s="20" t="s">
-        <v>1</v>
+      <c r="X99" s="27">
+        <v>23.76</v>
+      </c>
+      <c r="Y99" s="27">
+        <v>6.42</v>
+      </c>
+      <c r="Z99" s="27">
+        <v>24.48</v>
+      </c>
+      <c r="AA99" s="27">
+        <v>40.549999999999997</v>
+      </c>
+      <c r="AB99" s="27">
+        <v>28.55</v>
+      </c>
+      <c r="AC99" s="27">
+        <v>3732</v>
+      </c>
+      <c r="AD99" s="28">
+        <v>3040</v>
+      </c>
+      <c r="AE99" s="27">
+        <v>6.81</v>
+      </c>
+      <c r="AF99" s="29">
+        <v>24.38</v>
+      </c>
+      <c r="AG99" s="29">
+        <v>40.380000000000003</v>
+      </c>
+      <c r="AH99" s="29">
+        <v>28.43</v>
+      </c>
+      <c r="AI99" s="29">
+        <v>3716</v>
+      </c>
+      <c r="AJ99" s="20">
+        <v>3040</v>
       </c>
     </row>
     <row r="100" spans="1:36">
@@ -25208,44 +25208,44 @@
       <c r="W100" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X100" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y100" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z100" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA100" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB100" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC100" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD100" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE100" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF100" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG100" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH100" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI100" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ100" s="20" t="s">
-        <v>1</v>
+      <c r="X100" s="27">
+        <v>21.11</v>
+      </c>
+      <c r="Y100" s="27">
+        <v>6.04</v>
+      </c>
+      <c r="Z100" s="27">
+        <v>22.64</v>
+      </c>
+      <c r="AA100" s="27">
+        <v>45.57</v>
+      </c>
+      <c r="AB100" s="27">
+        <v>25.75</v>
+      </c>
+      <c r="AC100" s="27">
+        <v>3247</v>
+      </c>
+      <c r="AD100" s="28">
+        <v>2726</v>
+      </c>
+      <c r="AE100" s="27">
+        <v>6.46</v>
+      </c>
+      <c r="AF100" s="29">
+        <v>22.54</v>
+      </c>
+      <c r="AG100" s="29">
+        <v>45.37</v>
+      </c>
+      <c r="AH100" s="29">
+        <v>25.63</v>
+      </c>
+      <c r="AI100" s="29">
+        <v>3232</v>
+      </c>
+      <c r="AJ100" s="20">
+        <v>2726</v>
       </c>
     </row>
     <row r="101" spans="1:36">
@@ -25318,44 +25318,44 @@
       <c r="W101" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X101" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y101" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z101" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA101" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB101" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC101" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD101" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE101" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF101" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG101" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH101" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI101" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ101" s="20" t="s">
-        <v>1</v>
+      <c r="X101" s="27">
+        <v>22.5</v>
+      </c>
+      <c r="Y101" s="27">
+        <v>5.64</v>
+      </c>
+      <c r="Z101" s="27">
+        <v>21.17</v>
+      </c>
+      <c r="AA101" s="27">
+        <v>47.01</v>
+      </c>
+      <c r="AB101" s="27">
+        <v>26.18</v>
+      </c>
+      <c r="AC101" s="27">
+        <v>3239</v>
+      </c>
+      <c r="AD101" s="28">
+        <v>2660</v>
+      </c>
+      <c r="AE101" s="27">
+        <v>6.01</v>
+      </c>
+      <c r="AF101" s="29">
+        <v>21.09</v>
+      </c>
+      <c r="AG101" s="29">
+        <v>46.83</v>
+      </c>
+      <c r="AH101" s="29">
+        <v>26.08</v>
+      </c>
+      <c r="AI101" s="29">
+        <v>3226</v>
+      </c>
+      <c r="AJ101" s="20">
+        <v>2660</v>
       </c>
     </row>
     <row r="102" spans="1:36">
@@ -25428,44 +25428,44 @@
       <c r="W102" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X102" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y102" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z102" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA102" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB102" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC102" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD102" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE102" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF102" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG102" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH102" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI102" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ102" s="20" t="s">
-        <v>1</v>
+      <c r="X102" s="27">
+        <v>23.29</v>
+      </c>
+      <c r="Y102" s="27">
+        <v>6.16</v>
+      </c>
+      <c r="Z102" s="27">
+        <v>24.02</v>
+      </c>
+      <c r="AA102" s="27">
+        <v>34.58</v>
+      </c>
+      <c r="AB102" s="27">
+        <v>35.24</v>
+      </c>
+      <c r="AC102" s="27">
+        <v>4296</v>
+      </c>
+      <c r="AD102" s="28">
+        <v>3512</v>
+      </c>
+      <c r="AE102" s="27">
+        <v>7.54</v>
+      </c>
+      <c r="AF102" s="29">
+        <v>23.67</v>
+      </c>
+      <c r="AG102" s="29">
+        <v>34.07</v>
+      </c>
+      <c r="AH102" s="29">
+        <v>34.72</v>
+      </c>
+      <c r="AI102" s="29">
+        <v>4233</v>
+      </c>
+      <c r="AJ102" s="20">
+        <v>3512</v>
       </c>
     </row>
     <row r="103" spans="1:36">
@@ -25538,44 +25538,44 @@
       <c r="W103" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X103" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y103" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z103" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA103" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB103" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC103" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD103" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE103" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF103" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG103" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH103" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI103" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ103" s="20" t="s">
-        <v>1</v>
+      <c r="X103" s="27">
+        <v>22.91</v>
+      </c>
+      <c r="Y103" s="27">
+        <v>5.32</v>
+      </c>
+      <c r="Z103" s="27">
+        <v>20.92</v>
+      </c>
+      <c r="AA103" s="27">
+        <v>40.57</v>
+      </c>
+      <c r="AB103" s="27">
+        <v>33.19</v>
+      </c>
+      <c r="AC103" s="27">
+        <v>3845</v>
+      </c>
+      <c r="AD103" s="28">
+        <v>3131</v>
+      </c>
+      <c r="AE103" s="27">
+        <v>6.7</v>
+      </c>
+      <c r="AF103" s="29">
+        <v>20.62</v>
+      </c>
+      <c r="AG103" s="29">
+        <v>39.979999999999997</v>
+      </c>
+      <c r="AH103" s="29">
+        <v>32.71</v>
+      </c>
+      <c r="AI103" s="29">
+        <v>3789</v>
+      </c>
+      <c r="AJ103" s="20">
+        <v>3131</v>
       </c>
     </row>
     <row r="104" spans="1:36">
@@ -25648,44 +25648,44 @@
       <c r="W104" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X104" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y104" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z104" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA104" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB104" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC104" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD104" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE104" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF104" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG104" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH104" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI104" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ104" s="20" t="s">
-        <v>1</v>
+      <c r="X104" s="27">
+        <v>21.91</v>
+      </c>
+      <c r="Y104" s="27">
+        <v>6.48</v>
+      </c>
+      <c r="Z104" s="27">
+        <v>22.86</v>
+      </c>
+      <c r="AA104" s="27">
+        <v>42.39</v>
+      </c>
+      <c r="AB104" s="27">
+        <v>28.27</v>
+      </c>
+      <c r="AC104" s="27">
+        <v>3496</v>
+      </c>
+      <c r="AD104" s="28">
+        <v>2919</v>
+      </c>
+      <c r="AE104" s="27">
+        <v>6.83</v>
+      </c>
+      <c r="AF104" s="29">
+        <v>22.77</v>
+      </c>
+      <c r="AG104" s="29">
+        <v>42.23</v>
+      </c>
+      <c r="AH104" s="29">
+        <v>28.16</v>
+      </c>
+      <c r="AI104" s="29">
+        <v>3483</v>
+      </c>
+      <c r="AJ104" s="20">
+        <v>2919</v>
       </c>
     </row>
     <row r="105" spans="1:36">
@@ -25758,44 +25758,44 @@
       <c r="W105" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X105" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y105" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z105" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA105" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB105" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC105" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD105" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE105" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF105" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG105" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH105" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI105" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ105" s="20" t="s">
-        <v>1</v>
+      <c r="X105" s="27">
+        <v>22.19</v>
+      </c>
+      <c r="Y105" s="27">
+        <v>6.74</v>
+      </c>
+      <c r="Z105" s="27">
+        <v>24.88</v>
+      </c>
+      <c r="AA105" s="27">
+        <v>39.29</v>
+      </c>
+      <c r="AB105" s="27">
+        <v>29.09</v>
+      </c>
+      <c r="AC105" s="27">
+        <v>3714</v>
+      </c>
+      <c r="AD105" s="28">
+        <v>3099</v>
+      </c>
+      <c r="AE105" s="27">
+        <v>8.08</v>
+      </c>
+      <c r="AF105" s="29">
+        <v>24.52</v>
+      </c>
+      <c r="AG105" s="29">
+        <v>38.729999999999997</v>
+      </c>
+      <c r="AH105" s="29">
+        <v>28.67</v>
+      </c>
+      <c r="AI105" s="29">
+        <v>3661</v>
+      </c>
+      <c r="AJ105" s="20">
+        <v>3099</v>
       </c>
     </row>
     <row r="106" spans="1:36">
@@ -25868,44 +25868,44 @@
       <c r="W106" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X106" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y106" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z106" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA106" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB106" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC106" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD106" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE106" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF106" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG106" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH106" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI106" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ106" s="20" t="s">
-        <v>1</v>
+      <c r="X106" s="27">
+        <v>23.48</v>
+      </c>
+      <c r="Y106" s="27">
+        <v>6.33</v>
+      </c>
+      <c r="Z106" s="27">
+        <v>23.67</v>
+      </c>
+      <c r="AA106" s="27">
+        <v>42.66</v>
+      </c>
+      <c r="AB106" s="27">
+        <v>27.34</v>
+      </c>
+      <c r="AC106" s="27">
+        <v>3304</v>
+      </c>
+      <c r="AD106" s="28">
+        <v>2699</v>
+      </c>
+      <c r="AE106" s="27">
+        <v>6.78</v>
+      </c>
+      <c r="AF106" s="29">
+        <v>23.56</v>
+      </c>
+      <c r="AG106" s="29">
+        <v>42.46</v>
+      </c>
+      <c r="AH106" s="29">
+        <v>27.21</v>
+      </c>
+      <c r="AI106" s="29">
+        <v>3288</v>
+      </c>
+      <c r="AJ106" s="20">
+        <v>2699</v>
       </c>
     </row>
     <row r="107" spans="1:36">
@@ -25978,44 +25978,44 @@
       <c r="W107" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="X107" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y107" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z107" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA107" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB107" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC107" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD107" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE107" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF107" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG107" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH107" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI107" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ107" s="20" t="s">
-        <v>1</v>
+      <c r="X107" s="27">
+        <v>22.02</v>
+      </c>
+      <c r="Y107" s="27">
+        <v>5.7</v>
+      </c>
+      <c r="Z107" s="27">
+        <v>21.28</v>
+      </c>
+      <c r="AA107" s="27">
+        <v>41.92</v>
+      </c>
+      <c r="AB107" s="27">
+        <v>31.1</v>
+      </c>
+      <c r="AC107" s="27">
+        <v>3676</v>
+      </c>
+      <c r="AD107" s="28">
+        <v>3040</v>
+      </c>
+      <c r="AE107" s="27">
+        <v>5.98</v>
+      </c>
+      <c r="AF107" s="29">
+        <v>21.22</v>
+      </c>
+      <c r="AG107" s="29">
+        <v>41.8</v>
+      </c>
+      <c r="AH107" s="29">
+        <v>31.01</v>
+      </c>
+      <c r="AI107" s="29">
+        <v>3665</v>
+      </c>
+      <c r="AJ107" s="20">
+        <v>3040</v>
       </c>
     </row>
     <row r="108" spans="1:36">
@@ -26088,44 +26088,44 @@
       <c r="W108" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="X108" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y108" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z108" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA108" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB108" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC108" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD108" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE108" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF108" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG108" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH108" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI108" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ108" s="20" t="s">
-        <v>1</v>
+      <c r="X108" s="20">
+        <v>19.71</v>
+      </c>
+      <c r="Y108" s="20">
+        <v>5.85</v>
+      </c>
+      <c r="Z108" s="20">
+        <v>22.51</v>
+      </c>
+      <c r="AA108" s="20">
+        <v>42.15</v>
+      </c>
+      <c r="AB108" s="20">
+        <v>29.49</v>
+      </c>
+      <c r="AC108" s="20">
+        <v>3640</v>
+      </c>
+      <c r="AD108" s="20">
+        <v>3104</v>
+      </c>
+      <c r="AE108" s="20">
+        <v>6.37</v>
+      </c>
+      <c r="AF108" s="20">
+        <v>22.39</v>
+      </c>
+      <c r="AG108" s="20">
+        <v>41.92</v>
+      </c>
+      <c r="AH108" s="20">
+        <v>29.33</v>
+      </c>
+      <c r="AI108" s="20">
+        <v>3620</v>
+      </c>
+      <c r="AJ108" s="20">
+        <v>3104</v>
       </c>
     </row>
     <row r="109" spans="1:36">
@@ -26198,44 +26198,44 @@
       <c r="W109" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="X109" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y109" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z109" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA109" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB109" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC109" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD109" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE109" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF109" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG109" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH109" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI109" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ109" s="20" t="s">
-        <v>1</v>
+      <c r="X109" s="20">
+        <v>22.69</v>
+      </c>
+      <c r="Y109" s="20">
+        <v>6.76</v>
+      </c>
+      <c r="Z109" s="20">
+        <v>25.69</v>
+      </c>
+      <c r="AA109" s="20">
+        <v>30.47</v>
+      </c>
+      <c r="AB109" s="20">
+        <v>37.08</v>
+      </c>
+      <c r="AC109" s="20">
+        <v>4563</v>
+      </c>
+      <c r="AD109" s="20">
+        <v>3783</v>
+      </c>
+      <c r="AE109" s="20">
+        <v>7.14</v>
+      </c>
+      <c r="AF109" s="20">
+        <v>25.59</v>
+      </c>
+      <c r="AG109" s="20">
+        <v>30.35</v>
+      </c>
+      <c r="AH109" s="20">
+        <v>36.93</v>
+      </c>
+      <c r="AI109" s="20">
+        <v>4544</v>
+      </c>
+      <c r="AJ109" s="20">
+        <v>3783</v>
       </c>
     </row>
     <row r="110" spans="1:36">
@@ -26327,25 +26327,25 @@
         <v>3867</v>
       </c>
       <c r="AD110" s="20">
-        <v>3340.953</v>
+        <v>3341</v>
       </c>
       <c r="AE110" s="20">
         <v>7.32</v>
       </c>
       <c r="AF110" s="20">
-        <v>23.559370000000001</v>
+        <v>23.56</v>
       </c>
       <c r="AG110" s="20">
-        <v>38.306159999999998</v>
+        <v>38.31</v>
       </c>
       <c r="AH110" s="20">
-        <v>30.81447</v>
+        <v>30.81</v>
       </c>
       <c r="AI110" s="20">
-        <v>3811.886</v>
+        <v>3812</v>
       </c>
       <c r="AJ110" s="20">
-        <v>3340.953</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="112" spans="1:36" ht="45.75">
@@ -26370,7 +26370,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD3CE46B-EBFB-40D5-8B95-D45149ED2B06}">
-  <dimension ref="A1:AL16"/>
+  <dimension ref="A1:AL31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -26443,7 +26443,7 @@
       <c r="Y1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="Z1" s="45" t="s">
+      <c r="Z1" s="56" t="s">
         <v>3</v>
       </c>
       <c r="AA1" s="47" t="s">
@@ -26452,10 +26452,10 @@
       <c r="AB1" s="48"/>
       <c r="AC1" s="48"/>
       <c r="AD1" s="49"/>
-      <c r="AE1" s="40" t="s">
+      <c r="AE1" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="40" t="s">
+      <c r="AF1" s="55" t="s">
         <v>6</v>
       </c>
       <c r="AG1" s="47" t="s">
@@ -26465,7 +26465,7 @@
       <c r="AI1" s="48"/>
       <c r="AJ1" s="48"/>
       <c r="AK1" s="49"/>
-      <c r="AL1" s="40" t="s">
+      <c r="AL1" s="55" t="s">
         <v>6</v>
       </c>
     </row>
@@ -26522,14 +26522,14 @@
       <c r="AB2" s="51"/>
       <c r="AC2" s="51"/>
       <c r="AD2" s="52"/>
-      <c r="AE2" s="41"/>
-      <c r="AF2" s="41"/>
+      <c r="AE2" s="53"/>
+      <c r="AF2" s="53"/>
       <c r="AG2" s="50"/>
       <c r="AH2" s="51"/>
       <c r="AI2" s="51"/>
       <c r="AJ2" s="51"/>
       <c r="AK2" s="52"/>
-      <c r="AL2" s="41"/>
+      <c r="AL2" s="53"/>
     </row>
     <row r="3" spans="1:38" ht="60.75">
       <c r="A3" s="11" t="s">
@@ -26620,8 +26620,8 @@
       <c r="AD3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AE3" s="42"/>
-      <c r="AF3" s="42"/>
+      <c r="AE3" s="54"/>
+      <c r="AF3" s="54"/>
       <c r="AG3" s="6" t="s">
         <v>32</v>
       </c>
@@ -26637,7 +26637,7 @@
       <c r="AK3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL3" s="42"/>
+      <c r="AL3" s="54"/>
     </row>
     <row r="4" spans="1:38">
       <c r="A4" s="24">
@@ -26677,17 +26677,17 @@
       <c r="O4" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="P4" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R4" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="20" t="s">
-        <v>1</v>
+      <c r="P4" s="20">
+        <v>6.3</v>
+      </c>
+      <c r="Q4" s="20">
+        <v>23.73</v>
+      </c>
+      <c r="R4" s="20">
+        <v>40.79</v>
+      </c>
+      <c r="S4" s="20">
+        <v>3833</v>
       </c>
       <c r="T4" s="7">
         <v>21.3</v>
@@ -26699,7 +26699,7 @@
         <v>34.26</v>
       </c>
       <c r="W4" s="7">
-        <v>24.5</v>
+        <v>24.51</v>
       </c>
       <c r="X4" s="26">
         <v>3219</v>
@@ -26785,17 +26785,17 @@
       <c r="O5" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="P5" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R5" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="20" t="s">
-        <v>1</v>
+      <c r="P5" s="20">
+        <v>7.95</v>
+      </c>
+      <c r="Q5" s="20">
+        <v>27.11</v>
+      </c>
+      <c r="R5" s="20">
+        <v>37.950000000000003</v>
+      </c>
+      <c r="S5" s="20">
+        <v>3885</v>
       </c>
       <c r="T5" s="7">
         <v>21.34</v>
@@ -26893,17 +26893,17 @@
       <c r="O6" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R6" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="20" t="s">
-        <v>1</v>
+      <c r="P6" s="20">
+        <v>6.48</v>
+      </c>
+      <c r="Q6" s="20">
+        <v>22.25</v>
+      </c>
+      <c r="R6" s="20">
+        <v>41.24</v>
+      </c>
+      <c r="S6" s="20">
+        <v>3857</v>
       </c>
       <c r="T6" s="7">
         <v>23.67</v>
@@ -27001,17 +27001,17 @@
       <c r="O7" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="P7" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R7" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="20" t="s">
-        <v>1</v>
+      <c r="P7" s="20">
+        <v>6.62</v>
+      </c>
+      <c r="Q7" s="20">
+        <v>21.09</v>
+      </c>
+      <c r="R7" s="20">
+        <v>44.32</v>
+      </c>
+      <c r="S7" s="20">
+        <v>3517</v>
       </c>
       <c r="T7" s="7">
         <v>22.39</v>
@@ -27020,10 +27020,10 @@
         <v>17.53</v>
       </c>
       <c r="V7" s="7">
-        <v>36.83</v>
+        <v>36.840000000000003</v>
       </c>
       <c r="W7" s="7">
-        <v>23.25</v>
+        <v>23.24</v>
       </c>
       <c r="X7" s="26">
         <v>2923</v>
@@ -27109,17 +27109,17 @@
       <c r="O8" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="P8" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R8" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="S8" s="20" t="s">
-        <v>1</v>
+      <c r="P8" s="20">
+        <v>6.45</v>
+      </c>
+      <c r="Q8" s="20">
+        <v>21.39</v>
+      </c>
+      <c r="R8" s="20">
+        <v>42.88</v>
+      </c>
+      <c r="S8" s="20">
+        <v>3558</v>
       </c>
       <c r="T8" s="7">
         <v>21.88</v>
@@ -27128,10 +27128,10 @@
         <v>17.86</v>
       </c>
       <c r="V8" s="7">
-        <v>35.799999999999997</v>
+        <v>35.81</v>
       </c>
       <c r="W8" s="7">
-        <v>24.46</v>
+        <v>24.45</v>
       </c>
       <c r="X8" s="26">
         <v>2971</v>
@@ -27217,17 +27217,17 @@
       <c r="O9" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="P9" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R9" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="S9" s="20" t="s">
-        <v>1</v>
+      <c r="P9" s="20">
+        <v>6.57</v>
+      </c>
+      <c r="Q9" s="20">
+        <v>22.92</v>
+      </c>
+      <c r="R9" s="20">
+        <v>40.26</v>
+      </c>
+      <c r="S9" s="20">
+        <v>3770</v>
       </c>
       <c r="T9" s="7">
         <v>23.36</v>
@@ -27236,13 +27236,13 @@
         <v>18.8</v>
       </c>
       <c r="V9" s="7">
-        <v>33.020000000000003</v>
+        <v>33.03</v>
       </c>
       <c r="W9" s="7">
-        <v>24.82</v>
+        <v>24.81</v>
       </c>
       <c r="X9" s="26">
-        <v>3092</v>
+        <v>3093</v>
       </c>
       <c r="Y9" s="26" t="s">
         <v>1</v>
@@ -27325,18 +27325,10 @@
       <c r="O10" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="P10" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R10" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="S10" s="20" t="s">
-        <v>1</v>
-      </c>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
       <c r="T10" s="7">
         <v>23.63</v>
       </c>
@@ -27435,11 +27427,21 @@
       <c r="Q11" s="20"/>
       <c r="R11" s="20"/>
       <c r="S11" s="20"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="26"/>
+      <c r="T11" s="7">
+        <v>22.47</v>
+      </c>
+      <c r="U11" s="7">
+        <v>20.77</v>
+      </c>
+      <c r="V11" s="7">
+        <v>30.13</v>
+      </c>
+      <c r="W11" s="7">
+        <v>26.62</v>
+      </c>
+      <c r="X11" s="26">
+        <v>3348</v>
+      </c>
       <c r="Y11" s="26"/>
       <c r="Z11" s="27"/>
       <c r="AA11" s="27"/>
@@ -27495,11 +27497,21 @@
       <c r="Q12" s="20"/>
       <c r="R12" s="20"/>
       <c r="S12" s="20"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="26"/>
+      <c r="T12" s="7">
+        <v>21.32</v>
+      </c>
+      <c r="U12" s="7">
+        <v>20.190000000000001</v>
+      </c>
+      <c r="V12" s="7">
+        <v>37.729999999999997</v>
+      </c>
+      <c r="W12" s="7">
+        <v>20.76</v>
+      </c>
+      <c r="X12" s="26">
+        <v>2872</v>
+      </c>
       <c r="Y12" s="26"/>
       <c r="Z12" s="27"/>
       <c r="AA12" s="27"/>
@@ -27547,20 +27559,29 @@
       <c r="M13" s="20">
         <v>3389.7</v>
       </c>
-      <c r="N13" s="35">
-        <f>M13</f>
-        <v>3389.7</v>
+      <c r="N13" s="20">
+        <v>3326.68</v>
       </c>
       <c r="O13" s="20"/>
       <c r="P13" s="20"/>
       <c r="Q13" s="20"/>
       <c r="R13" s="20"/>
       <c r="S13" s="20"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="26"/>
+      <c r="T13" s="7">
+        <v>22.88</v>
+      </c>
+      <c r="U13" s="7">
+        <v>24.15</v>
+      </c>
+      <c r="V13" s="7">
+        <v>21.69</v>
+      </c>
+      <c r="W13" s="7">
+        <v>31.28</v>
+      </c>
+      <c r="X13" s="26">
+        <v>4140</v>
+      </c>
       <c r="Y13" s="26"/>
       <c r="Z13" s="27"/>
       <c r="AA13" s="27"/>
@@ -27616,11 +27637,21 @@
       <c r="Q14" s="20"/>
       <c r="R14" s="20"/>
       <c r="S14" s="20"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="7"/>
-      <c r="X14" s="26"/>
+      <c r="T14" s="7">
+        <v>19.510000000000002</v>
+      </c>
+      <c r="U14" s="7">
+        <v>22.66</v>
+      </c>
+      <c r="V14" s="7">
+        <v>32.79</v>
+      </c>
+      <c r="W14" s="7">
+        <v>25.04</v>
+      </c>
+      <c r="X14" s="26">
+        <v>3150</v>
+      </c>
       <c r="Y14" s="26"/>
       <c r="Z14" s="27"/>
       <c r="AA14" s="27"/>
@@ -27676,11 +27707,21 @@
       <c r="Q15" s="20"/>
       <c r="R15" s="20"/>
       <c r="S15" s="20"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="7"/>
-      <c r="X15" s="26"/>
+      <c r="T15" s="7">
+        <v>19.71</v>
+      </c>
+      <c r="U15" s="7">
+        <v>20.86</v>
+      </c>
+      <c r="V15" s="7">
+        <v>38.86</v>
+      </c>
+      <c r="W15" s="7">
+        <v>20.57</v>
+      </c>
+      <c r="X15" s="26">
+        <v>2920</v>
+      </c>
       <c r="Y15" s="26"/>
       <c r="Z15" s="27"/>
       <c r="AA15" s="27"/>
@@ -27736,11 +27777,21 @@
       <c r="Q16" s="20"/>
       <c r="R16" s="20"/>
       <c r="S16" s="20"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="X16" s="26"/>
+      <c r="T16" s="7">
+        <v>21.08</v>
+      </c>
+      <c r="U16" s="7">
+        <v>20.79</v>
+      </c>
+      <c r="V16" s="7">
+        <v>37.54</v>
+      </c>
+      <c r="W16" s="7">
+        <v>20.58</v>
+      </c>
+      <c r="X16" s="26">
+        <v>2924</v>
+      </c>
       <c r="Y16" s="26"/>
       <c r="Z16" s="27"/>
       <c r="AA16" s="27"/>
@@ -27756,6 +27807,999 @@
       <c r="AK16" s="29"/>
       <c r="AL16" s="20"/>
     </row>
+    <row r="17" spans="1:38">
+      <c r="A17" s="24">
+        <v>14</v>
+      </c>
+      <c r="B17" s="20">
+        <v>16670</v>
+      </c>
+      <c r="C17" s="25">
+        <v>46273</v>
+      </c>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J17" s="20">
+        <v>162011752</v>
+      </c>
+      <c r="K17" s="25">
+        <v>46271</v>
+      </c>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20">
+        <v>3939.1</v>
+      </c>
+      <c r="N17" s="20">
+        <v>3957.8</v>
+      </c>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="7">
+        <v>22.84</v>
+      </c>
+      <c r="U17" s="7">
+        <v>24.37</v>
+      </c>
+      <c r="V17" s="7">
+        <v>20.34</v>
+      </c>
+      <c r="W17" s="7">
+        <v>32.450000000000003</v>
+      </c>
+      <c r="X17" s="26">
+        <v>4236</v>
+      </c>
+      <c r="Y17" s="26"/>
+      <c r="Z17" s="27"/>
+      <c r="AA17" s="27"/>
+      <c r="AB17" s="27"/>
+      <c r="AC17" s="27"/>
+      <c r="AD17" s="27"/>
+      <c r="AE17" s="27"/>
+      <c r="AF17" s="28"/>
+      <c r="AG17" s="27"/>
+      <c r="AH17" s="29"/>
+      <c r="AI17" s="29"/>
+      <c r="AJ17" s="29"/>
+      <c r="AK17" s="29"/>
+      <c r="AL17" s="20"/>
+    </row>
+    <row r="18" spans="1:38">
+      <c r="A18" s="24">
+        <v>15</v>
+      </c>
+      <c r="B18" s="20">
+        <v>16671</v>
+      </c>
+      <c r="C18" s="25">
+        <v>46273</v>
+      </c>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J18" s="20">
+        <v>162004436</v>
+      </c>
+      <c r="K18" s="25">
+        <v>46272</v>
+      </c>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20">
+        <v>4009.6</v>
+      </c>
+      <c r="N18" s="20">
+        <v>3977.6</v>
+      </c>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="7">
+        <v>21.34</v>
+      </c>
+      <c r="U18" s="7">
+        <v>21.17</v>
+      </c>
+      <c r="V18" s="7">
+        <v>30.49</v>
+      </c>
+      <c r="W18" s="7">
+        <v>27</v>
+      </c>
+      <c r="X18" s="26">
+        <v>3544</v>
+      </c>
+      <c r="Y18" s="26"/>
+      <c r="Z18" s="27"/>
+      <c r="AA18" s="27"/>
+      <c r="AB18" s="27"/>
+      <c r="AC18" s="27"/>
+      <c r="AD18" s="27"/>
+      <c r="AE18" s="27"/>
+      <c r="AF18" s="28"/>
+      <c r="AG18" s="27"/>
+      <c r="AH18" s="29"/>
+      <c r="AI18" s="29"/>
+      <c r="AJ18" s="29"/>
+      <c r="AK18" s="29"/>
+      <c r="AL18" s="20"/>
+    </row>
+    <row r="19" spans="1:38">
+      <c r="A19" s="24">
+        <v>16</v>
+      </c>
+      <c r="B19" s="20">
+        <v>16672</v>
+      </c>
+      <c r="C19" s="25">
+        <v>46273</v>
+      </c>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J19" s="20">
+        <v>162004437</v>
+      </c>
+      <c r="K19" s="25">
+        <v>46272</v>
+      </c>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20">
+        <v>4110.2</v>
+      </c>
+      <c r="N19" s="20">
+        <v>4005.6</v>
+      </c>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="20"/>
+      <c r="T19" s="7">
+        <v>20.14</v>
+      </c>
+      <c r="U19" s="7">
+        <v>20.77</v>
+      </c>
+      <c r="V19" s="7">
+        <v>36.75</v>
+      </c>
+      <c r="W19" s="7">
+        <v>22.34</v>
+      </c>
+      <c r="X19" s="26">
+        <v>3058</v>
+      </c>
+      <c r="Y19" s="26"/>
+      <c r="Z19" s="27"/>
+      <c r="AA19" s="27"/>
+      <c r="AB19" s="27"/>
+      <c r="AC19" s="27"/>
+      <c r="AD19" s="27"/>
+      <c r="AE19" s="27"/>
+      <c r="AF19" s="28"/>
+      <c r="AG19" s="27"/>
+      <c r="AH19" s="29"/>
+      <c r="AI19" s="29"/>
+      <c r="AJ19" s="29"/>
+      <c r="AK19" s="29"/>
+      <c r="AL19" s="20"/>
+    </row>
+    <row r="20" spans="1:38">
+      <c r="A20" s="24">
+        <v>17</v>
+      </c>
+      <c r="B20" s="20">
+        <v>16673</v>
+      </c>
+      <c r="C20" s="25">
+        <v>46273</v>
+      </c>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J20" s="20">
+        <v>162011753</v>
+      </c>
+      <c r="K20" s="25">
+        <v>46272</v>
+      </c>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20">
+        <v>3786.1</v>
+      </c>
+      <c r="N20" s="20">
+        <v>3840.4</v>
+      </c>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="7">
+        <v>20.14</v>
+      </c>
+      <c r="U20" s="7">
+        <v>19.07</v>
+      </c>
+      <c r="V20" s="7">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="W20" s="7">
+        <v>20.59</v>
+      </c>
+      <c r="X20" s="26">
+        <v>2822</v>
+      </c>
+      <c r="Y20" s="26"/>
+      <c r="Z20" s="27"/>
+      <c r="AA20" s="27"/>
+      <c r="AB20" s="27"/>
+      <c r="AC20" s="27"/>
+      <c r="AD20" s="27"/>
+      <c r="AE20" s="27"/>
+      <c r="AF20" s="28"/>
+      <c r="AG20" s="27"/>
+      <c r="AH20" s="29"/>
+      <c r="AI20" s="29"/>
+      <c r="AJ20" s="29"/>
+      <c r="AK20" s="29"/>
+      <c r="AL20" s="20"/>
+    </row>
+    <row r="21" spans="1:38">
+      <c r="A21" s="24">
+        <v>18</v>
+      </c>
+      <c r="B21" s="20">
+        <v>16674</v>
+      </c>
+      <c r="C21" s="25">
+        <v>46273</v>
+      </c>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J21" s="20">
+        <v>162006507</v>
+      </c>
+      <c r="K21" s="25">
+        <v>46272</v>
+      </c>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20">
+        <v>4110.8</v>
+      </c>
+      <c r="N21" s="20">
+        <v>4013</v>
+      </c>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="7">
+        <v>20.29</v>
+      </c>
+      <c r="U21" s="7">
+        <v>20.68</v>
+      </c>
+      <c r="V21" s="7">
+        <v>38.64</v>
+      </c>
+      <c r="W21" s="7">
+        <v>20.39</v>
+      </c>
+      <c r="X21" s="26">
+        <v>2820</v>
+      </c>
+      <c r="Y21" s="26"/>
+      <c r="Z21" s="27"/>
+      <c r="AA21" s="27"/>
+      <c r="AB21" s="27"/>
+      <c r="AC21" s="27"/>
+      <c r="AD21" s="27"/>
+      <c r="AE21" s="27"/>
+      <c r="AF21" s="28"/>
+      <c r="AG21" s="27"/>
+      <c r="AH21" s="29"/>
+      <c r="AI21" s="29"/>
+      <c r="AJ21" s="29"/>
+      <c r="AK21" s="29"/>
+      <c r="AL21" s="20"/>
+    </row>
+    <row r="22" spans="1:38">
+      <c r="A22" s="24">
+        <v>19</v>
+      </c>
+      <c r="B22" s="20">
+        <v>16675</v>
+      </c>
+      <c r="C22" s="25">
+        <v>46273</v>
+      </c>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J22" s="20">
+        <v>162011755</v>
+      </c>
+      <c r="K22" s="25">
+        <v>46272</v>
+      </c>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20">
+        <v>3944.8</v>
+      </c>
+      <c r="N22" s="35">
+        <f>M22</f>
+        <v>3944.8</v>
+      </c>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="20"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="7">
+        <v>22.63</v>
+      </c>
+      <c r="U22" s="7">
+        <v>22.15</v>
+      </c>
+      <c r="V22" s="7">
+        <v>25.97</v>
+      </c>
+      <c r="W22" s="7">
+        <v>29.24</v>
+      </c>
+      <c r="X22" s="26">
+        <v>3818</v>
+      </c>
+      <c r="Y22" s="26"/>
+      <c r="Z22" s="27"/>
+      <c r="AA22" s="27"/>
+      <c r="AB22" s="27"/>
+      <c r="AC22" s="27"/>
+      <c r="AD22" s="27"/>
+      <c r="AE22" s="27"/>
+      <c r="AF22" s="28"/>
+      <c r="AG22" s="27"/>
+      <c r="AH22" s="29"/>
+      <c r="AI22" s="29"/>
+      <c r="AJ22" s="29"/>
+      <c r="AK22" s="29"/>
+      <c r="AL22" s="20"/>
+    </row>
+    <row r="23" spans="1:38">
+      <c r="A23" s="24">
+        <v>20</v>
+      </c>
+      <c r="B23" s="20">
+        <v>16676</v>
+      </c>
+      <c r="C23" s="25">
+        <v>46274</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J23" s="20">
+        <v>162006512</v>
+      </c>
+      <c r="K23" s="25">
+        <v>46273</v>
+      </c>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20">
+        <v>4061.4</v>
+      </c>
+      <c r="N23" s="20">
+        <v>3998.4</v>
+      </c>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="7">
+        <v>19.46</v>
+      </c>
+      <c r="U23" s="7">
+        <v>20.94</v>
+      </c>
+      <c r="V23" s="7">
+        <v>38.94</v>
+      </c>
+      <c r="W23" s="7">
+        <v>20.66</v>
+      </c>
+      <c r="X23" s="26">
+        <v>2861</v>
+      </c>
+      <c r="Y23" s="26"/>
+      <c r="Z23" s="27"/>
+      <c r="AA23" s="27"/>
+      <c r="AB23" s="27"/>
+      <c r="AC23" s="27"/>
+      <c r="AD23" s="27"/>
+      <c r="AE23" s="27"/>
+      <c r="AF23" s="28"/>
+      <c r="AG23" s="27"/>
+      <c r="AH23" s="29"/>
+      <c r="AI23" s="29"/>
+      <c r="AJ23" s="29"/>
+      <c r="AK23" s="29"/>
+      <c r="AL23" s="20"/>
+    </row>
+    <row r="24" spans="1:38">
+      <c r="A24" s="24">
+        <v>21</v>
+      </c>
+      <c r="B24" s="20">
+        <v>16677</v>
+      </c>
+      <c r="C24" s="25">
+        <v>46274</v>
+      </c>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J24" s="20">
+        <v>162004438</v>
+      </c>
+      <c r="K24" s="25">
+        <v>46273</v>
+      </c>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20">
+        <v>3896</v>
+      </c>
+      <c r="N24" s="20">
+        <v>3744.8</v>
+      </c>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="7">
+        <v>21.71</v>
+      </c>
+      <c r="U24" s="7">
+        <v>21.65</v>
+      </c>
+      <c r="V24" s="7">
+        <v>32.630000000000003</v>
+      </c>
+      <c r="W24" s="7">
+        <v>24.01</v>
+      </c>
+      <c r="X24" s="26">
+        <v>3257</v>
+      </c>
+      <c r="Y24" s="26"/>
+      <c r="Z24" s="27"/>
+      <c r="AA24" s="27"/>
+      <c r="AB24" s="27"/>
+      <c r="AC24" s="27"/>
+      <c r="AD24" s="27"/>
+      <c r="AE24" s="27"/>
+      <c r="AF24" s="28"/>
+      <c r="AG24" s="27"/>
+      <c r="AH24" s="29"/>
+      <c r="AI24" s="29"/>
+      <c r="AJ24" s="29"/>
+      <c r="AK24" s="29"/>
+      <c r="AL24" s="20"/>
+    </row>
+    <row r="25" spans="1:38">
+      <c r="A25" s="24">
+        <v>22</v>
+      </c>
+      <c r="B25" s="20">
+        <v>16679</v>
+      </c>
+      <c r="C25" s="25">
+        <v>46275</v>
+      </c>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J25" s="20">
+        <v>162003248</v>
+      </c>
+      <c r="K25" s="25">
+        <v>46274</v>
+      </c>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20">
+        <v>3480.7</v>
+      </c>
+      <c r="N25" s="20">
+        <v>3419.8</v>
+      </c>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="20"/>
+      <c r="S25" s="20"/>
+      <c r="T25" s="7">
+        <v>20.48</v>
+      </c>
+      <c r="U25" s="7">
+        <v>21.45</v>
+      </c>
+      <c r="V25" s="7">
+        <v>39.11</v>
+      </c>
+      <c r="W25" s="7">
+        <v>18.96</v>
+      </c>
+      <c r="X25" s="26">
+        <v>2834</v>
+      </c>
+      <c r="Y25" s="26"/>
+      <c r="Z25" s="27"/>
+      <c r="AA25" s="27"/>
+      <c r="AB25" s="27"/>
+      <c r="AC25" s="27"/>
+      <c r="AD25" s="27"/>
+      <c r="AE25" s="27"/>
+      <c r="AF25" s="28"/>
+      <c r="AG25" s="27"/>
+      <c r="AH25" s="29"/>
+      <c r="AI25" s="29"/>
+      <c r="AJ25" s="29"/>
+      <c r="AK25" s="29"/>
+      <c r="AL25" s="20"/>
+    </row>
+    <row r="26" spans="1:38">
+      <c r="A26" s="24">
+        <v>23</v>
+      </c>
+      <c r="B26" s="20">
+        <v>16680</v>
+      </c>
+      <c r="C26" s="25">
+        <v>46275</v>
+      </c>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J26" s="20">
+        <v>162006519</v>
+      </c>
+      <c r="K26" s="25">
+        <v>46274</v>
+      </c>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20">
+        <v>4051.3</v>
+      </c>
+      <c r="N26" s="20">
+        <f>M26</f>
+        <v>4051.3</v>
+      </c>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20"/>
+      <c r="R26" s="20"/>
+      <c r="S26" s="20"/>
+      <c r="T26" s="7"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="7"/>
+      <c r="W26" s="7"/>
+      <c r="X26" s="26"/>
+      <c r="Y26" s="26"/>
+      <c r="Z26" s="27"/>
+      <c r="AA26" s="27"/>
+      <c r="AB26" s="27"/>
+      <c r="AC26" s="27"/>
+      <c r="AD26" s="27"/>
+      <c r="AE26" s="27"/>
+      <c r="AF26" s="28"/>
+      <c r="AG26" s="27"/>
+      <c r="AH26" s="29"/>
+      <c r="AI26" s="29"/>
+      <c r="AJ26" s="29"/>
+      <c r="AK26" s="29"/>
+      <c r="AL26" s="20"/>
+    </row>
+    <row r="27" spans="1:38">
+      <c r="A27" s="24">
+        <v>24</v>
+      </c>
+      <c r="B27" s="20">
+        <v>16682</v>
+      </c>
+      <c r="C27" s="25">
+        <v>46275</v>
+      </c>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J27" s="20">
+        <v>162011758</v>
+      </c>
+      <c r="K27" s="25">
+        <v>46274</v>
+      </c>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20">
+        <v>3291.7</v>
+      </c>
+      <c r="N27" s="20">
+        <v>3276.2</v>
+      </c>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
+      <c r="R27" s="20"/>
+      <c r="S27" s="20"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="7"/>
+      <c r="X27" s="26"/>
+      <c r="Y27" s="26"/>
+      <c r="Z27" s="27"/>
+      <c r="AA27" s="27"/>
+      <c r="AB27" s="27"/>
+      <c r="AC27" s="27"/>
+      <c r="AD27" s="27"/>
+      <c r="AE27" s="27"/>
+      <c r="AF27" s="28"/>
+      <c r="AG27" s="27"/>
+      <c r="AH27" s="29"/>
+      <c r="AI27" s="29"/>
+      <c r="AJ27" s="29"/>
+      <c r="AK27" s="29"/>
+      <c r="AL27" s="20"/>
+    </row>
+    <row r="28" spans="1:38">
+      <c r="A28" s="24">
+        <v>25</v>
+      </c>
+      <c r="B28" s="20">
+        <v>16683</v>
+      </c>
+      <c r="C28" s="25">
+        <v>46275</v>
+      </c>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J28" s="20">
+        <v>162011756</v>
+      </c>
+      <c r="K28" s="25">
+        <v>46273</v>
+      </c>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20">
+        <v>3394.2</v>
+      </c>
+      <c r="N28" s="20">
+        <v>3398.8</v>
+      </c>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="20"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="7"/>
+      <c r="V28" s="7"/>
+      <c r="W28" s="7"/>
+      <c r="X28" s="26"/>
+      <c r="Y28" s="26"/>
+      <c r="Z28" s="27"/>
+      <c r="AA28" s="27"/>
+      <c r="AB28" s="27"/>
+      <c r="AC28" s="27"/>
+      <c r="AD28" s="27"/>
+      <c r="AE28" s="27"/>
+      <c r="AF28" s="28"/>
+      <c r="AG28" s="27"/>
+      <c r="AH28" s="29"/>
+      <c r="AI28" s="29"/>
+      <c r="AJ28" s="29"/>
+      <c r="AK28" s="29"/>
+      <c r="AL28" s="20"/>
+    </row>
+    <row r="29" spans="1:38">
+      <c r="A29" s="24">
+        <v>26</v>
+      </c>
+      <c r="B29" s="20">
+        <v>16685</v>
+      </c>
+      <c r="C29" s="25">
+        <v>46276</v>
+      </c>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J29" s="20">
+        <v>162004440</v>
+      </c>
+      <c r="K29" s="25">
+        <v>46274</v>
+      </c>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20">
+        <v>3974.7</v>
+      </c>
+      <c r="N29" s="20">
+        <v>3864.2</v>
+      </c>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="20"/>
+      <c r="T29" s="7"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="7"/>
+      <c r="W29" s="7"/>
+      <c r="X29" s="26"/>
+      <c r="Y29" s="26"/>
+      <c r="Z29" s="27"/>
+      <c r="AA29" s="27"/>
+      <c r="AB29" s="27"/>
+      <c r="AC29" s="27"/>
+      <c r="AD29" s="27"/>
+      <c r="AE29" s="27"/>
+      <c r="AF29" s="28"/>
+      <c r="AG29" s="27"/>
+      <c r="AH29" s="29"/>
+      <c r="AI29" s="29"/>
+      <c r="AJ29" s="29"/>
+      <c r="AK29" s="29"/>
+      <c r="AL29" s="20"/>
+    </row>
+    <row r="30" spans="1:38">
+      <c r="A30" s="24">
+        <v>27</v>
+      </c>
+      <c r="B30" s="20">
+        <v>16687</v>
+      </c>
+      <c r="C30" s="25">
+        <v>46276</v>
+      </c>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J30" s="20">
+        <v>162001479</v>
+      </c>
+      <c r="K30" s="25">
+        <v>46274</v>
+      </c>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20">
+        <v>3750.7</v>
+      </c>
+      <c r="N30" s="20">
+        <v>3861.8</v>
+      </c>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="20"/>
+      <c r="S30" s="20"/>
+      <c r="T30" s="7"/>
+      <c r="U30" s="7"/>
+      <c r="V30" s="7"/>
+      <c r="W30" s="7"/>
+      <c r="X30" s="26"/>
+      <c r="Y30" s="26"/>
+      <c r="Z30" s="27"/>
+      <c r="AA30" s="27"/>
+      <c r="AB30" s="27"/>
+      <c r="AC30" s="27"/>
+      <c r="AD30" s="27"/>
+      <c r="AE30" s="27"/>
+      <c r="AF30" s="28"/>
+      <c r="AG30" s="27"/>
+      <c r="AH30" s="29"/>
+      <c r="AI30" s="29"/>
+      <c r="AJ30" s="29"/>
+      <c r="AK30" s="29"/>
+      <c r="AL30" s="20"/>
+    </row>
+    <row r="31" spans="1:38">
+      <c r="A31" s="24">
+        <v>28</v>
+      </c>
+      <c r="B31" s="20">
+        <v>16690</v>
+      </c>
+      <c r="C31" s="25">
+        <v>46276</v>
+      </c>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J31" s="20">
+        <v>162011760</v>
+      </c>
+      <c r="K31" s="25">
+        <v>46275</v>
+      </c>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20">
+        <v>3712.6</v>
+      </c>
+      <c r="N31" s="20">
+        <f>M31</f>
+        <v>3712.6</v>
+      </c>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+      <c r="R31" s="20"/>
+      <c r="S31" s="20"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7"/>
+      <c r="X31" s="26"/>
+      <c r="Y31" s="26"/>
+      <c r="Z31" s="27"/>
+      <c r="AA31" s="27"/>
+      <c r="AB31" s="27"/>
+      <c r="AC31" s="27"/>
+      <c r="AD31" s="27"/>
+      <c r="AE31" s="27"/>
+      <c r="AF31" s="28"/>
+      <c r="AG31" s="27"/>
+      <c r="AH31" s="29"/>
+      <c r="AI31" s="29"/>
+      <c r="AJ31" s="29"/>
+      <c r="AK31" s="29"/>
+      <c r="AL31" s="20"/>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="AL1:AL3"/>

--- a/Quality.xlsx
+++ b/Quality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30516"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ppgclindia-my.sharepoint.com/personal/bikram_mohapatra_ppgcl_co_in/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{826187C2-81AF-4FE5-9A89-100E910FC15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7BD2DF1-5611-40CD-9F88-A5964EB79A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JULY-26" sheetId="11" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1942" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2053" uniqueCount="56">
   <si>
     <t>IGI Report</t>
   </si>
@@ -234,7 +234,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -299,6 +299,24 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -550,7 +568,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -669,14 +687,41 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -684,7 +729,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -708,17 +753,23 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1063,21 +1114,21 @@
       <c r="U1" s="13"/>
       <c r="V1" s="13"/>
       <c r="W1" s="13"/>
-      <c r="X1" s="40" t="s">
+      <c r="X1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="41"/>
-      <c r="AB1" s="41"/>
-      <c r="AC1" s="41"/>
-      <c r="AD1" s="41"/>
-      <c r="AE1" s="41"/>
-      <c r="AF1" s="41"/>
-      <c r="AG1" s="41"/>
-      <c r="AH1" s="41"/>
-      <c r="AI1" s="41"/>
-      <c r="AJ1" s="42"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
+      <c r="AH1" s="63"/>
+      <c r="AI1" s="63"/>
+      <c r="AJ1" s="64"/>
     </row>
     <row r="2" spans="1:36" ht="15" customHeight="1">
       <c r="A2" s="15"/>
@@ -1095,43 +1146,43 @@
       <c r="M2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="43" t="s">
+      <c r="N2" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="44"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="53"/>
       <c r="W2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="45" t="s">
+      <c r="X2" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="Y2" s="47" t="s">
+      <c r="Y2" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="Z2" s="48"/>
-      <c r="AA2" s="48"/>
-      <c r="AB2" s="49"/>
-      <c r="AC2" s="53" t="s">
+      <c r="Z2" s="57"/>
+      <c r="AA2" s="57"/>
+      <c r="AB2" s="58"/>
+      <c r="AC2" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AD2" s="53" t="s">
+      <c r="AD2" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="47" t="s">
+      <c r="AE2" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="AF2" s="48"/>
-      <c r="AG2" s="48"/>
-      <c r="AH2" s="48"/>
-      <c r="AI2" s="49"/>
-      <c r="AJ2" s="53" t="s">
+      <c r="AF2" s="57"/>
+      <c r="AG2" s="57"/>
+      <c r="AH2" s="57"/>
+      <c r="AI2" s="58"/>
+      <c r="AJ2" s="50" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1205,19 +1256,19 @@
       <c r="W3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="X3" s="46"/>
-      <c r="Y3" s="50"/>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
-      <c r="AB3" s="52"/>
-      <c r="AC3" s="53"/>
-      <c r="AD3" s="53"/>
-      <c r="AE3" s="50"/>
-      <c r="AF3" s="51"/>
-      <c r="AG3" s="51"/>
-      <c r="AH3" s="51"/>
-      <c r="AI3" s="52"/>
-      <c r="AJ3" s="53"/>
+      <c r="X3" s="55"/>
+      <c r="Y3" s="59"/>
+      <c r="Z3" s="60"/>
+      <c r="AA3" s="60"/>
+      <c r="AB3" s="61"/>
+      <c r="AC3" s="50"/>
+      <c r="AD3" s="50"/>
+      <c r="AE3" s="59"/>
+      <c r="AF3" s="60"/>
+      <c r="AG3" s="60"/>
+      <c r="AH3" s="60"/>
+      <c r="AI3" s="61"/>
+      <c r="AJ3" s="50"/>
     </row>
     <row r="4" spans="1:36" ht="60.75">
       <c r="A4" s="11" t="s">
@@ -1304,8 +1355,8 @@
       <c r="AB4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AC4" s="54"/>
-      <c r="AD4" s="54"/>
+      <c r="AC4" s="51"/>
+      <c r="AD4" s="51"/>
       <c r="AE4" s="6" t="s">
         <v>32</v>
       </c>
@@ -1321,7 +1372,7 @@
       <c r="AI4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AJ4" s="54"/>
+      <c r="AJ4" s="51"/>
     </row>
     <row r="5" spans="1:36">
       <c r="A5" s="24">
@@ -14456,21 +14507,21 @@
       <c r="U1" s="13"/>
       <c r="V1" s="13"/>
       <c r="W1" s="13"/>
-      <c r="X1" s="40" t="s">
+      <c r="X1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="41"/>
-      <c r="AB1" s="41"/>
-      <c r="AC1" s="41"/>
-      <c r="AD1" s="41"/>
-      <c r="AE1" s="41"/>
-      <c r="AF1" s="41"/>
-      <c r="AG1" s="41"/>
-      <c r="AH1" s="41"/>
-      <c r="AI1" s="41"/>
-      <c r="AJ1" s="42"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
+      <c r="AH1" s="63"/>
+      <c r="AI1" s="63"/>
+      <c r="AJ1" s="64"/>
     </row>
     <row r="2" spans="1:36" ht="15.75" customHeight="1">
       <c r="A2" s="15"/>
@@ -14486,43 +14537,43 @@
       <c r="K2" s="31"/>
       <c r="L2" s="16"/>
       <c r="M2" s="17"/>
-      <c r="N2" s="43" t="s">
+      <c r="N2" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="44"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="53"/>
       <c r="W2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="45" t="s">
+      <c r="X2" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="Y2" s="47" t="s">
+      <c r="Y2" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="Z2" s="48"/>
-      <c r="AA2" s="48"/>
-      <c r="AB2" s="49"/>
-      <c r="AC2" s="53" t="s">
+      <c r="Z2" s="57"/>
+      <c r="AA2" s="57"/>
+      <c r="AB2" s="58"/>
+      <c r="AC2" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AD2" s="53" t="s">
+      <c r="AD2" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="47" t="s">
+      <c r="AE2" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="AF2" s="48"/>
-      <c r="AG2" s="48"/>
-      <c r="AH2" s="48"/>
-      <c r="AI2" s="49"/>
-      <c r="AJ2" s="53" t="s">
+      <c r="AF2" s="57"/>
+      <c r="AG2" s="57"/>
+      <c r="AH2" s="57"/>
+      <c r="AI2" s="58"/>
+      <c r="AJ2" s="50" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14570,19 +14621,19 @@
       <c r="W3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="X3" s="46"/>
-      <c r="Y3" s="50"/>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
-      <c r="AB3" s="52"/>
-      <c r="AC3" s="53"/>
-      <c r="AD3" s="53"/>
-      <c r="AE3" s="50"/>
-      <c r="AF3" s="51"/>
-      <c r="AG3" s="51"/>
-      <c r="AH3" s="51"/>
-      <c r="AI3" s="52"/>
-      <c r="AJ3" s="53"/>
+      <c r="X3" s="55"/>
+      <c r="Y3" s="59"/>
+      <c r="Z3" s="60"/>
+      <c r="AA3" s="60"/>
+      <c r="AB3" s="61"/>
+      <c r="AC3" s="50"/>
+      <c r="AD3" s="50"/>
+      <c r="AE3" s="59"/>
+      <c r="AF3" s="60"/>
+      <c r="AG3" s="60"/>
+      <c r="AH3" s="60"/>
+      <c r="AI3" s="61"/>
+      <c r="AJ3" s="50"/>
     </row>
     <row r="4" spans="1:36" ht="60.75">
       <c r="A4" s="11" t="s">
@@ -14669,8 +14720,8 @@
       <c r="AB4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AC4" s="54"/>
-      <c r="AD4" s="54"/>
+      <c r="AC4" s="51"/>
+      <c r="AD4" s="51"/>
       <c r="AE4" s="6" t="s">
         <v>32</v>
       </c>
@@ -14686,7 +14737,7 @@
       <c r="AI4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AJ4" s="54"/>
+      <c r="AJ4" s="51"/>
     </row>
     <row r="5" spans="1:36">
       <c r="A5" s="24">
@@ -26370,7 +26421,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD3CE46B-EBFB-40D5-8B95-D45149ED2B06}">
-  <dimension ref="A1:AL31"/>
+  <dimension ref="A1:AL68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -26429,43 +26480,43 @@
       <c r="O1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="43" t="s">
+      <c r="P1" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
-      <c r="V1" s="43"/>
-      <c r="W1" s="43"/>
-      <c r="X1" s="44"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="52"/>
+      <c r="V1" s="52"/>
+      <c r="W1" s="52"/>
+      <c r="X1" s="53"/>
       <c r="Y1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="Z1" s="56" t="s">
+      <c r="Z1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" s="47" t="s">
+      <c r="AA1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="AB1" s="48"/>
-      <c r="AC1" s="48"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="55" t="s">
+      <c r="AB1" s="57"/>
+      <c r="AC1" s="57"/>
+      <c r="AD1" s="58"/>
+      <c r="AE1" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="55" t="s">
+      <c r="AF1" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="AG1" s="47" t="s">
+      <c r="AG1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="AH1" s="48"/>
-      <c r="AI1" s="48"/>
-      <c r="AJ1" s="48"/>
-      <c r="AK1" s="49"/>
-      <c r="AL1" s="55" t="s">
+      <c r="AH1" s="57"/>
+      <c r="AI1" s="57"/>
+      <c r="AJ1" s="57"/>
+      <c r="AK1" s="58"/>
+      <c r="AL1" s="49" t="s">
         <v>6</v>
       </c>
     </row>
@@ -26517,19 +26568,19 @@
       <c r="Y2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="Z2" s="46"/>
-      <c r="AA2" s="50"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="52"/>
-      <c r="AE2" s="53"/>
-      <c r="AF2" s="53"/>
-      <c r="AG2" s="50"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="52"/>
-      <c r="AL2" s="53"/>
+      <c r="Z2" s="55"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="61"/>
+      <c r="AE2" s="50"/>
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="59"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="61"/>
+      <c r="AL2" s="50"/>
     </row>
     <row r="3" spans="1:38" ht="60.75">
       <c r="A3" s="11" t="s">
@@ -26620,8 +26671,8 @@
       <c r="AD3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AE3" s="54"/>
-      <c r="AF3" s="54"/>
+      <c r="AE3" s="51"/>
+      <c r="AF3" s="51"/>
       <c r="AG3" s="6" t="s">
         <v>32</v>
       </c>
@@ -26637,7 +26688,7 @@
       <c r="AK3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL3" s="54"/>
+      <c r="AL3" s="51"/>
     </row>
     <row r="4" spans="1:38">
       <c r="A4" s="24">
@@ -26671,7 +26722,7 @@
       <c r="M4" s="20">
         <v>3694.6</v>
       </c>
-      <c r="N4" s="20">
+      <c r="N4" s="66">
         <v>3845.8</v>
       </c>
       <c r="O4" s="20" t="s">
@@ -26702,7 +26753,7 @@
         <v>24.51</v>
       </c>
       <c r="X4" s="26">
-        <v>3219</v>
+        <v>3219.39</v>
       </c>
       <c r="Y4" s="26" t="s">
         <v>1</v>
@@ -26779,7 +26830,7 @@
       <c r="M5" s="20">
         <v>3542.7</v>
       </c>
-      <c r="N5" s="20">
+      <c r="N5" s="66">
         <v>3514.2</v>
       </c>
       <c r="O5" s="20" t="s">
@@ -26810,7 +26861,7 @@
         <v>23.06</v>
       </c>
       <c r="X5" s="26">
-        <v>3320</v>
+        <v>3319.87</v>
       </c>
       <c r="Y5" s="26" t="s">
         <v>1</v>
@@ -26887,7 +26938,7 @@
       <c r="M6" s="20">
         <v>3894.1</v>
       </c>
-      <c r="N6" s="20">
+      <c r="N6" s="66">
         <v>3901.4</v>
       </c>
       <c r="O6" s="20" t="s">
@@ -26918,7 +26969,7 @@
         <v>24.51</v>
       </c>
       <c r="X6" s="26">
-        <v>3148</v>
+        <v>3148.04</v>
       </c>
       <c r="Y6" s="26" t="s">
         <v>1</v>
@@ -26995,7 +27046,7 @@
       <c r="M7" s="20">
         <v>4009.9</v>
       </c>
-      <c r="N7" s="20">
+      <c r="N7" s="66">
         <v>4241.8</v>
       </c>
       <c r="O7" s="20" t="s">
@@ -27026,7 +27077,7 @@
         <v>23.24</v>
       </c>
       <c r="X7" s="26">
-        <v>2923</v>
+        <v>2923.05</v>
       </c>
       <c r="Y7" s="26" t="s">
         <v>1</v>
@@ -27103,7 +27154,7 @@
       <c r="M8" s="20">
         <v>3979.7</v>
       </c>
-      <c r="N8" s="20">
+      <c r="N8" s="66">
         <v>3935.8</v>
       </c>
       <c r="O8" s="20" t="s">
@@ -27134,7 +27185,7 @@
         <v>24.45</v>
       </c>
       <c r="X8" s="26">
-        <v>2971</v>
+        <v>2971.15</v>
       </c>
       <c r="Y8" s="26" t="s">
         <v>1</v>
@@ -27211,7 +27262,7 @@
       <c r="M9" s="20">
         <v>3650.5</v>
       </c>
-      <c r="N9" s="20">
+      <c r="N9" s="66">
         <v>3714.4</v>
       </c>
       <c r="O9" s="20" t="s">
@@ -27242,7 +27293,7 @@
         <v>24.81</v>
       </c>
       <c r="X9" s="26">
-        <v>3093</v>
+        <v>3092.51</v>
       </c>
       <c r="Y9" s="26" t="s">
         <v>1</v>
@@ -27319,16 +27370,24 @@
       <c r="M10" s="20">
         <v>3273.8</v>
       </c>
-      <c r="N10" s="20">
+      <c r="N10" s="66">
         <v>3166.6</v>
       </c>
       <c r="O10" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="P10" s="20"/>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="20"/>
-      <c r="S10" s="20"/>
+      <c r="P10" s="20">
+        <v>6.84</v>
+      </c>
+      <c r="Q10" s="20">
+        <v>25.76</v>
+      </c>
+      <c r="R10" s="20">
+        <v>33.479999999999997</v>
+      </c>
+      <c r="S10" s="20">
+        <v>4401</v>
+      </c>
       <c r="T10" s="7">
         <v>23.63</v>
       </c>
@@ -27339,10 +27398,10 @@
         <v>27.45</v>
       </c>
       <c r="W10" s="7">
-        <v>27.81</v>
+        <v>27.8</v>
       </c>
       <c r="X10" s="26">
-        <v>3608</v>
+        <v>3607.82</v>
       </c>
       <c r="Y10" s="26" t="s">
         <v>1</v>
@@ -27419,14 +27478,22 @@
       <c r="M11" s="20">
         <v>4014.4</v>
       </c>
-      <c r="N11" s="20">
+      <c r="N11" s="66">
         <v>4018.4</v>
       </c>
       <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="20"/>
-      <c r="S11" s="20"/>
+      <c r="P11" s="20">
+        <v>7.28</v>
+      </c>
+      <c r="Q11" s="20">
+        <v>24.84</v>
+      </c>
+      <c r="R11" s="20">
+        <v>36.04</v>
+      </c>
+      <c r="S11" s="20">
+        <v>4005</v>
+      </c>
       <c r="T11" s="7">
         <v>22.47</v>
       </c>
@@ -27434,13 +27501,13 @@
         <v>20.77</v>
       </c>
       <c r="V11" s="7">
-        <v>30.13</v>
+        <v>30.14</v>
       </c>
       <c r="W11" s="7">
         <v>26.62</v>
       </c>
       <c r="X11" s="26">
-        <v>3348</v>
+        <v>3348.87</v>
       </c>
       <c r="Y11" s="26"/>
       <c r="Z11" s="27"/>
@@ -27489,14 +27556,22 @@
       <c r="M12" s="20">
         <v>4141.8999999999996</v>
       </c>
-      <c r="N12" s="20">
+      <c r="N12" s="66">
         <v>4098.3999999999996</v>
       </c>
       <c r="O12" s="20"/>
-      <c r="P12" s="20"/>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="20"/>
-      <c r="S12" s="20"/>
+      <c r="P12" s="20">
+        <v>6.62</v>
+      </c>
+      <c r="Q12" s="20">
+        <v>23.96</v>
+      </c>
+      <c r="R12" s="20">
+        <v>44.78</v>
+      </c>
+      <c r="S12" s="20">
+        <v>3409</v>
+      </c>
       <c r="T12" s="7">
         <v>21.32</v>
       </c>
@@ -27510,7 +27585,7 @@
         <v>20.76</v>
       </c>
       <c r="X12" s="26">
-        <v>2872</v>
+        <v>2872.35</v>
       </c>
       <c r="Y12" s="26"/>
       <c r="Z12" s="27"/>
@@ -27559,14 +27634,22 @@
       <c r="M13" s="20">
         <v>3389.7</v>
       </c>
-      <c r="N13" s="20">
+      <c r="N13" s="66">
         <v>3326.68</v>
       </c>
       <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="20"/>
+      <c r="P13" s="20">
+        <v>7.98</v>
+      </c>
+      <c r="Q13" s="20">
+        <v>28.81</v>
+      </c>
+      <c r="R13" s="20">
+        <v>25.88</v>
+      </c>
+      <c r="S13" s="20">
+        <v>4940</v>
+      </c>
       <c r="T13" s="7">
         <v>22.88</v>
       </c>
@@ -27580,7 +27663,7 @@
         <v>31.28</v>
       </c>
       <c r="X13" s="26">
-        <v>4140</v>
+        <v>4140.1099999999997</v>
       </c>
       <c r="Y13" s="26"/>
       <c r="Z13" s="27"/>
@@ -27629,28 +27712,36 @@
       <c r="M14" s="20">
         <v>3923.6</v>
       </c>
-      <c r="N14" s="20">
+      <c r="N14" s="66">
         <v>3786.6</v>
       </c>
       <c r="O14" s="20"/>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="20"/>
-      <c r="S14" s="20"/>
+      <c r="P14" s="20">
+        <v>6.54</v>
+      </c>
+      <c r="Q14" s="20">
+        <v>26.32</v>
+      </c>
+      <c r="R14" s="20">
+        <v>38.08</v>
+      </c>
+      <c r="S14" s="20">
+        <v>3657</v>
+      </c>
       <c r="T14" s="7">
         <v>19.510000000000002</v>
       </c>
       <c r="U14" s="7">
-        <v>22.66</v>
+        <v>22.67</v>
       </c>
       <c r="V14" s="7">
-        <v>32.79</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="W14" s="7">
-        <v>25.04</v>
+        <v>25.02</v>
       </c>
       <c r="X14" s="26">
-        <v>3150</v>
+        <v>3149.5</v>
       </c>
       <c r="Y14" s="26"/>
       <c r="Z14" s="27"/>
@@ -27699,14 +27790,22 @@
       <c r="M15" s="20">
         <v>3714.9</v>
       </c>
-      <c r="N15" s="20">
+      <c r="N15" s="66">
         <v>3665</v>
       </c>
       <c r="O15" s="20"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="20"/>
+      <c r="P15" s="20">
+        <v>6.72</v>
+      </c>
+      <c r="Q15" s="20">
+        <v>24.24</v>
+      </c>
+      <c r="R15" s="20">
+        <v>45.15</v>
+      </c>
+      <c r="S15" s="20">
+        <v>3392</v>
+      </c>
       <c r="T15" s="7">
         <v>19.71</v>
       </c>
@@ -27720,7 +27819,7 @@
         <v>20.57</v>
       </c>
       <c r="X15" s="26">
-        <v>2920</v>
+        <v>2919.64</v>
       </c>
       <c r="Y15" s="26"/>
       <c r="Z15" s="27"/>
@@ -27769,19 +27868,27 @@
       <c r="M16" s="20">
         <v>3711.6</v>
       </c>
-      <c r="N16" s="20">
+      <c r="N16" s="66">
         <v>3669.6</v>
       </c>
       <c r="O16" s="20"/>
-      <c r="P16" s="20"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="20"/>
-      <c r="S16" s="20"/>
+      <c r="P16" s="20">
+        <v>7.1</v>
+      </c>
+      <c r="Q16" s="20">
+        <v>24.48</v>
+      </c>
+      <c r="R16" s="20">
+        <v>44.19</v>
+      </c>
+      <c r="S16" s="20">
+        <v>3441</v>
+      </c>
       <c r="T16" s="7">
         <v>21.08</v>
       </c>
       <c r="U16" s="7">
-        <v>20.79</v>
+        <v>20.8</v>
       </c>
       <c r="V16" s="7">
         <v>37.54</v>
@@ -27790,7 +27897,7 @@
         <v>20.58</v>
       </c>
       <c r="X16" s="26">
-        <v>2924</v>
+        <v>2923.18</v>
       </c>
       <c r="Y16" s="26"/>
       <c r="Z16" s="27"/>
@@ -27839,14 +27946,22 @@
       <c r="M17" s="20">
         <v>3939.1</v>
       </c>
-      <c r="N17" s="20">
+      <c r="N17" s="66">
         <v>3957.8</v>
       </c>
       <c r="O17" s="20"/>
-      <c r="P17" s="20"/>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="20"/>
-      <c r="S17" s="20"/>
+      <c r="P17" s="20">
+        <v>7.82</v>
+      </c>
+      <c r="Q17" s="20">
+        <v>29.11</v>
+      </c>
+      <c r="R17" s="20">
+        <v>24.3</v>
+      </c>
+      <c r="S17" s="20">
+        <v>5061</v>
+      </c>
       <c r="T17" s="7">
         <v>22.84</v>
       </c>
@@ -27860,7 +27975,7 @@
         <v>32.450000000000003</v>
       </c>
       <c r="X17" s="26">
-        <v>4236</v>
+        <v>4236.3500000000004</v>
       </c>
       <c r="Y17" s="26"/>
       <c r="Z17" s="27"/>
@@ -27909,14 +28024,22 @@
       <c r="M18" s="20">
         <v>4009.6</v>
       </c>
-      <c r="N18" s="20">
+      <c r="N18" s="66">
         <v>3977.6</v>
       </c>
       <c r="O18" s="20"/>
-      <c r="P18" s="20"/>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="20"/>
-      <c r="S18" s="20"/>
+      <c r="P18" s="20">
+        <v>6.67</v>
+      </c>
+      <c r="Q18" s="20">
+        <v>25.12</v>
+      </c>
+      <c r="R18" s="20">
+        <v>36.18</v>
+      </c>
+      <c r="S18" s="20">
+        <v>4205</v>
+      </c>
       <c r="T18" s="7">
         <v>21.34</v>
       </c>
@@ -27930,7 +28053,7 @@
         <v>27</v>
       </c>
       <c r="X18" s="26">
-        <v>3544</v>
+        <v>3544.04</v>
       </c>
       <c r="Y18" s="26"/>
       <c r="Z18" s="27"/>
@@ -27979,14 +28102,22 @@
       <c r="M19" s="20">
         <v>4110.2</v>
       </c>
-      <c r="N19" s="20">
+      <c r="N19" s="66">
         <v>4005.6</v>
       </c>
       <c r="O19" s="20"/>
-      <c r="P19" s="20"/>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="20"/>
-      <c r="S19" s="20"/>
+      <c r="P19" s="20">
+        <v>6.59</v>
+      </c>
+      <c r="Q19" s="20">
+        <v>24.29</v>
+      </c>
+      <c r="R19" s="20">
+        <v>42.99</v>
+      </c>
+      <c r="S19" s="20">
+        <v>3576</v>
+      </c>
       <c r="T19" s="7">
         <v>20.14</v>
       </c>
@@ -28000,7 +28131,7 @@
         <v>22.34</v>
       </c>
       <c r="X19" s="26">
-        <v>3058</v>
+        <v>3057.27</v>
       </c>
       <c r="Y19" s="26"/>
       <c r="Z19" s="27"/>
@@ -28049,14 +28180,22 @@
       <c r="M20" s="20">
         <v>3786.1</v>
       </c>
-      <c r="N20" s="20">
+      <c r="N20" s="66">
         <v>3840.4</v>
       </c>
       <c r="O20" s="20"/>
-      <c r="P20" s="20"/>
-      <c r="Q20" s="20"/>
-      <c r="R20" s="20"/>
-      <c r="S20" s="20"/>
+      <c r="P20" s="20">
+        <v>5.96</v>
+      </c>
+      <c r="Q20" s="20">
+        <v>22.46</v>
+      </c>
+      <c r="R20" s="20">
+        <v>47.34</v>
+      </c>
+      <c r="S20" s="20">
+        <v>3323</v>
+      </c>
       <c r="T20" s="7">
         <v>20.14</v>
       </c>
@@ -28070,7 +28209,7 @@
         <v>20.59</v>
       </c>
       <c r="X20" s="26">
-        <v>2822</v>
+        <v>2821.94</v>
       </c>
       <c r="Y20" s="26"/>
       <c r="Z20" s="27"/>
@@ -28119,14 +28258,22 @@
       <c r="M21" s="20">
         <v>4110.8</v>
       </c>
-      <c r="N21" s="20">
+      <c r="N21" s="66">
         <v>4013</v>
       </c>
       <c r="O21" s="20"/>
-      <c r="P21" s="20"/>
-      <c r="Q21" s="20"/>
-      <c r="R21" s="20"/>
-      <c r="S21" s="20"/>
+      <c r="P21" s="20">
+        <v>6.74</v>
+      </c>
+      <c r="Q21" s="20">
+        <v>24.2</v>
+      </c>
+      <c r="R21" s="20">
+        <v>45.21</v>
+      </c>
+      <c r="S21" s="20">
+        <v>3299</v>
+      </c>
       <c r="T21" s="7">
         <v>20.29</v>
       </c>
@@ -28140,7 +28287,7 @@
         <v>20.39</v>
       </c>
       <c r="X21" s="26">
-        <v>2820</v>
+        <v>2819.68</v>
       </c>
       <c r="Y21" s="26"/>
       <c r="Z21" s="27"/>
@@ -28189,15 +28336,22 @@
       <c r="M22" s="20">
         <v>3944.8</v>
       </c>
-      <c r="N22" s="35">
-        <f>M22</f>
-        <v>3944.8</v>
+      <c r="N22" s="66">
+        <v>3904.8</v>
       </c>
       <c r="O22" s="20"/>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
-      <c r="R22" s="20"/>
-      <c r="S22" s="20"/>
+      <c r="P22" s="20">
+        <v>7.48</v>
+      </c>
+      <c r="Q22" s="20">
+        <v>26.49</v>
+      </c>
+      <c r="R22" s="20">
+        <v>31.06</v>
+      </c>
+      <c r="S22" s="20">
+        <v>4565</v>
+      </c>
       <c r="T22" s="7">
         <v>22.63</v>
       </c>
@@ -28208,10 +28362,10 @@
         <v>25.97</v>
       </c>
       <c r="W22" s="7">
-        <v>29.24</v>
+        <v>29.25</v>
       </c>
       <c r="X22" s="26">
-        <v>3818</v>
+        <v>3817.49</v>
       </c>
       <c r="Y22" s="26"/>
       <c r="Z22" s="27"/>
@@ -28260,14 +28414,22 @@
       <c r="M23" s="20">
         <v>4061.4</v>
       </c>
-      <c r="N23" s="20">
+      <c r="N23" s="66">
         <v>3998.4</v>
       </c>
       <c r="O23" s="20"/>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
-      <c r="R23" s="20"/>
-      <c r="S23" s="20"/>
+      <c r="P23" s="20">
+        <v>7.65</v>
+      </c>
+      <c r="Q23" s="20">
+        <v>24.01</v>
+      </c>
+      <c r="R23" s="20">
+        <v>44.65</v>
+      </c>
+      <c r="S23" s="20">
+        <v>3280</v>
+      </c>
       <c r="T23" s="7">
         <v>19.46</v>
       </c>
@@ -28281,7 +28443,7 @@
         <v>20.66</v>
       </c>
       <c r="X23" s="26">
-        <v>2861</v>
+        <v>2860.54</v>
       </c>
       <c r="Y23" s="26"/>
       <c r="Z23" s="27"/>
@@ -28330,14 +28492,22 @@
       <c r="M24" s="20">
         <v>3896</v>
       </c>
-      <c r="N24" s="20">
+      <c r="N24" s="66">
         <v>3744.8</v>
       </c>
       <c r="O24" s="20"/>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
-      <c r="R24" s="20"/>
-      <c r="S24" s="20"/>
+      <c r="P24" s="20">
+        <v>7.2</v>
+      </c>
+      <c r="Q24" s="20">
+        <v>25.66</v>
+      </c>
+      <c r="R24" s="20">
+        <v>38.68</v>
+      </c>
+      <c r="S24" s="20">
+        <v>3861</v>
+      </c>
       <c r="T24" s="7">
         <v>21.71</v>
       </c>
@@ -28351,7 +28521,7 @@
         <v>24.01</v>
       </c>
       <c r="X24" s="26">
-        <v>3257</v>
+        <v>3257.3</v>
       </c>
       <c r="Y24" s="26"/>
       <c r="Z24" s="27"/>
@@ -28400,14 +28570,22 @@
       <c r="M25" s="20">
         <v>3480.7</v>
       </c>
-      <c r="N25" s="20">
+      <c r="N25" s="66">
         <v>3419.8</v>
       </c>
       <c r="O25" s="20"/>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
-      <c r="R25" s="20"/>
-      <c r="S25" s="20"/>
+      <c r="P25" s="20">
+        <v>6.45</v>
+      </c>
+      <c r="Q25" s="20">
+        <v>25.24</v>
+      </c>
+      <c r="R25" s="20">
+        <v>46.01</v>
+      </c>
+      <c r="S25" s="20">
+        <v>3334</v>
+      </c>
       <c r="T25" s="7">
         <v>20.48</v>
       </c>
@@ -28421,7 +28599,7 @@
         <v>18.96</v>
       </c>
       <c r="X25" s="26">
-        <v>2834</v>
+        <v>2833.99</v>
       </c>
       <c r="Y25" s="26"/>
       <c r="Z25" s="27"/>
@@ -28470,20 +28648,37 @@
       <c r="M26" s="20">
         <v>4051.3</v>
       </c>
-      <c r="N26" s="20">
-        <f>M26</f>
-        <v>4051.3</v>
+      <c r="N26" s="66">
+        <v>4031.2</v>
       </c>
       <c r="O26" s="20"/>
-      <c r="P26" s="20"/>
-      <c r="Q26" s="20"/>
-      <c r="R26" s="20"/>
-      <c r="S26" s="20"/>
-      <c r="T26" s="7"/>
-      <c r="U26" s="7"/>
-      <c r="V26" s="7"/>
-      <c r="W26" s="7"/>
-      <c r="X26" s="26"/>
+      <c r="P26" s="20">
+        <v>5.89</v>
+      </c>
+      <c r="Q26" s="20">
+        <v>18.739999999999998</v>
+      </c>
+      <c r="R26" s="20">
+        <v>57.49</v>
+      </c>
+      <c r="S26" s="20">
+        <v>2446</v>
+      </c>
+      <c r="T26" s="7">
+        <v>16.09</v>
+      </c>
+      <c r="U26" s="7">
+        <v>16.71</v>
+      </c>
+      <c r="V26" s="7">
+        <v>51.26</v>
+      </c>
+      <c r="W26" s="7">
+        <v>15.94</v>
+      </c>
+      <c r="X26" s="26">
+        <v>2180.89</v>
+      </c>
       <c r="Y26" s="26"/>
       <c r="Z26" s="27"/>
       <c r="AA26" s="27"/>
@@ -28531,19 +28726,37 @@
       <c r="M27" s="20">
         <v>3291.7</v>
       </c>
-      <c r="N27" s="20">
+      <c r="N27" s="66">
         <v>3276.2</v>
       </c>
       <c r="O27" s="20"/>
-      <c r="P27" s="20"/>
-      <c r="Q27" s="20"/>
-      <c r="R27" s="20"/>
-      <c r="S27" s="20"/>
-      <c r="T27" s="7"/>
-      <c r="U27" s="7"/>
-      <c r="V27" s="7"/>
-      <c r="W27" s="7"/>
-      <c r="X27" s="26"/>
+      <c r="P27" s="20">
+        <v>7.48</v>
+      </c>
+      <c r="Q27" s="20">
+        <v>27.47</v>
+      </c>
+      <c r="R27" s="20">
+        <v>29.69</v>
+      </c>
+      <c r="S27" s="20">
+        <v>4767</v>
+      </c>
+      <c r="T27" s="7">
+        <v>21.92</v>
+      </c>
+      <c r="U27" s="7">
+        <v>23.18</v>
+      </c>
+      <c r="V27" s="7">
+        <v>25.06</v>
+      </c>
+      <c r="W27" s="7">
+        <v>29.84</v>
+      </c>
+      <c r="X27" s="26">
+        <v>4022.99</v>
+      </c>
       <c r="Y27" s="26"/>
       <c r="Z27" s="27"/>
       <c r="AA27" s="27"/>
@@ -28591,19 +28804,37 @@
       <c r="M28" s="20">
         <v>3394.2</v>
       </c>
-      <c r="N28" s="20">
+      <c r="N28" s="66">
         <v>3398.8</v>
       </c>
       <c r="O28" s="20"/>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="20"/>
-      <c r="R28" s="20"/>
-      <c r="S28" s="20"/>
-      <c r="T28" s="7"/>
-      <c r="U28" s="7"/>
-      <c r="V28" s="7"/>
-      <c r="W28" s="7"/>
-      <c r="X28" s="26"/>
+      <c r="P28" s="20">
+        <v>6.98</v>
+      </c>
+      <c r="Q28" s="20">
+        <v>24.91</v>
+      </c>
+      <c r="R28" s="20">
+        <v>36.17</v>
+      </c>
+      <c r="S28" s="20">
+        <v>4250</v>
+      </c>
+      <c r="T28" s="7">
+        <v>20.03</v>
+      </c>
+      <c r="U28" s="7">
+        <v>21.42</v>
+      </c>
+      <c r="V28" s="7">
+        <v>31.1</v>
+      </c>
+      <c r="W28" s="7">
+        <v>27.45</v>
+      </c>
+      <c r="X28" s="26">
+        <v>3653.76</v>
+      </c>
       <c r="Y28" s="26"/>
       <c r="Z28" s="27"/>
       <c r="AA28" s="27"/>
@@ -28651,19 +28882,37 @@
       <c r="M29" s="20">
         <v>3974.7</v>
       </c>
-      <c r="N29" s="20">
+      <c r="N29" s="66">
         <v>3864.2</v>
       </c>
       <c r="O29" s="20"/>
-      <c r="P29" s="20"/>
-      <c r="Q29" s="20"/>
-      <c r="R29" s="20"/>
-      <c r="S29" s="20"/>
-      <c r="T29" s="7"/>
-      <c r="U29" s="7"/>
-      <c r="V29" s="7"/>
-      <c r="W29" s="7"/>
-      <c r="X29" s="26"/>
+      <c r="P29" s="20">
+        <v>5.86</v>
+      </c>
+      <c r="Q29" s="20">
+        <v>21.58</v>
+      </c>
+      <c r="R29" s="20">
+        <v>48.72</v>
+      </c>
+      <c r="S29" s="20">
+        <v>3269</v>
+      </c>
+      <c r="T29" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="U29" s="7">
+        <v>18.68</v>
+      </c>
+      <c r="V29" s="7">
+        <v>42.18</v>
+      </c>
+      <c r="W29" s="7">
+        <v>20.64</v>
+      </c>
+      <c r="X29" s="26">
+        <v>2830.08</v>
+      </c>
       <c r="Y29" s="26"/>
       <c r="Z29" s="27"/>
       <c r="AA29" s="27"/>
@@ -28711,19 +28960,37 @@
       <c r="M30" s="20">
         <v>3750.7</v>
       </c>
-      <c r="N30" s="20">
+      <c r="N30" s="66">
         <v>3861.8</v>
       </c>
       <c r="O30" s="20"/>
-      <c r="P30" s="20"/>
-      <c r="Q30" s="20"/>
-      <c r="R30" s="20"/>
-      <c r="S30" s="20"/>
-      <c r="T30" s="7"/>
-      <c r="U30" s="7"/>
-      <c r="V30" s="7"/>
-      <c r="W30" s="7"/>
-      <c r="X30" s="26"/>
+      <c r="P30" s="20">
+        <v>6.18</v>
+      </c>
+      <c r="Q30" s="20">
+        <v>23.25</v>
+      </c>
+      <c r="R30" s="20">
+        <v>46.35</v>
+      </c>
+      <c r="S30" s="20">
+        <v>3413</v>
+      </c>
+      <c r="T30" s="7">
+        <v>19.489999999999998</v>
+      </c>
+      <c r="U30" s="7">
+        <v>19.95</v>
+      </c>
+      <c r="V30" s="7">
+        <v>39.770000000000003</v>
+      </c>
+      <c r="W30" s="7">
+        <v>20.79</v>
+      </c>
+      <c r="X30" s="26">
+        <v>2928.81</v>
+      </c>
       <c r="Y30" s="26"/>
       <c r="Z30" s="27"/>
       <c r="AA30" s="27"/>
@@ -28771,20 +29038,37 @@
       <c r="M31" s="20">
         <v>3712.6</v>
       </c>
-      <c r="N31" s="20">
-        <f>M31</f>
-        <v>3712.6</v>
+      <c r="N31" s="66">
+        <v>3766.4</v>
       </c>
       <c r="O31" s="20"/>
-      <c r="P31" s="20"/>
-      <c r="Q31" s="20"/>
-      <c r="R31" s="20"/>
-      <c r="S31" s="20"/>
-      <c r="T31" s="7"/>
-      <c r="U31" s="7"/>
-      <c r="V31" s="7"/>
-      <c r="W31" s="7"/>
-      <c r="X31" s="26"/>
+      <c r="P31" s="20">
+        <v>7.43</v>
+      </c>
+      <c r="Q31" s="20">
+        <v>24.38</v>
+      </c>
+      <c r="R31" s="20">
+        <v>36.049999999999997</v>
+      </c>
+      <c r="S31" s="20">
+        <v>4301</v>
+      </c>
+      <c r="T31" s="7">
+        <v>21.69</v>
+      </c>
+      <c r="U31" s="7">
+        <v>20.62</v>
+      </c>
+      <c r="V31" s="7">
+        <v>30.5</v>
+      </c>
+      <c r="W31" s="7">
+        <v>27.19</v>
+      </c>
+      <c r="X31" s="26">
+        <v>3638.45</v>
+      </c>
       <c r="Y31" s="26"/>
       <c r="Z31" s="27"/>
       <c r="AA31" s="27"/>
@@ -28800,6 +29084,2662 @@
       <c r="AK31" s="29"/>
       <c r="AL31" s="20"/>
     </row>
+    <row r="32" spans="1:38">
+      <c r="A32" s="40">
+        <v>29</v>
+      </c>
+      <c r="B32" s="41">
+        <v>16691</v>
+      </c>
+      <c r="C32" s="42">
+        <v>46277</v>
+      </c>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="G32" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J32" s="41">
+        <v>142000549</v>
+      </c>
+      <c r="K32" s="42">
+        <v>46275</v>
+      </c>
+      <c r="L32" s="41"/>
+      <c r="M32" s="41">
+        <v>4054.6</v>
+      </c>
+      <c r="N32" s="67">
+        <v>4054.4</v>
+      </c>
+      <c r="O32" s="41"/>
+      <c r="P32" s="41">
+        <v>6.28</v>
+      </c>
+      <c r="Q32" s="41">
+        <v>21.5</v>
+      </c>
+      <c r="R32" s="41">
+        <v>52.28</v>
+      </c>
+      <c r="S32" s="41">
+        <v>2882</v>
+      </c>
+      <c r="T32" s="43">
+        <v>17.05</v>
+      </c>
+      <c r="U32" s="43">
+        <v>19.03</v>
+      </c>
+      <c r="V32" s="43">
+        <v>46.27</v>
+      </c>
+      <c r="W32" s="43">
+        <v>17.649999999999999</v>
+      </c>
+      <c r="X32" s="44">
+        <v>2550.81</v>
+      </c>
+      <c r="Y32" s="44"/>
+      <c r="Z32" s="45"/>
+      <c r="AA32" s="45"/>
+      <c r="AB32" s="45"/>
+      <c r="AC32" s="45"/>
+      <c r="AD32" s="45"/>
+      <c r="AE32" s="45"/>
+      <c r="AF32" s="46"/>
+      <c r="AG32" s="45"/>
+      <c r="AH32" s="47"/>
+      <c r="AI32" s="47"/>
+      <c r="AJ32" s="47"/>
+      <c r="AK32" s="47"/>
+      <c r="AL32" s="41"/>
+    </row>
+    <row r="33" spans="1:38">
+      <c r="A33" s="40">
+        <v>30</v>
+      </c>
+      <c r="B33" s="41">
+        <v>16693</v>
+      </c>
+      <c r="C33" s="42">
+        <v>46277</v>
+      </c>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G33" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H33" s="41"/>
+      <c r="I33" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J33" s="41">
+        <v>162011761</v>
+      </c>
+      <c r="K33" s="42">
+        <v>46275</v>
+      </c>
+      <c r="L33" s="41"/>
+      <c r="M33" s="41">
+        <v>3994.7</v>
+      </c>
+      <c r="N33" s="67">
+        <v>4030.2</v>
+      </c>
+      <c r="O33" s="41"/>
+      <c r="P33" s="41">
+        <v>7.16</v>
+      </c>
+      <c r="Q33" s="41">
+        <v>25.15</v>
+      </c>
+      <c r="R33" s="41">
+        <v>36.46</v>
+      </c>
+      <c r="S33" s="41">
+        <v>4184</v>
+      </c>
+      <c r="T33" s="43">
+        <v>20.77</v>
+      </c>
+      <c r="U33" s="43">
+        <v>21.46</v>
+      </c>
+      <c r="V33" s="43">
+        <v>31.12</v>
+      </c>
+      <c r="W33" s="43">
+        <v>26.65</v>
+      </c>
+      <c r="X33" s="44">
+        <v>3571</v>
+      </c>
+      <c r="Y33" s="44"/>
+      <c r="Z33" s="45"/>
+      <c r="AA33" s="45"/>
+      <c r="AB33" s="45"/>
+      <c r="AC33" s="45"/>
+      <c r="AD33" s="45"/>
+      <c r="AE33" s="45"/>
+      <c r="AF33" s="46"/>
+      <c r="AG33" s="45"/>
+      <c r="AH33" s="47"/>
+      <c r="AI33" s="47"/>
+      <c r="AJ33" s="47"/>
+      <c r="AK33" s="47"/>
+      <c r="AL33" s="41"/>
+    </row>
+    <row r="34" spans="1:38">
+      <c r="A34" s="40">
+        <v>31</v>
+      </c>
+      <c r="B34" s="41">
+        <v>16694</v>
+      </c>
+      <c r="C34" s="42">
+        <v>46277</v>
+      </c>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G34" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H34" s="41"/>
+      <c r="I34" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J34" s="41">
+        <v>162004442</v>
+      </c>
+      <c r="K34" s="42">
+        <v>46276</v>
+      </c>
+      <c r="L34" s="41"/>
+      <c r="M34" s="41">
+        <v>4033.1</v>
+      </c>
+      <c r="N34" s="67">
+        <v>3911.2</v>
+      </c>
+      <c r="O34" s="41"/>
+      <c r="P34" s="41">
+        <v>6.41</v>
+      </c>
+      <c r="Q34" s="41">
+        <v>22.86</v>
+      </c>
+      <c r="R34" s="41">
+        <v>45.19</v>
+      </c>
+      <c r="S34" s="41">
+        <v>3542</v>
+      </c>
+      <c r="T34" s="43">
+        <v>17.96</v>
+      </c>
+      <c r="U34" s="43">
+        <v>20.04</v>
+      </c>
+      <c r="V34" s="43">
+        <v>39.61</v>
+      </c>
+      <c r="W34" s="43">
+        <v>22.39</v>
+      </c>
+      <c r="X34" s="44">
+        <v>3105</v>
+      </c>
+      <c r="Y34" s="44"/>
+      <c r="Z34" s="45"/>
+      <c r="AA34" s="45"/>
+      <c r="AB34" s="45"/>
+      <c r="AC34" s="45"/>
+      <c r="AD34" s="45"/>
+      <c r="AE34" s="45"/>
+      <c r="AF34" s="46"/>
+      <c r="AG34" s="45"/>
+      <c r="AH34" s="47"/>
+      <c r="AI34" s="47"/>
+      <c r="AJ34" s="47"/>
+      <c r="AK34" s="47"/>
+      <c r="AL34" s="41"/>
+    </row>
+    <row r="35" spans="1:38">
+      <c r="A35" s="40">
+        <v>32</v>
+      </c>
+      <c r="B35" s="41">
+        <v>16695</v>
+      </c>
+      <c r="C35" s="42">
+        <v>46277</v>
+      </c>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="G35" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H35" s="41"/>
+      <c r="I35" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J35" s="41">
+        <v>162003252</v>
+      </c>
+      <c r="K35" s="42">
+        <v>46276</v>
+      </c>
+      <c r="L35" s="41"/>
+      <c r="M35" s="41">
+        <v>3976.5</v>
+      </c>
+      <c r="N35" s="67">
+        <v>3901</v>
+      </c>
+      <c r="O35" s="41"/>
+      <c r="P35" s="41">
+        <v>5.17</v>
+      </c>
+      <c r="Q35" s="41">
+        <v>18.73</v>
+      </c>
+      <c r="R35" s="41">
+        <v>59.64</v>
+      </c>
+      <c r="S35" s="41">
+        <v>2393</v>
+      </c>
+      <c r="T35" s="43">
+        <v>14.67</v>
+      </c>
+      <c r="U35" s="43">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="V35" s="43">
+        <v>53.67</v>
+      </c>
+      <c r="W35" s="43">
+        <v>14.81</v>
+      </c>
+      <c r="X35" s="44">
+        <v>2153</v>
+      </c>
+      <c r="Y35" s="44"/>
+      <c r="Z35" s="45"/>
+      <c r="AA35" s="45"/>
+      <c r="AB35" s="45"/>
+      <c r="AC35" s="45"/>
+      <c r="AD35" s="45"/>
+      <c r="AE35" s="45"/>
+      <c r="AF35" s="46"/>
+      <c r="AG35" s="45"/>
+      <c r="AH35" s="47"/>
+      <c r="AI35" s="47"/>
+      <c r="AJ35" s="47"/>
+      <c r="AK35" s="47"/>
+      <c r="AL35" s="41"/>
+    </row>
+    <row r="36" spans="1:38">
+      <c r="A36" s="40">
+        <v>33</v>
+      </c>
+      <c r="B36" s="41">
+        <v>16696</v>
+      </c>
+      <c r="C36" s="42">
+        <v>46278</v>
+      </c>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="G36" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H36" s="41"/>
+      <c r="I36" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J36" s="41">
+        <v>162001482</v>
+      </c>
+      <c r="K36" s="42">
+        <v>46276</v>
+      </c>
+      <c r="L36" s="41"/>
+      <c r="M36" s="41">
+        <v>3892.1</v>
+      </c>
+      <c r="N36" s="67">
+        <v>3930.2</v>
+      </c>
+      <c r="O36" s="41"/>
+      <c r="P36" s="41">
+        <v>5.88</v>
+      </c>
+      <c r="Q36" s="41">
+        <v>21.75</v>
+      </c>
+      <c r="R36" s="41">
+        <v>49</v>
+      </c>
+      <c r="S36" s="41">
+        <v>3248</v>
+      </c>
+      <c r="T36" s="43">
+        <v>18.05</v>
+      </c>
+      <c r="U36" s="43">
+        <v>18.940000000000001</v>
+      </c>
+      <c r="V36" s="43">
+        <v>42.66</v>
+      </c>
+      <c r="W36" s="43">
+        <v>20.350000000000001</v>
+      </c>
+      <c r="X36" s="44">
+        <v>2828</v>
+      </c>
+      <c r="Y36" s="44"/>
+      <c r="Z36" s="45"/>
+      <c r="AA36" s="45"/>
+      <c r="AB36" s="45"/>
+      <c r="AC36" s="45"/>
+      <c r="AD36" s="45"/>
+      <c r="AE36" s="45"/>
+      <c r="AF36" s="46"/>
+      <c r="AG36" s="45"/>
+      <c r="AH36" s="47"/>
+      <c r="AI36" s="47"/>
+      <c r="AJ36" s="47"/>
+      <c r="AK36" s="47"/>
+      <c r="AL36" s="41"/>
+    </row>
+    <row r="37" spans="1:38">
+      <c r="A37" s="40">
+        <v>34</v>
+      </c>
+      <c r="B37" s="41">
+        <v>16697</v>
+      </c>
+      <c r="C37" s="42">
+        <v>46278</v>
+      </c>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G37" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H37" s="41"/>
+      <c r="I37" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J37" s="41">
+        <v>162004443</v>
+      </c>
+      <c r="K37" s="42">
+        <v>46276</v>
+      </c>
+      <c r="L37" s="41"/>
+      <c r="M37" s="41">
+        <v>3957.5</v>
+      </c>
+      <c r="N37" s="67">
+        <v>3812.6</v>
+      </c>
+      <c r="O37" s="41"/>
+      <c r="P37" s="41">
+        <v>6.49</v>
+      </c>
+      <c r="Q37" s="41">
+        <v>21.36</v>
+      </c>
+      <c r="R37" s="41">
+        <v>49.35</v>
+      </c>
+      <c r="S37" s="41">
+        <v>3236</v>
+      </c>
+      <c r="T37" s="43">
+        <v>16.87</v>
+      </c>
+      <c r="U37" s="43">
+        <v>18.989999999999998</v>
+      </c>
+      <c r="V37" s="43">
+        <v>43.87</v>
+      </c>
+      <c r="W37" s="43">
+        <v>20.27</v>
+      </c>
+      <c r="X37" s="44">
+        <v>2877</v>
+      </c>
+      <c r="Y37" s="44"/>
+      <c r="Z37" s="45"/>
+      <c r="AA37" s="45"/>
+      <c r="AB37" s="45"/>
+      <c r="AC37" s="45"/>
+      <c r="AD37" s="45"/>
+      <c r="AE37" s="45"/>
+      <c r="AF37" s="46"/>
+      <c r="AG37" s="45"/>
+      <c r="AH37" s="47"/>
+      <c r="AI37" s="47"/>
+      <c r="AJ37" s="47"/>
+      <c r="AK37" s="47"/>
+      <c r="AL37" s="41"/>
+    </row>
+    <row r="38" spans="1:38">
+      <c r="A38" s="40">
+        <v>35</v>
+      </c>
+      <c r="B38" s="41">
+        <v>16698</v>
+      </c>
+      <c r="C38" s="42">
+        <v>46278</v>
+      </c>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G38" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H38" s="41"/>
+      <c r="I38" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J38" s="41">
+        <v>162011764</v>
+      </c>
+      <c r="K38" s="42">
+        <v>46277</v>
+      </c>
+      <c r="L38" s="41"/>
+      <c r="M38" s="41">
+        <v>3905.1</v>
+      </c>
+      <c r="N38" s="67">
+        <v>3929.6</v>
+      </c>
+      <c r="O38" s="41"/>
+      <c r="P38" s="41">
+        <v>5.75</v>
+      </c>
+      <c r="Q38" s="41">
+        <v>19.920000000000002</v>
+      </c>
+      <c r="R38" s="41">
+        <v>51.8</v>
+      </c>
+      <c r="S38" s="41">
+        <v>3073</v>
+      </c>
+      <c r="T38" s="43">
+        <v>16.59</v>
+      </c>
+      <c r="U38" s="43">
+        <v>17.63</v>
+      </c>
+      <c r="V38" s="43">
+        <v>45.84</v>
+      </c>
+      <c r="W38" s="43">
+        <v>19.940000000000001</v>
+      </c>
+      <c r="X38" s="44">
+        <v>2720</v>
+      </c>
+      <c r="Y38" s="44"/>
+      <c r="Z38" s="45"/>
+      <c r="AA38" s="45"/>
+      <c r="AB38" s="45"/>
+      <c r="AC38" s="45"/>
+      <c r="AD38" s="45"/>
+      <c r="AE38" s="45"/>
+      <c r="AF38" s="46"/>
+      <c r="AG38" s="45"/>
+      <c r="AH38" s="47"/>
+      <c r="AI38" s="47"/>
+      <c r="AJ38" s="47"/>
+      <c r="AK38" s="47"/>
+      <c r="AL38" s="41"/>
+    </row>
+    <row r="39" spans="1:38">
+      <c r="A39" s="40">
+        <v>36</v>
+      </c>
+      <c r="B39" s="41">
+        <v>16702</v>
+      </c>
+      <c r="C39" s="42">
+        <v>46279</v>
+      </c>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="G39" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H39" s="41"/>
+      <c r="I39" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J39" s="41">
+        <v>162003253</v>
+      </c>
+      <c r="K39" s="42">
+        <v>46277</v>
+      </c>
+      <c r="L39" s="41"/>
+      <c r="M39" s="41">
+        <v>3907.8</v>
+      </c>
+      <c r="N39" s="67">
+        <v>3791.8</v>
+      </c>
+      <c r="O39" s="41"/>
+      <c r="P39" s="41">
+        <v>7.49</v>
+      </c>
+      <c r="Q39" s="41">
+        <v>22.85</v>
+      </c>
+      <c r="R39" s="41">
+        <v>49.28</v>
+      </c>
+      <c r="S39" s="41">
+        <v>2969</v>
+      </c>
+      <c r="T39" s="43">
+        <v>17.14</v>
+      </c>
+      <c r="U39" s="43">
+        <v>20.47</v>
+      </c>
+      <c r="V39" s="43">
+        <v>44.14</v>
+      </c>
+      <c r="W39" s="43">
+        <v>18.25</v>
+      </c>
+      <c r="X39" s="44">
+        <v>2659</v>
+      </c>
+      <c r="Y39" s="44"/>
+      <c r="Z39" s="45"/>
+      <c r="AA39" s="45"/>
+      <c r="AB39" s="45"/>
+      <c r="AC39" s="45"/>
+      <c r="AD39" s="45"/>
+      <c r="AE39" s="45"/>
+      <c r="AF39" s="46"/>
+      <c r="AG39" s="45"/>
+      <c r="AH39" s="47"/>
+      <c r="AI39" s="47"/>
+      <c r="AJ39" s="47"/>
+      <c r="AK39" s="47"/>
+      <c r="AL39" s="41"/>
+    </row>
+    <row r="40" spans="1:38">
+      <c r="A40" s="40">
+        <v>37</v>
+      </c>
+      <c r="B40" s="41">
+        <v>16703</v>
+      </c>
+      <c r="C40" s="42">
+        <v>46280</v>
+      </c>
+      <c r="D40" s="41"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="G40" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H40" s="41"/>
+      <c r="I40" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J40" s="41">
+        <v>162003256</v>
+      </c>
+      <c r="K40" s="42">
+        <v>46278</v>
+      </c>
+      <c r="L40" s="41"/>
+      <c r="M40" s="41">
+        <v>4050.3</v>
+      </c>
+      <c r="N40" s="67">
+        <v>3945.8</v>
+      </c>
+      <c r="O40" s="41"/>
+      <c r="P40" s="41">
+        <v>6.32</v>
+      </c>
+      <c r="Q40" s="41">
+        <v>22.65</v>
+      </c>
+      <c r="R40" s="41">
+        <v>50.2</v>
+      </c>
+      <c r="S40" s="41">
+        <v>2978</v>
+      </c>
+      <c r="T40" s="43">
+        <v>16.170000000000002</v>
+      </c>
+      <c r="U40" s="43">
+        <v>20.27</v>
+      </c>
+      <c r="V40" s="43">
+        <v>44.92</v>
+      </c>
+      <c r="W40" s="43">
+        <v>18.64</v>
+      </c>
+      <c r="X40" s="44">
+        <v>2665</v>
+      </c>
+      <c r="Y40" s="44"/>
+      <c r="Z40" s="45"/>
+      <c r="AA40" s="45"/>
+      <c r="AB40" s="45"/>
+      <c r="AC40" s="45"/>
+      <c r="AD40" s="45"/>
+      <c r="AE40" s="45"/>
+      <c r="AF40" s="46"/>
+      <c r="AG40" s="45"/>
+      <c r="AH40" s="47"/>
+      <c r="AI40" s="47"/>
+      <c r="AJ40" s="47"/>
+      <c r="AK40" s="47"/>
+      <c r="AL40" s="41"/>
+    </row>
+    <row r="41" spans="1:38">
+      <c r="A41" s="40">
+        <v>38</v>
+      </c>
+      <c r="B41" s="41">
+        <v>16705</v>
+      </c>
+      <c r="C41" s="42">
+        <v>46280</v>
+      </c>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G41" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H41" s="41"/>
+      <c r="I41" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J41" s="41">
+        <v>162004447</v>
+      </c>
+      <c r="K41" s="42">
+        <v>46278</v>
+      </c>
+      <c r="L41" s="41"/>
+      <c r="M41" s="41">
+        <v>4084</v>
+      </c>
+      <c r="N41" s="67">
+        <v>4015.6</v>
+      </c>
+      <c r="O41" s="41"/>
+      <c r="P41" s="41">
+        <v>7.54</v>
+      </c>
+      <c r="Q41" s="41">
+        <v>25.47</v>
+      </c>
+      <c r="R41" s="41">
+        <v>38.119999999999997</v>
+      </c>
+      <c r="S41" s="41">
+        <v>3945</v>
+      </c>
+      <c r="T41" s="43">
+        <v>21.61</v>
+      </c>
+      <c r="U41" s="43">
+        <v>21.59</v>
+      </c>
+      <c r="V41" s="43">
+        <v>32.32</v>
+      </c>
+      <c r="W41" s="43">
+        <v>24.48</v>
+      </c>
+      <c r="X41" s="44">
+        <v>3345</v>
+      </c>
+      <c r="Y41" s="44"/>
+      <c r="Z41" s="45"/>
+      <c r="AA41" s="45"/>
+      <c r="AB41" s="45"/>
+      <c r="AC41" s="45"/>
+      <c r="AD41" s="45"/>
+      <c r="AE41" s="45"/>
+      <c r="AF41" s="46"/>
+      <c r="AG41" s="45"/>
+      <c r="AH41" s="47"/>
+      <c r="AI41" s="47"/>
+      <c r="AJ41" s="47"/>
+      <c r="AK41" s="47"/>
+      <c r="AL41" s="41"/>
+    </row>
+    <row r="42" spans="1:38">
+      <c r="A42" s="40">
+        <v>39</v>
+      </c>
+      <c r="B42" s="41">
+        <v>16706</v>
+      </c>
+      <c r="C42" s="42">
+        <v>46280</v>
+      </c>
+      <c r="D42" s="41"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G42" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H42" s="41"/>
+      <c r="I42" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J42" s="41">
+        <v>162004448</v>
+      </c>
+      <c r="K42" s="42">
+        <v>46279</v>
+      </c>
+      <c r="L42" s="41"/>
+      <c r="M42" s="41">
+        <v>3950.1</v>
+      </c>
+      <c r="N42" s="67">
+        <v>3832</v>
+      </c>
+      <c r="O42" s="41"/>
+      <c r="P42" s="41">
+        <v>7.32</v>
+      </c>
+      <c r="Q42" s="41">
+        <v>25.03</v>
+      </c>
+      <c r="R42" s="41">
+        <v>40.96</v>
+      </c>
+      <c r="S42" s="41">
+        <v>3782</v>
+      </c>
+      <c r="T42" s="43">
+        <v>21.38</v>
+      </c>
+      <c r="U42" s="43">
+        <v>21.23</v>
+      </c>
+      <c r="V42" s="43">
+        <v>34.75</v>
+      </c>
+      <c r="W42" s="43">
+        <v>22.64</v>
+      </c>
+      <c r="X42" s="44">
+        <v>3208</v>
+      </c>
+      <c r="Y42" s="44"/>
+      <c r="Z42" s="45"/>
+      <c r="AA42" s="45"/>
+      <c r="AB42" s="45"/>
+      <c r="AC42" s="45"/>
+      <c r="AD42" s="45"/>
+      <c r="AE42" s="45"/>
+      <c r="AF42" s="46"/>
+      <c r="AG42" s="45"/>
+      <c r="AH42" s="47"/>
+      <c r="AI42" s="47"/>
+      <c r="AJ42" s="47"/>
+      <c r="AK42" s="47"/>
+      <c r="AL42" s="41"/>
+    </row>
+    <row r="43" spans="1:38">
+      <c r="A43" s="40">
+        <v>40</v>
+      </c>
+      <c r="B43" s="41">
+        <v>16709</v>
+      </c>
+      <c r="C43" s="42">
+        <v>46281</v>
+      </c>
+      <c r="D43" s="41"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="G43" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H43" s="41"/>
+      <c r="I43" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J43" s="41">
+        <v>162001487</v>
+      </c>
+      <c r="K43" s="42">
+        <v>46279</v>
+      </c>
+      <c r="L43" s="41"/>
+      <c r="M43" s="41">
+        <v>3953.1</v>
+      </c>
+      <c r="N43" s="67">
+        <v>3907.4</v>
+      </c>
+      <c r="O43" s="41"/>
+      <c r="P43" s="41">
+        <v>7.19</v>
+      </c>
+      <c r="Q43" s="41">
+        <v>23.8</v>
+      </c>
+      <c r="R43" s="41">
+        <v>44.94</v>
+      </c>
+      <c r="S43" s="41">
+        <v>3368</v>
+      </c>
+      <c r="T43" s="43">
+        <v>18.07</v>
+      </c>
+      <c r="U43" s="43">
+        <v>21.01</v>
+      </c>
+      <c r="V43" s="43">
+        <v>39.67</v>
+      </c>
+      <c r="W43" s="43">
+        <v>21.25</v>
+      </c>
+      <c r="X43" s="44">
+        <v>2973</v>
+      </c>
+      <c r="Y43" s="44"/>
+      <c r="Z43" s="45"/>
+      <c r="AA43" s="45"/>
+      <c r="AB43" s="45"/>
+      <c r="AC43" s="45"/>
+      <c r="AD43" s="45"/>
+      <c r="AE43" s="45"/>
+      <c r="AF43" s="46"/>
+      <c r="AG43" s="45"/>
+      <c r="AH43" s="47"/>
+      <c r="AI43" s="47"/>
+      <c r="AJ43" s="47"/>
+      <c r="AK43" s="47"/>
+      <c r="AL43" s="41"/>
+    </row>
+    <row r="44" spans="1:38">
+      <c r="A44" s="40">
+        <v>41</v>
+      </c>
+      <c r="B44" s="41">
+        <v>16711</v>
+      </c>
+      <c r="C44" s="42">
+        <v>46281</v>
+      </c>
+      <c r="D44" s="41"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="G44" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H44" s="41"/>
+      <c r="I44" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J44" s="41">
+        <v>162003258</v>
+      </c>
+      <c r="K44" s="42">
+        <v>46279</v>
+      </c>
+      <c r="L44" s="41"/>
+      <c r="M44" s="41">
+        <v>4178.3</v>
+      </c>
+      <c r="N44" s="67">
+        <v>4146.3999999999996</v>
+      </c>
+      <c r="O44" s="41"/>
+      <c r="P44" s="41">
+        <v>6.93</v>
+      </c>
+      <c r="Q44" s="41">
+        <v>24.92</v>
+      </c>
+      <c r="R44" s="41">
+        <v>44.98</v>
+      </c>
+      <c r="S44" s="41">
+        <v>3356</v>
+      </c>
+      <c r="T44" s="43">
+        <v>19.78</v>
+      </c>
+      <c r="U44" s="43">
+        <v>21.48</v>
+      </c>
+      <c r="V44" s="43">
+        <v>38.770000000000003</v>
+      </c>
+      <c r="W44" s="43">
+        <v>19.97</v>
+      </c>
+      <c r="X44" s="44">
+        <v>2893</v>
+      </c>
+      <c r="Y44" s="44"/>
+      <c r="Z44" s="45"/>
+      <c r="AA44" s="45"/>
+      <c r="AB44" s="45"/>
+      <c r="AC44" s="45"/>
+      <c r="AD44" s="45"/>
+      <c r="AE44" s="45"/>
+      <c r="AF44" s="46"/>
+      <c r="AG44" s="45"/>
+      <c r="AH44" s="47"/>
+      <c r="AI44" s="47"/>
+      <c r="AJ44" s="47"/>
+      <c r="AK44" s="47"/>
+      <c r="AL44" s="41"/>
+    </row>
+    <row r="45" spans="1:38">
+      <c r="A45" s="40">
+        <v>42</v>
+      </c>
+      <c r="B45" s="41">
+        <v>16712</v>
+      </c>
+      <c r="C45" s="42">
+        <v>46281</v>
+      </c>
+      <c r="D45" s="41"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="G45" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H45" s="41"/>
+      <c r="I45" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J45" s="41">
+        <v>162003259</v>
+      </c>
+      <c r="K45" s="42">
+        <v>46280</v>
+      </c>
+      <c r="L45" s="41"/>
+      <c r="M45" s="41">
+        <v>4052.1</v>
+      </c>
+      <c r="N45" s="67">
+        <v>4112</v>
+      </c>
+      <c r="O45" s="41"/>
+      <c r="P45" s="41">
+        <v>6.24</v>
+      </c>
+      <c r="Q45" s="41">
+        <v>23.16</v>
+      </c>
+      <c r="R45" s="41">
+        <v>49.94</v>
+      </c>
+      <c r="S45" s="41">
+        <v>3043</v>
+      </c>
+      <c r="T45" s="43">
+        <v>18.2</v>
+      </c>
+      <c r="U45" s="43">
+        <v>20.21</v>
+      </c>
+      <c r="V45" s="43">
+        <v>43.57</v>
+      </c>
+      <c r="W45" s="43">
+        <v>18.02</v>
+      </c>
+      <c r="X45" s="44">
+        <v>2655</v>
+      </c>
+      <c r="Y45" s="44"/>
+      <c r="Z45" s="45"/>
+      <c r="AA45" s="45"/>
+      <c r="AB45" s="45"/>
+      <c r="AC45" s="45"/>
+      <c r="AD45" s="45"/>
+      <c r="AE45" s="45"/>
+      <c r="AF45" s="46"/>
+      <c r="AG45" s="45"/>
+      <c r="AH45" s="47"/>
+      <c r="AI45" s="47"/>
+      <c r="AJ45" s="47"/>
+      <c r="AK45" s="47"/>
+      <c r="AL45" s="41"/>
+    </row>
+    <row r="46" spans="1:38">
+      <c r="A46" s="40">
+        <v>43</v>
+      </c>
+      <c r="B46" s="41">
+        <v>16714</v>
+      </c>
+      <c r="C46" s="42">
+        <v>46282</v>
+      </c>
+      <c r="D46" s="41"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H46" s="41"/>
+      <c r="I46" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J46" s="41">
+        <v>162011771</v>
+      </c>
+      <c r="K46" s="42">
+        <v>46280</v>
+      </c>
+      <c r="L46" s="41"/>
+      <c r="M46" s="41">
+        <v>3901.6</v>
+      </c>
+      <c r="N46" s="41">
+        <v>3946.6</v>
+      </c>
+      <c r="O46" s="41"/>
+      <c r="P46" s="41"/>
+      <c r="Q46" s="41"/>
+      <c r="R46" s="41"/>
+      <c r="S46" s="41"/>
+      <c r="T46" s="43">
+        <v>20.27</v>
+      </c>
+      <c r="U46" s="43">
+        <v>19.12</v>
+      </c>
+      <c r="V46" s="43">
+        <v>38.61</v>
+      </c>
+      <c r="W46" s="43">
+        <v>22</v>
+      </c>
+      <c r="X46" s="44">
+        <v>2932</v>
+      </c>
+      <c r="Y46" s="44"/>
+      <c r="Z46" s="45"/>
+      <c r="AA46" s="45"/>
+      <c r="AB46" s="45"/>
+      <c r="AC46" s="45"/>
+      <c r="AD46" s="45"/>
+      <c r="AE46" s="45"/>
+      <c r="AF46" s="46"/>
+      <c r="AG46" s="45"/>
+      <c r="AH46" s="47"/>
+      <c r="AI46" s="47"/>
+      <c r="AJ46" s="47"/>
+      <c r="AK46" s="47"/>
+      <c r="AL46" s="41"/>
+    </row>
+    <row r="47" spans="1:38">
+      <c r="A47" s="40">
+        <v>44</v>
+      </c>
+      <c r="B47" s="41">
+        <v>16716</v>
+      </c>
+      <c r="C47" s="42">
+        <v>46282</v>
+      </c>
+      <c r="D47" s="41"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="G47" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H47" s="41"/>
+      <c r="I47" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J47" s="41">
+        <v>162001489</v>
+      </c>
+      <c r="K47" s="42">
+        <v>46281</v>
+      </c>
+      <c r="L47" s="41"/>
+      <c r="M47" s="41">
+        <v>3956.7</v>
+      </c>
+      <c r="N47" s="41">
+        <v>4172</v>
+      </c>
+      <c r="O47" s="41"/>
+      <c r="P47" s="41"/>
+      <c r="Q47" s="41"/>
+      <c r="R47" s="41"/>
+      <c r="S47" s="41"/>
+      <c r="T47" s="43">
+        <v>20.53</v>
+      </c>
+      <c r="U47" s="43">
+        <v>21.63</v>
+      </c>
+      <c r="V47" s="43">
+        <v>36.32</v>
+      </c>
+      <c r="W47" s="43">
+        <v>21.52</v>
+      </c>
+      <c r="X47" s="44">
+        <v>3079</v>
+      </c>
+      <c r="Y47" s="44"/>
+      <c r="Z47" s="45"/>
+      <c r="AA47" s="45"/>
+      <c r="AB47" s="45"/>
+      <c r="AC47" s="45"/>
+      <c r="AD47" s="45"/>
+      <c r="AE47" s="45"/>
+      <c r="AF47" s="46"/>
+      <c r="AG47" s="45"/>
+      <c r="AH47" s="47"/>
+      <c r="AI47" s="47"/>
+      <c r="AJ47" s="47"/>
+      <c r="AK47" s="47"/>
+      <c r="AL47" s="41"/>
+    </row>
+    <row r="48" spans="1:38">
+      <c r="A48" s="40">
+        <v>45</v>
+      </c>
+      <c r="B48" s="41">
+        <v>16717</v>
+      </c>
+      <c r="C48" s="42">
+        <v>46282</v>
+      </c>
+      <c r="D48" s="41"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G48" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H48" s="41"/>
+      <c r="I48" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J48" s="41">
+        <v>162011774</v>
+      </c>
+      <c r="K48" s="42">
+        <v>46281</v>
+      </c>
+      <c r="L48" s="41"/>
+      <c r="M48" s="41">
+        <v>3987.2</v>
+      </c>
+      <c r="N48" s="41">
+        <v>4157</v>
+      </c>
+      <c r="O48" s="41"/>
+      <c r="P48" s="41"/>
+      <c r="Q48" s="41"/>
+      <c r="R48" s="41"/>
+      <c r="S48" s="41"/>
+      <c r="T48" s="43">
+        <v>19.32</v>
+      </c>
+      <c r="U48" s="43">
+        <v>18.27</v>
+      </c>
+      <c r="V48" s="43">
+        <v>40.08</v>
+      </c>
+      <c r="W48" s="43">
+        <v>22.33</v>
+      </c>
+      <c r="X48" s="44">
+        <v>2851</v>
+      </c>
+      <c r="Y48" s="44"/>
+      <c r="Z48" s="45"/>
+      <c r="AA48" s="45"/>
+      <c r="AB48" s="45"/>
+      <c r="AC48" s="45"/>
+      <c r="AD48" s="45"/>
+      <c r="AE48" s="45"/>
+      <c r="AF48" s="46"/>
+      <c r="AG48" s="45"/>
+      <c r="AH48" s="47"/>
+      <c r="AI48" s="47"/>
+      <c r="AJ48" s="47"/>
+      <c r="AK48" s="47"/>
+      <c r="AL48" s="41"/>
+    </row>
+    <row r="49" spans="1:38">
+      <c r="A49" s="40">
+        <v>46</v>
+      </c>
+      <c r="B49" s="41">
+        <v>16719</v>
+      </c>
+      <c r="C49" s="42">
+        <v>46283</v>
+      </c>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="G49" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H49" s="41"/>
+      <c r="I49" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J49" s="41">
+        <v>162001492</v>
+      </c>
+      <c r="K49" s="42">
+        <v>46281</v>
+      </c>
+      <c r="L49" s="41"/>
+      <c r="M49" s="41">
+        <v>4038.4</v>
+      </c>
+      <c r="N49" s="41">
+        <v>3992</v>
+      </c>
+      <c r="O49" s="41"/>
+      <c r="P49" s="41"/>
+      <c r="Q49" s="41"/>
+      <c r="R49" s="41"/>
+      <c r="S49" s="41"/>
+      <c r="T49" s="43">
+        <v>20.7</v>
+      </c>
+      <c r="U49" s="43">
+        <v>22.37</v>
+      </c>
+      <c r="V49" s="43">
+        <v>33.28</v>
+      </c>
+      <c r="W49" s="43">
+        <v>23.65</v>
+      </c>
+      <c r="X49" s="44">
+        <v>3338</v>
+      </c>
+      <c r="Y49" s="44"/>
+      <c r="Z49" s="45"/>
+      <c r="AA49" s="45"/>
+      <c r="AB49" s="45"/>
+      <c r="AC49" s="45"/>
+      <c r="AD49" s="45"/>
+      <c r="AE49" s="45"/>
+      <c r="AF49" s="46"/>
+      <c r="AG49" s="45"/>
+      <c r="AH49" s="47"/>
+      <c r="AI49" s="47"/>
+      <c r="AJ49" s="47"/>
+      <c r="AK49" s="47"/>
+      <c r="AL49" s="41"/>
+    </row>
+    <row r="50" spans="1:38">
+      <c r="A50" s="40">
+        <v>47</v>
+      </c>
+      <c r="B50" s="41">
+        <v>16721</v>
+      </c>
+      <c r="C50" s="42">
+        <v>46283</v>
+      </c>
+      <c r="D50" s="41"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G50" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H50" s="41"/>
+      <c r="I50" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J50" s="41">
+        <v>162004450</v>
+      </c>
+      <c r="K50" s="42">
+        <v>46280</v>
+      </c>
+      <c r="L50" s="41"/>
+      <c r="M50" s="41">
+        <v>3962.2</v>
+      </c>
+      <c r="N50" s="41">
+        <v>3796.4</v>
+      </c>
+      <c r="O50" s="41"/>
+      <c r="P50" s="41"/>
+      <c r="Q50" s="41"/>
+      <c r="R50" s="41"/>
+      <c r="S50" s="41"/>
+      <c r="T50" s="43">
+        <v>19.53</v>
+      </c>
+      <c r="U50" s="43">
+        <v>20.91</v>
+      </c>
+      <c r="V50" s="43">
+        <v>38.25</v>
+      </c>
+      <c r="W50" s="43">
+        <v>21.31</v>
+      </c>
+      <c r="X50" s="44">
+        <v>3029</v>
+      </c>
+      <c r="Y50" s="44"/>
+      <c r="Z50" s="45"/>
+      <c r="AA50" s="45"/>
+      <c r="AB50" s="45"/>
+      <c r="AC50" s="45"/>
+      <c r="AD50" s="45"/>
+      <c r="AE50" s="45"/>
+      <c r="AF50" s="46"/>
+      <c r="AG50" s="45"/>
+      <c r="AH50" s="47"/>
+      <c r="AI50" s="47"/>
+      <c r="AJ50" s="47"/>
+      <c r="AK50" s="47"/>
+      <c r="AL50" s="41"/>
+    </row>
+    <row r="51" spans="1:38">
+      <c r="A51" s="40">
+        <v>48</v>
+      </c>
+      <c r="B51" s="41">
+        <v>16722</v>
+      </c>
+      <c r="C51" s="42">
+        <v>46283</v>
+      </c>
+      <c r="D51" s="41"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="G51" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H51" s="41"/>
+      <c r="I51" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J51" s="41">
+        <v>162006553</v>
+      </c>
+      <c r="K51" s="42">
+        <v>46281</v>
+      </c>
+      <c r="L51" s="41"/>
+      <c r="M51" s="41">
+        <v>3904.9</v>
+      </c>
+      <c r="N51" s="41">
+        <v>3908.6</v>
+      </c>
+      <c r="O51" s="41"/>
+      <c r="P51" s="41"/>
+      <c r="Q51" s="41"/>
+      <c r="R51" s="41"/>
+      <c r="S51" s="41"/>
+      <c r="T51" s="43">
+        <v>17.53</v>
+      </c>
+      <c r="U51" s="43">
+        <v>20.86</v>
+      </c>
+      <c r="V51" s="43">
+        <v>42.33</v>
+      </c>
+      <c r="W51" s="43">
+        <v>19.28</v>
+      </c>
+      <c r="X51" s="44">
+        <v>2750</v>
+      </c>
+      <c r="Y51" s="44"/>
+      <c r="Z51" s="45"/>
+      <c r="AA51" s="45"/>
+      <c r="AB51" s="45"/>
+      <c r="AC51" s="45"/>
+      <c r="AD51" s="45"/>
+      <c r="AE51" s="45"/>
+      <c r="AF51" s="46"/>
+      <c r="AG51" s="45"/>
+      <c r="AH51" s="47"/>
+      <c r="AI51" s="47"/>
+      <c r="AJ51" s="47"/>
+      <c r="AK51" s="47"/>
+      <c r="AL51" s="41"/>
+    </row>
+    <row r="52" spans="1:38">
+      <c r="A52" s="40">
+        <v>49</v>
+      </c>
+      <c r="B52" s="41">
+        <v>16724</v>
+      </c>
+      <c r="C52" s="42">
+        <v>46283</v>
+      </c>
+      <c r="D52" s="41"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="G52" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H52" s="41"/>
+      <c r="I52" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J52" s="41">
+        <v>162003261</v>
+      </c>
+      <c r="K52" s="42">
+        <v>46282</v>
+      </c>
+      <c r="L52" s="41"/>
+      <c r="M52" s="41">
+        <v>3984.1</v>
+      </c>
+      <c r="N52" s="41">
+        <v>3872</v>
+      </c>
+      <c r="O52" s="41"/>
+      <c r="P52" s="41"/>
+      <c r="Q52" s="41"/>
+      <c r="R52" s="41"/>
+      <c r="S52" s="41"/>
+      <c r="T52" s="43">
+        <v>19.32</v>
+      </c>
+      <c r="U52" s="43">
+        <v>22.18</v>
+      </c>
+      <c r="V52" s="43">
+        <v>38.9</v>
+      </c>
+      <c r="W52" s="43">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="X52" s="44">
+        <v>2904</v>
+      </c>
+      <c r="Y52" s="44"/>
+      <c r="Z52" s="45"/>
+      <c r="AA52" s="45"/>
+      <c r="AB52" s="45"/>
+      <c r="AC52" s="45"/>
+      <c r="AD52" s="45"/>
+      <c r="AE52" s="45"/>
+      <c r="AF52" s="46"/>
+      <c r="AG52" s="45"/>
+      <c r="AH52" s="47"/>
+      <c r="AI52" s="47"/>
+      <c r="AJ52" s="47"/>
+      <c r="AK52" s="47"/>
+      <c r="AL52" s="41"/>
+    </row>
+    <row r="53" spans="1:38">
+      <c r="A53" s="40">
+        <v>50</v>
+      </c>
+      <c r="B53" s="41">
+        <v>16726</v>
+      </c>
+      <c r="C53" s="42">
+        <v>46284</v>
+      </c>
+      <c r="D53" s="41"/>
+      <c r="E53" s="41"/>
+      <c r="F53" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G53" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H53" s="41"/>
+      <c r="I53" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J53" s="41">
+        <v>162004452</v>
+      </c>
+      <c r="K53" s="42">
+        <v>46281</v>
+      </c>
+      <c r="L53" s="41"/>
+      <c r="M53" s="41">
+        <v>3811.6</v>
+      </c>
+      <c r="N53" s="41">
+        <v>3717.4</v>
+      </c>
+      <c r="O53" s="41"/>
+      <c r="P53" s="41"/>
+      <c r="Q53" s="41"/>
+      <c r="R53" s="41"/>
+      <c r="S53" s="41"/>
+      <c r="T53" s="43">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="U53" s="43">
+        <v>20.93</v>
+      </c>
+      <c r="V53" s="43">
+        <v>36.25</v>
+      </c>
+      <c r="W53" s="43">
+        <v>22.42</v>
+      </c>
+      <c r="X53" s="44">
+        <v>3105</v>
+      </c>
+      <c r="Y53" s="44"/>
+      <c r="Z53" s="45"/>
+      <c r="AA53" s="45"/>
+      <c r="AB53" s="45"/>
+      <c r="AC53" s="45"/>
+      <c r="AD53" s="45"/>
+      <c r="AE53" s="45"/>
+      <c r="AF53" s="46"/>
+      <c r="AG53" s="45"/>
+      <c r="AH53" s="47"/>
+      <c r="AI53" s="47"/>
+      <c r="AJ53" s="47"/>
+      <c r="AK53" s="47"/>
+      <c r="AL53" s="41"/>
+    </row>
+    <row r="54" spans="1:38">
+      <c r="A54" s="40">
+        <v>51</v>
+      </c>
+      <c r="B54" s="41">
+        <v>16727</v>
+      </c>
+      <c r="C54" s="42">
+        <v>46284</v>
+      </c>
+      <c r="D54" s="41"/>
+      <c r="E54" s="41"/>
+      <c r="F54" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="G54" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H54" s="41"/>
+      <c r="I54" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J54" s="41">
+        <v>162006554</v>
+      </c>
+      <c r="K54" s="42">
+        <v>46281</v>
+      </c>
+      <c r="L54" s="41"/>
+      <c r="M54" s="41">
+        <v>3645.1</v>
+      </c>
+      <c r="N54" s="41">
+        <v>3626</v>
+      </c>
+      <c r="O54" s="41"/>
+      <c r="P54" s="41"/>
+      <c r="Q54" s="41"/>
+      <c r="R54" s="41"/>
+      <c r="S54" s="41"/>
+      <c r="T54" s="43">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="U54" s="43">
+        <v>16.760000000000002</v>
+      </c>
+      <c r="V54" s="43">
+        <v>51.24</v>
+      </c>
+      <c r="W54" s="43">
+        <v>15.9</v>
+      </c>
+      <c r="X54" s="44">
+        <v>2229</v>
+      </c>
+      <c r="Y54" s="44"/>
+      <c r="Z54" s="45"/>
+      <c r="AA54" s="45"/>
+      <c r="AB54" s="45"/>
+      <c r="AC54" s="45"/>
+      <c r="AD54" s="45"/>
+      <c r="AE54" s="45"/>
+      <c r="AF54" s="46"/>
+      <c r="AG54" s="45"/>
+      <c r="AH54" s="47"/>
+      <c r="AI54" s="47"/>
+      <c r="AJ54" s="47"/>
+      <c r="AK54" s="47"/>
+      <c r="AL54" s="41"/>
+    </row>
+    <row r="55" spans="1:38">
+      <c r="A55" s="40">
+        <v>52</v>
+      </c>
+      <c r="B55" s="41">
+        <v>16729</v>
+      </c>
+      <c r="C55" s="42">
+        <v>46285</v>
+      </c>
+      <c r="D55" s="41"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="G55" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H55" s="41"/>
+      <c r="I55" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J55" s="41">
+        <v>162006555</v>
+      </c>
+      <c r="K55" s="42">
+        <v>46282</v>
+      </c>
+      <c r="L55" s="41"/>
+      <c r="M55" s="41">
+        <v>3980.4</v>
+      </c>
+      <c r="N55" s="41">
+        <v>3900.4</v>
+      </c>
+      <c r="O55" s="41"/>
+      <c r="P55" s="41"/>
+      <c r="Q55" s="41"/>
+      <c r="R55" s="41"/>
+      <c r="S55" s="41"/>
+      <c r="T55" s="43">
+        <v>15.82</v>
+      </c>
+      <c r="U55" s="43">
+        <v>17.350000000000001</v>
+      </c>
+      <c r="V55" s="43">
+        <v>51.86</v>
+      </c>
+      <c r="W55" s="43">
+        <v>14.97</v>
+      </c>
+      <c r="X55" s="44">
+        <v>2187</v>
+      </c>
+      <c r="Y55" s="44"/>
+      <c r="Z55" s="45"/>
+      <c r="AA55" s="45"/>
+      <c r="AB55" s="45"/>
+      <c r="AC55" s="45"/>
+      <c r="AD55" s="45"/>
+      <c r="AE55" s="45"/>
+      <c r="AF55" s="46"/>
+      <c r="AG55" s="45"/>
+      <c r="AH55" s="47"/>
+      <c r="AI55" s="47"/>
+      <c r="AJ55" s="47"/>
+      <c r="AK55" s="47"/>
+      <c r="AL55" s="41"/>
+    </row>
+    <row r="56" spans="1:38">
+      <c r="A56" s="40">
+        <v>53</v>
+      </c>
+      <c r="B56" s="41">
+        <v>16730</v>
+      </c>
+      <c r="C56" s="42">
+        <v>46285</v>
+      </c>
+      <c r="D56" s="41"/>
+      <c r="E56" s="41"/>
+      <c r="F56" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G56" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H56" s="41"/>
+      <c r="I56" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J56" s="41">
+        <v>162011773</v>
+      </c>
+      <c r="K56" s="42">
+        <v>46280</v>
+      </c>
+      <c r="L56" s="41"/>
+      <c r="M56" s="41">
+        <v>3904.1</v>
+      </c>
+      <c r="N56" s="41">
+        <v>3963.8</v>
+      </c>
+      <c r="O56" s="41"/>
+      <c r="P56" s="41"/>
+      <c r="Q56" s="41"/>
+      <c r="R56" s="41"/>
+      <c r="S56" s="41"/>
+      <c r="T56" s="43">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="U56" s="43">
+        <v>16.989999999999998</v>
+      </c>
+      <c r="V56" s="43">
+        <v>47.56</v>
+      </c>
+      <c r="W56" s="43">
+        <v>18.84</v>
+      </c>
+      <c r="X56" s="44">
+        <v>2501</v>
+      </c>
+      <c r="Y56" s="44"/>
+      <c r="Z56" s="45"/>
+      <c r="AA56" s="45"/>
+      <c r="AB56" s="45"/>
+      <c r="AC56" s="45"/>
+      <c r="AD56" s="45"/>
+      <c r="AE56" s="45"/>
+      <c r="AF56" s="46"/>
+      <c r="AG56" s="45"/>
+      <c r="AH56" s="47"/>
+      <c r="AI56" s="47"/>
+      <c r="AJ56" s="47"/>
+      <c r="AK56" s="47"/>
+      <c r="AL56" s="41"/>
+    </row>
+    <row r="57" spans="1:38">
+      <c r="A57" s="40">
+        <v>54</v>
+      </c>
+      <c r="B57" s="41">
+        <v>16732</v>
+      </c>
+      <c r="C57" s="42">
+        <v>46285</v>
+      </c>
+      <c r="D57" s="41"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G57" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H57" s="41"/>
+      <c r="I57" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J57" s="41">
+        <v>162011778</v>
+      </c>
+      <c r="K57" s="42">
+        <v>46283</v>
+      </c>
+      <c r="L57" s="41"/>
+      <c r="M57" s="41">
+        <v>3747.8</v>
+      </c>
+      <c r="N57" s="41">
+        <v>3796.8</v>
+      </c>
+      <c r="O57" s="41"/>
+      <c r="P57" s="41"/>
+      <c r="Q57" s="41"/>
+      <c r="R57" s="41"/>
+      <c r="S57" s="41"/>
+      <c r="T57" s="43">
+        <v>20.39</v>
+      </c>
+      <c r="U57" s="43">
+        <v>19.89</v>
+      </c>
+      <c r="V57" s="43">
+        <v>31.75</v>
+      </c>
+      <c r="W57" s="43">
+        <v>27.97</v>
+      </c>
+      <c r="X57" s="44">
+        <v>3532</v>
+      </c>
+      <c r="Y57" s="44"/>
+      <c r="Z57" s="45"/>
+      <c r="AA57" s="45"/>
+      <c r="AB57" s="45"/>
+      <c r="AC57" s="45"/>
+      <c r="AD57" s="45"/>
+      <c r="AE57" s="45"/>
+      <c r="AF57" s="46"/>
+      <c r="AG57" s="45"/>
+      <c r="AH57" s="47"/>
+      <c r="AI57" s="47"/>
+      <c r="AJ57" s="47"/>
+      <c r="AK57" s="47"/>
+      <c r="AL57" s="41"/>
+    </row>
+    <row r="58" spans="1:38">
+      <c r="A58" s="40">
+        <v>55</v>
+      </c>
+      <c r="B58" s="41">
+        <v>16734</v>
+      </c>
+      <c r="C58" s="42">
+        <v>46286</v>
+      </c>
+      <c r="D58" s="41"/>
+      <c r="E58" s="41"/>
+      <c r="F58" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="G58" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H58" s="41"/>
+      <c r="I58" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J58" s="41">
+        <v>162001494</v>
+      </c>
+      <c r="K58" s="42">
+        <v>46283</v>
+      </c>
+      <c r="L58" s="41"/>
+      <c r="M58" s="41">
+        <v>4059.1</v>
+      </c>
+      <c r="N58" s="41">
+        <v>3764</v>
+      </c>
+      <c r="O58" s="41"/>
+      <c r="P58" s="41"/>
+      <c r="Q58" s="41"/>
+      <c r="R58" s="41"/>
+      <c r="S58" s="41"/>
+      <c r="T58" s="43">
+        <v>18.670000000000002</v>
+      </c>
+      <c r="U58" s="43">
+        <v>19.309999999999999</v>
+      </c>
+      <c r="V58" s="43">
+        <v>42.72</v>
+      </c>
+      <c r="W58" s="43">
+        <v>19.3</v>
+      </c>
+      <c r="X58" s="44">
+        <v>2727</v>
+      </c>
+      <c r="Y58" s="44"/>
+      <c r="Z58" s="45"/>
+      <c r="AA58" s="45"/>
+      <c r="AB58" s="45"/>
+      <c r="AC58" s="45"/>
+      <c r="AD58" s="45"/>
+      <c r="AE58" s="45"/>
+      <c r="AF58" s="46"/>
+      <c r="AG58" s="45"/>
+      <c r="AH58" s="47"/>
+      <c r="AI58" s="47"/>
+      <c r="AJ58" s="47"/>
+      <c r="AK58" s="47"/>
+      <c r="AL58" s="41"/>
+    </row>
+    <row r="59" spans="1:38">
+      <c r="A59" s="40">
+        <v>56</v>
+      </c>
+      <c r="B59" s="41">
+        <v>16736</v>
+      </c>
+      <c r="C59" s="42">
+        <v>46287</v>
+      </c>
+      <c r="D59" s="41"/>
+      <c r="E59" s="41"/>
+      <c r="F59" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G59" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H59" s="41"/>
+      <c r="I59" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J59" s="41">
+        <v>162011776</v>
+      </c>
+      <c r="K59" s="42">
+        <v>46282</v>
+      </c>
+      <c r="L59" s="41"/>
+      <c r="M59" s="41">
+        <v>4063.2</v>
+      </c>
+      <c r="N59" s="41">
+        <v>4058.4</v>
+      </c>
+      <c r="O59" s="41"/>
+      <c r="P59" s="41"/>
+      <c r="Q59" s="41"/>
+      <c r="R59" s="41"/>
+      <c r="S59" s="41"/>
+      <c r="T59" s="43">
+        <v>22.91</v>
+      </c>
+      <c r="U59" s="43">
+        <v>19.07</v>
+      </c>
+      <c r="V59" s="43">
+        <v>34.369999999999997</v>
+      </c>
+      <c r="W59" s="43">
+        <v>23.65</v>
+      </c>
+      <c r="X59" s="44">
+        <v>3205</v>
+      </c>
+      <c r="Y59" s="44"/>
+      <c r="Z59" s="45"/>
+      <c r="AA59" s="45"/>
+      <c r="AB59" s="45"/>
+      <c r="AC59" s="45"/>
+      <c r="AD59" s="45"/>
+      <c r="AE59" s="45"/>
+      <c r="AF59" s="46"/>
+      <c r="AG59" s="45"/>
+      <c r="AH59" s="47"/>
+      <c r="AI59" s="47"/>
+      <c r="AJ59" s="47"/>
+      <c r="AK59" s="47"/>
+      <c r="AL59" s="41"/>
+    </row>
+    <row r="60" spans="1:38">
+      <c r="A60" s="40">
+        <v>57</v>
+      </c>
+      <c r="B60" s="41">
+        <v>16738</v>
+      </c>
+      <c r="C60" s="42">
+        <v>46287</v>
+      </c>
+      <c r="D60" s="41"/>
+      <c r="E60" s="41"/>
+      <c r="F60" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="G60" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H60" s="41"/>
+      <c r="I60" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J60" s="41">
+        <v>162006571</v>
+      </c>
+      <c r="K60" s="42">
+        <v>46285</v>
+      </c>
+      <c r="L60" s="41"/>
+      <c r="M60" s="41">
+        <v>3954.4</v>
+      </c>
+      <c r="N60" s="41">
+        <v>3873.4</v>
+      </c>
+      <c r="O60" s="41"/>
+      <c r="P60" s="41"/>
+      <c r="Q60" s="41"/>
+      <c r="R60" s="41"/>
+      <c r="S60" s="41"/>
+      <c r="T60" s="43">
+        <v>16.54</v>
+      </c>
+      <c r="U60" s="43">
+        <v>19.04</v>
+      </c>
+      <c r="V60" s="43">
+        <v>47.39</v>
+      </c>
+      <c r="W60" s="43">
+        <v>17.03</v>
+      </c>
+      <c r="X60" s="44">
+        <v>2456</v>
+      </c>
+      <c r="Y60" s="44"/>
+      <c r="Z60" s="45"/>
+      <c r="AA60" s="45"/>
+      <c r="AB60" s="45"/>
+      <c r="AC60" s="45"/>
+      <c r="AD60" s="45"/>
+      <c r="AE60" s="45"/>
+      <c r="AF60" s="46"/>
+      <c r="AG60" s="45"/>
+      <c r="AH60" s="47"/>
+      <c r="AI60" s="47"/>
+      <c r="AJ60" s="47"/>
+      <c r="AK60" s="47"/>
+      <c r="AL60" s="41"/>
+    </row>
+    <row r="61" spans="1:38">
+      <c r="A61" s="40">
+        <v>58</v>
+      </c>
+      <c r="B61" s="41">
+        <v>16739</v>
+      </c>
+      <c r="C61" s="42">
+        <v>46287</v>
+      </c>
+      <c r="D61" s="41"/>
+      <c r="E61" s="41"/>
+      <c r="F61" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G61" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H61" s="41"/>
+      <c r="I61" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J61" s="41">
+        <v>162011784</v>
+      </c>
+      <c r="K61" s="42">
+        <v>46285</v>
+      </c>
+      <c r="L61" s="41"/>
+      <c r="M61" s="41">
+        <v>3876.2</v>
+      </c>
+      <c r="N61" s="41">
+        <v>3891.98</v>
+      </c>
+      <c r="O61" s="41"/>
+      <c r="P61" s="41"/>
+      <c r="Q61" s="41"/>
+      <c r="R61" s="41"/>
+      <c r="S61" s="41"/>
+      <c r="T61" s="43">
+        <v>21.47</v>
+      </c>
+      <c r="U61" s="43">
+        <v>19.09</v>
+      </c>
+      <c r="V61" s="43">
+        <v>35.18</v>
+      </c>
+      <c r="W61" s="43">
+        <v>24.26</v>
+      </c>
+      <c r="X61" s="44">
+        <v>3183</v>
+      </c>
+      <c r="Y61" s="44"/>
+      <c r="Z61" s="45"/>
+      <c r="AA61" s="45"/>
+      <c r="AB61" s="45"/>
+      <c r="AC61" s="45"/>
+      <c r="AD61" s="45"/>
+      <c r="AE61" s="45"/>
+      <c r="AF61" s="46"/>
+      <c r="AG61" s="45"/>
+      <c r="AH61" s="47"/>
+      <c r="AI61" s="47"/>
+      <c r="AJ61" s="47"/>
+      <c r="AK61" s="47"/>
+      <c r="AL61" s="41"/>
+    </row>
+    <row r="62" spans="1:38">
+      <c r="A62" s="40">
+        <v>59</v>
+      </c>
+      <c r="B62" s="41">
+        <v>16740</v>
+      </c>
+      <c r="C62" s="42">
+        <v>46287</v>
+      </c>
+      <c r="D62" s="41"/>
+      <c r="E62" s="41"/>
+      <c r="F62" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G62" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H62" s="41"/>
+      <c r="I62" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J62" s="41">
+        <v>162004455</v>
+      </c>
+      <c r="K62" s="42">
+        <v>46286</v>
+      </c>
+      <c r="L62" s="41"/>
+      <c r="M62" s="41">
+        <v>3904.4</v>
+      </c>
+      <c r="N62" s="41">
+        <v>3832</v>
+      </c>
+      <c r="O62" s="41"/>
+      <c r="P62" s="41"/>
+      <c r="Q62" s="41"/>
+      <c r="R62" s="41"/>
+      <c r="S62" s="41"/>
+      <c r="T62" s="43">
+        <v>20.350000000000001</v>
+      </c>
+      <c r="U62" s="43">
+        <v>20.079999999999998</v>
+      </c>
+      <c r="V62" s="43">
+        <v>37.96</v>
+      </c>
+      <c r="W62" s="43">
+        <v>21.61</v>
+      </c>
+      <c r="X62" s="44">
+        <v>2996</v>
+      </c>
+      <c r="Y62" s="44"/>
+      <c r="Z62" s="45"/>
+      <c r="AA62" s="45"/>
+      <c r="AB62" s="45"/>
+      <c r="AC62" s="45"/>
+      <c r="AD62" s="45"/>
+      <c r="AE62" s="45"/>
+      <c r="AF62" s="46"/>
+      <c r="AG62" s="45"/>
+      <c r="AH62" s="47"/>
+      <c r="AI62" s="47"/>
+      <c r="AJ62" s="47"/>
+      <c r="AK62" s="47"/>
+      <c r="AL62" s="41"/>
+    </row>
+    <row r="63" spans="1:38">
+      <c r="A63" s="40">
+        <v>60</v>
+      </c>
+      <c r="B63" s="41">
+        <v>16741</v>
+      </c>
+      <c r="C63" s="42">
+        <v>46287</v>
+      </c>
+      <c r="D63" s="41"/>
+      <c r="E63" s="41"/>
+      <c r="F63" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="G63" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H63" s="41"/>
+      <c r="I63" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J63" s="41">
+        <v>162003267</v>
+      </c>
+      <c r="K63" s="42">
+        <v>46285</v>
+      </c>
+      <c r="L63" s="41"/>
+      <c r="M63" s="41">
+        <v>4040</v>
+      </c>
+      <c r="N63" s="41">
+        <v>3909.44</v>
+      </c>
+      <c r="O63" s="41"/>
+      <c r="P63" s="41"/>
+      <c r="Q63" s="41"/>
+      <c r="R63" s="41"/>
+      <c r="S63" s="41"/>
+      <c r="T63" s="43">
+        <v>16.37</v>
+      </c>
+      <c r="U63" s="43">
+        <v>18.690000000000001</v>
+      </c>
+      <c r="V63" s="43">
+        <v>47.78</v>
+      </c>
+      <c r="W63" s="43">
+        <v>17.16</v>
+      </c>
+      <c r="X63" s="44">
+        <v>2477</v>
+      </c>
+      <c r="Y63" s="44"/>
+      <c r="Z63" s="45"/>
+      <c r="AA63" s="45"/>
+      <c r="AB63" s="45"/>
+      <c r="AC63" s="45"/>
+      <c r="AD63" s="45"/>
+      <c r="AE63" s="45"/>
+      <c r="AF63" s="46"/>
+      <c r="AG63" s="45"/>
+      <c r="AH63" s="47"/>
+      <c r="AI63" s="47"/>
+      <c r="AJ63" s="47"/>
+      <c r="AK63" s="47"/>
+      <c r="AL63" s="41"/>
+    </row>
+    <row r="64" spans="1:38">
+      <c r="A64" s="40">
+        <v>61</v>
+      </c>
+      <c r="B64" s="41">
+        <v>16744</v>
+      </c>
+      <c r="C64" s="42">
+        <v>46288</v>
+      </c>
+      <c r="D64" s="41"/>
+      <c r="E64" s="41"/>
+      <c r="F64" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="G64" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H64" s="41"/>
+      <c r="I64" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J64" s="41">
+        <v>142000536</v>
+      </c>
+      <c r="K64" s="42">
+        <v>46285</v>
+      </c>
+      <c r="L64" s="41"/>
+      <c r="M64" s="41">
+        <v>4139.2</v>
+      </c>
+      <c r="N64" s="41">
+        <v>4066.8</v>
+      </c>
+      <c r="O64" s="41"/>
+      <c r="P64" s="41"/>
+      <c r="Q64" s="41"/>
+      <c r="R64" s="41"/>
+      <c r="S64" s="41"/>
+      <c r="T64" s="43"/>
+      <c r="U64" s="43"/>
+      <c r="V64" s="43"/>
+      <c r="W64" s="43"/>
+      <c r="X64" s="44"/>
+      <c r="Y64" s="44"/>
+      <c r="Z64" s="45"/>
+      <c r="AA64" s="45"/>
+      <c r="AB64" s="45"/>
+      <c r="AC64" s="45"/>
+      <c r="AD64" s="45"/>
+      <c r="AE64" s="45"/>
+      <c r="AF64" s="46"/>
+      <c r="AG64" s="45"/>
+      <c r="AH64" s="47"/>
+      <c r="AI64" s="47"/>
+      <c r="AJ64" s="47"/>
+      <c r="AK64" s="47"/>
+      <c r="AL64" s="41"/>
+    </row>
+    <row r="65" spans="1:38">
+      <c r="A65" s="40">
+        <v>62</v>
+      </c>
+      <c r="B65" s="41">
+        <v>16745</v>
+      </c>
+      <c r="C65" s="42">
+        <v>46288</v>
+      </c>
+      <c r="D65" s="41"/>
+      <c r="E65" s="41"/>
+      <c r="F65" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="G65" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H65" s="41"/>
+      <c r="I65" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J65" s="41">
+        <v>162003268</v>
+      </c>
+      <c r="K65" s="42">
+        <v>46286</v>
+      </c>
+      <c r="L65" s="41"/>
+      <c r="M65" s="41">
+        <v>3917.2</v>
+      </c>
+      <c r="N65" s="48">
+        <f>M65</f>
+        <v>3917.2</v>
+      </c>
+      <c r="O65" s="41"/>
+      <c r="P65" s="41"/>
+      <c r="Q65" s="41"/>
+      <c r="R65" s="41"/>
+      <c r="S65" s="41"/>
+      <c r="T65" s="43"/>
+      <c r="U65" s="43"/>
+      <c r="V65" s="43"/>
+      <c r="W65" s="43"/>
+      <c r="X65" s="44"/>
+      <c r="Y65" s="44"/>
+      <c r="Z65" s="45"/>
+      <c r="AA65" s="45"/>
+      <c r="AB65" s="45"/>
+      <c r="AC65" s="45"/>
+      <c r="AD65" s="45"/>
+      <c r="AE65" s="45"/>
+      <c r="AF65" s="46"/>
+      <c r="AG65" s="45"/>
+      <c r="AH65" s="47"/>
+      <c r="AI65" s="47"/>
+      <c r="AJ65" s="47"/>
+      <c r="AK65" s="47"/>
+      <c r="AL65" s="41"/>
+    </row>
+    <row r="66" spans="1:38">
+      <c r="A66" s="40">
+        <v>63</v>
+      </c>
+      <c r="B66" s="41">
+        <v>16749</v>
+      </c>
+      <c r="C66" s="42">
+        <v>46289</v>
+      </c>
+      <c r="D66" s="41"/>
+      <c r="E66" s="41"/>
+      <c r="F66" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="G66" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H66" s="41"/>
+      <c r="I66" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J66" s="41">
+        <v>162006580</v>
+      </c>
+      <c r="K66" s="42">
+        <v>46287</v>
+      </c>
+      <c r="L66" s="41"/>
+      <c r="M66" s="41">
+        <v>4152.1000000000004</v>
+      </c>
+      <c r="N66" s="48">
+        <f>M66</f>
+        <v>4152.1000000000004</v>
+      </c>
+      <c r="O66" s="41"/>
+      <c r="P66" s="41"/>
+      <c r="Q66" s="41"/>
+      <c r="R66" s="41"/>
+      <c r="S66" s="41"/>
+      <c r="T66" s="43"/>
+      <c r="U66" s="43"/>
+      <c r="V66" s="43"/>
+      <c r="W66" s="43"/>
+      <c r="X66" s="44"/>
+      <c r="Y66" s="44"/>
+      <c r="Z66" s="45"/>
+      <c r="AA66" s="45"/>
+      <c r="AB66" s="45"/>
+      <c r="AC66" s="45"/>
+      <c r="AD66" s="45"/>
+      <c r="AE66" s="45"/>
+      <c r="AF66" s="46"/>
+      <c r="AG66" s="45"/>
+      <c r="AH66" s="47"/>
+      <c r="AI66" s="47"/>
+      <c r="AJ66" s="47"/>
+      <c r="AK66" s="47"/>
+      <c r="AL66" s="41"/>
+    </row>
+    <row r="67" spans="1:38">
+      <c r="A67" s="40">
+        <v>64</v>
+      </c>
+      <c r="B67" s="41">
+        <v>16750</v>
+      </c>
+      <c r="C67" s="42">
+        <v>46289</v>
+      </c>
+      <c r="D67" s="41"/>
+      <c r="E67" s="41"/>
+      <c r="F67" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G67" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H67" s="41"/>
+      <c r="I67" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J67" s="41">
+        <v>162011788</v>
+      </c>
+      <c r="K67" s="42">
+        <v>46287</v>
+      </c>
+      <c r="L67" s="41"/>
+      <c r="M67" s="41">
+        <v>3261.2</v>
+      </c>
+      <c r="N67" s="48">
+        <f>M67</f>
+        <v>3261.2</v>
+      </c>
+      <c r="O67" s="41"/>
+      <c r="P67" s="41"/>
+      <c r="Q67" s="41"/>
+      <c r="R67" s="41"/>
+      <c r="S67" s="41"/>
+      <c r="T67" s="43"/>
+      <c r="U67" s="43"/>
+      <c r="V67" s="43"/>
+      <c r="W67" s="43"/>
+      <c r="X67" s="44"/>
+      <c r="Y67" s="44"/>
+      <c r="Z67" s="45"/>
+      <c r="AA67" s="45"/>
+      <c r="AB67" s="45"/>
+      <c r="AC67" s="45"/>
+      <c r="AD67" s="45"/>
+      <c r="AE67" s="45"/>
+      <c r="AF67" s="46"/>
+      <c r="AG67" s="45"/>
+      <c r="AH67" s="47"/>
+      <c r="AI67" s="47"/>
+      <c r="AJ67" s="47"/>
+      <c r="AK67" s="47"/>
+      <c r="AL67" s="41"/>
+    </row>
+    <row r="68" spans="1:38">
+      <c r="A68" s="40">
+        <v>65</v>
+      </c>
+      <c r="B68" s="41">
+        <v>16751</v>
+      </c>
+      <c r="C68" s="42">
+        <v>46289</v>
+      </c>
+      <c r="D68" s="41"/>
+      <c r="E68" s="41"/>
+      <c r="F68" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G68" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H68" s="41"/>
+      <c r="I68" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J68" s="41">
+        <v>162011789</v>
+      </c>
+      <c r="K68" s="42">
+        <v>46287</v>
+      </c>
+      <c r="L68" s="41"/>
+      <c r="M68" s="41">
+        <v>3836.6</v>
+      </c>
+      <c r="N68" s="48">
+        <f>M68</f>
+        <v>3836.6</v>
+      </c>
+      <c r="O68" s="41"/>
+      <c r="P68" s="41"/>
+      <c r="Q68" s="41"/>
+      <c r="R68" s="41"/>
+      <c r="S68" s="41"/>
+      <c r="T68" s="43"/>
+      <c r="U68" s="43"/>
+      <c r="V68" s="43"/>
+      <c r="W68" s="43"/>
+      <c r="X68" s="44"/>
+      <c r="Y68" s="44"/>
+      <c r="Z68" s="45"/>
+      <c r="AA68" s="45"/>
+      <c r="AB68" s="45"/>
+      <c r="AC68" s="45"/>
+      <c r="AD68" s="45"/>
+      <c r="AE68" s="45"/>
+      <c r="AF68" s="46"/>
+      <c r="AG68" s="45"/>
+      <c r="AH68" s="47"/>
+      <c r="AI68" s="47"/>
+      <c r="AJ68" s="47"/>
+      <c r="AK68" s="47"/>
+      <c r="AL68" s="41"/>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="AL1:AL3"/>
